--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -1049,28 +1049,28 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3137173358551308</v>
+        <v>0.3163272478320253</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5378148515394482</v>
+        <v>0.5315363677345756</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.148467812605421</v>
+        <v>0.1521363844333992</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3064873643909752</v>
+        <v>0.3002088805861026</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3064873643909752</v>
+        <v>0.3002088805861026</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5378148515394482</v>
+        <v>0.5315363677345756</v>
       </c>
       <c r="W7" t="n">
         <v>4.1</v>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>37.64703960776137</v>
+        <v>37.20754574142029</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.64703960776137</v>
+        <v>37.20754574142029</v>
       </c>
     </row>
     <row r="8">
@@ -1665,28 +1665,28 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3670770600203078</v>
+        <v>0.3522794075213345</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4077433881239975</v>
+        <v>0.3992244010656373</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2251795518556948</v>
+        <v>0.2484961914130281</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1713797517603611</v>
+        <v>0.162860764702001</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1713797517603611</v>
+        <v>0.162860764702001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4077433881239975</v>
+        <v>0.3992244010656373</v>
       </c>
       <c r="W14" t="n">
         <v>4</v>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>28.54203716867982</v>
+        <v>27.94570807459461</v>
       </c>
       <c r="Z14" t="n">
-        <v>28.54203716867982</v>
+        <v>27.94570807459461</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,20 +562,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hK8xvrmh</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -585,85 +585,85 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>3.25</v>
+        <v>1.48</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.15</v>
+        <v>6.25</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2928767382461451</v>
+        <v>0.6386964914272737</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2644026109166588</v>
+        <v>0.2100601794027478</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4427206508371961</v>
+        <v>0.1512433291699784</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05058636453985299</v>
+        <v>0.0578978978978979</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1782451111666511</v>
+        <v>0.4436791468412691</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3571235536153105</v>
+        <v>0.3705221432445802</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4646313352180383</v>
+        <v>0.1857987099141508</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02191068438084226</v>
+        <v>-0.1950173445860046</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02191068438084226</v>
+        <v>0.1950173445860046</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4646313352180383</v>
+        <v>0.5563208531587309</v>
       </c>
       <c r="W2" t="n">
-        <v>2.15</v>
+        <v>2.616279069767442</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>32.52419346526268</v>
+        <v>38.94245972111116</v>
       </c>
       <c r="Z2" t="n">
-        <v>32.52419346526268</v>
+        <v>38.94245972111116</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rwisKhLu</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -673,85 +673,85 @@
         <v>1671</v>
       </c>
       <c r="G3" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.449677174325864</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.2552221800227877</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.2951006456513482</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.05896074646074645</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2571887055520775</v>
+        <v>0.3319918150420612</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3187289200171914</v>
+        <v>0.2821118769142622</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4240823744307311</v>
+        <v>0.3858963080436765</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.146534424073454</v>
+        <v>0.09079566239232822</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.146534424073454</v>
+        <v>0.09079566239232822</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4240823744307311</v>
+        <v>0.3858963080436765</v>
       </c>
       <c r="W3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>29.68576621015118</v>
+        <v>27.01274156305735</v>
       </c>
       <c r="Z3" t="n">
-        <v>29.68576621015118</v>
+        <v>27.01274156305735</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2u7rIWkh</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -761,85 +761,85 @@
         <v>1671</v>
       </c>
       <c r="G4" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4851944345344275</v>
+        <v>0.6098357297414951</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2365322868355333</v>
+        <v>0.2183014736949925</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2782732786300393</v>
+        <v>0.1718627965635123</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05693815987933637</v>
+        <v>0.05792635435785254</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3069573833806068</v>
+        <v>0.5605383605228289</v>
       </c>
       <c r="P4" t="n">
-        <v>0.432377296398577</v>
+        <v>0.3535581894345241</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2606653202208161</v>
+        <v>0.08590345004264675</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1958450095630437</v>
+        <v>-0.04929736921866623</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1958450095630437</v>
+        <v>-0.04929736921866623</v>
       </c>
       <c r="V4" t="n">
-        <v>0.432377296398577</v>
+        <v>0.5605383605228289</v>
       </c>
       <c r="W4" t="n">
-        <v>4</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>30.26641074790039</v>
+        <v>39.23768523659803</v>
       </c>
       <c r="Z4" t="n">
-        <v>30.26641074790039</v>
+        <v>39.23768523659803</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tW5nHj5b</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>inter miami</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -849,85 +849,85 @@
         <v>1671</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="I5" t="n">
-        <v>2.15</v>
+        <v>5.25</v>
       </c>
       <c r="J5" t="n">
-        <v>0.313989239046887</v>
+        <v>0.6018171661844011</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2478862413528055</v>
+        <v>0.2182108431661685</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4381245196003075</v>
+        <v>0.1799719906494304</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0616075071399429</v>
+        <v>0.05836574785251614</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5402763867114466</v>
+        <v>0.4065117704358618</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2716252169503502</v>
+        <v>0.4180952329923645</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1880983963382031</v>
+        <v>0.1753929965717735</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2262871476645597</v>
+        <v>0.1998843898261959</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2262871476645597</v>
+        <v>0.1998843898261959</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5402763867114466</v>
+        <v>0.4180952329923645</v>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>37.81934706980126</v>
+        <v>29.26666630946551</v>
       </c>
       <c r="Z5" t="n">
-        <v>37.81934706980126</v>
+        <v>29.26666630946551</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WA7tw22b</t>
+          <t>WYwYSm4A</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45462.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -937,85 +937,85 @@
         <v>1671</v>
       </c>
       <c r="G6" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4415584415584415</v>
+        <v>0.54584017471928</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2792207792207792</v>
+        <v>0.2360758755660886</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2792207792207792</v>
+        <v>0.2180839497146315</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05335157318741457</v>
+        <v>0.05898156429801493</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05171002128636167</v>
+        <v>0.4336241512981687</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5831063597486422</v>
+        <v>0.3839572154861549</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3651836189649961</v>
+        <v>0.1824186332156764</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.303885580527863</v>
+        <v>-0.1122160234211114</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.303885580527863</v>
+        <v>0.1122160234211114</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5831063597486422</v>
+        <v>0.5663758487018313</v>
       </c>
       <c r="W6" t="n">
-        <v>3.4</v>
+        <v>2.079231692677071</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>40.81744518240495</v>
+        <v>39.64630940912819</v>
       </c>
       <c r="Z6" t="n">
-        <v>40.81744518240495</v>
+        <v>39.64630940912819</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MTkoJCzn</t>
+          <t>APxxS7JG</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45462.98958333334</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1025,85 +1025,85 @@
         <v>1671</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5579074690051407</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="K7" t="n">
-        <v>0.231327487148473</v>
+        <v>0.2368421052631579</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2107650438463864</v>
+        <v>0.2368421052631579</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05435995536425953</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3137173358551308</v>
+        <v>0.4538576876343147</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5378148515394482</v>
+        <v>0.3445537488859154</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.148467812605421</v>
+        <v>0.20158856347977</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3064873643909752</v>
+        <v>-0.07245810183936946</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3064873643909752</v>
+        <v>0.07245810183936946</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5378148515394482</v>
+        <v>0.5461423123656852</v>
       </c>
       <c r="W7" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>37.64703960776137</v>
+        <v>38.22996186559796</v>
       </c>
       <c r="Z7" t="n">
-        <v>37.64703960776137</v>
+        <v>38.22996186559796</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>zg5jGAK4</t>
+          <t>4nxtRRYM</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>austin fc</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>los angeles fc</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1113,85 +1113,85 @@
         <v>1671</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3</v>
+        <v>1.75</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
-        <v>0.286028602860286</v>
+        <v>0.5393258426966292</v>
       </c>
       <c r="K8" t="n">
-        <v>0.242024202420242</v>
+        <v>0.2359550561797753</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4719471947194719</v>
+        <v>0.2247191011235955</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05944055944055959</v>
+        <v>0.05952380952380953</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1248404827603851</v>
+        <v>0.3797770002987284</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4023580553124324</v>
+        <v>0.2412557721298951</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4728014619271825</v>
+        <v>0.3789672275713766</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0008542672077105906</v>
+        <v>-0.1595488423979008</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0008542672077105906</v>
+        <v>0.1595488423979008</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4728014619271825</v>
+        <v>0.6202229997012716</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>2.048780487804879</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>33.09610233490277</v>
+        <v>43.41560997908901</v>
       </c>
       <c r="Z8" t="n">
-        <v>33.09610233490277</v>
+        <v>43.41560997908901</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ld9fFUZA</t>
+          <t>IktpQolT</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1201,85 +1201,85 @@
         <v>1671</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4545454545454546</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2727272727272728</v>
+        <v>0.2857142857142858</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2727272727272728</v>
+        <v>0.2857142857142858</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04761904761904745</v>
+        <v>0.06060606060606055</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2898941193190928</v>
+        <v>0.3757201307377791</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4422466191872576</v>
+        <v>0.3500274915414723</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2678592614936495</v>
+        <v>0.2742523777207485</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1695193464599848</v>
+        <v>-0.0528512978336495</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1695193464599848</v>
+        <v>0.0528512978336495</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4422466191872576</v>
+        <v>0.6242798692622209</v>
       </c>
       <c r="W9" t="n">
-        <v>3.5</v>
+        <v>1.65</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>30.95726334310803</v>
+        <v>43.69959084835546</v>
       </c>
       <c r="Z9" t="n">
-        <v>30.95726334310803</v>
+        <v>43.69959084835546</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>WKbaElkH</t>
+          <t>OWICL5dp</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1289,85 +1289,85 @@
         <v>1671</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4509283819628647</v>
+        <v>0.5129935875801552</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2705570291777188</v>
+        <v>0.2372595342558218</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2785145888594164</v>
+        <v>0.2497468781640229</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05602240896358546</v>
+        <v>0.05369843527738261</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4957383107137407</v>
+        <v>0.2618796408719433</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3722175717727494</v>
+        <v>0.3590715274375488</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1320441175135099</v>
+        <v>0.3790488316905077</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.04480992875087608</v>
+        <v>0.1293019535264847</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.04480992875087608</v>
+        <v>0.1293019535264847</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4957383107137407</v>
+        <v>0.3790488316905077</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>34.70168174996185</v>
+        <v>26.53341821833554</v>
       </c>
       <c r="Z10" t="n">
-        <v>34.70168174996185</v>
+        <v>26.53341821833554</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ABc3D84N</t>
+          <t>Sx1kytXA</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.9375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>colorado rapids</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1377,85 +1377,85 @@
         <v>1671</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>2.55</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3647199046483909</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2634088200238379</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3718712753277712</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05455002513826046</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3471049403890203</v>
+        <v>0.3086285968254135</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3545298080055802</v>
+        <v>0.5316170522423062</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2983652516053995</v>
+        <v>0.1597543509322801</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.09112098798174229</v>
+        <v>0.3210907364528325</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09112098798174229</v>
+        <v>0.3210907364528325</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3545298080055802</v>
+        <v>0.5316170522423062</v>
       </c>
       <c r="W11" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>24.81708656039061</v>
+        <v>37.21319365696143</v>
       </c>
       <c r="Z11" t="n">
-        <v>24.81708656039061</v>
+        <v>37.21319365696143</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>vo27CSJT</t>
+          <t>2NHGKPBj</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45463.02083333334</v>
+        <v>45465.9375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>colorado rapids</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1465,85 +1465,85 @@
         <v>1671</v>
       </c>
       <c r="G12" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4880098022054963</v>
+        <v>0.550173120294781</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2321022230001751</v>
+        <v>0.2160033035799371</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2798879747943288</v>
+        <v>0.2338235761252819</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05084059890372661</v>
+        <v>0.06918217633473711</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4856464530380509</v>
+        <v>0.289341441372672</v>
       </c>
       <c r="P12" t="n">
-        <v>0.378293936563841</v>
+        <v>0.243865103015309</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1360596103981081</v>
+        <v>0.4667934556120188</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.00236334916744535</v>
+        <v>0.2329698794867369</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.00236334916744535</v>
+        <v>0.2329698794867369</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4856464530380509</v>
+        <v>0.4667934556120188</v>
       </c>
       <c r="W12" t="n">
-        <v>1.95</v>
+        <v>4</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>33.99525171266357</v>
+        <v>32.67554189284132</v>
       </c>
       <c r="Z12" t="n">
-        <v>33.99525171266357</v>
+        <v>32.67554189284132</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>tflZ7nSp</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45463.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1553,85 +1553,85 @@
         <v>1671</v>
       </c>
       <c r="G13" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4971246449109679</v>
+        <v>0.6880733944954128</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2315873345804753</v>
+        <v>0.1871559633027523</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2712880205085568</v>
+        <v>0.1247706422018349</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0531769341627597</v>
+        <v>0.06862745098039214</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4721479090124855</v>
+        <v>0.6190558219313727</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3170924136355052</v>
+        <v>0.3026384164933133</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2107596773520092</v>
+        <v>0.07830576157531427</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.02497673589848237</v>
+        <v>-0.06901757256404017</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.02497673589848237</v>
+        <v>0.06901757256404017</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4721479090124855</v>
+        <v>0.3809441780686273</v>
       </c>
       <c r="W13" t="n">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>33.05035363087399</v>
+        <v>26.66609246480391</v>
       </c>
       <c r="Z13" t="n">
-        <v>33.05035363087399</v>
+        <v>26.66609246480391</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>raSHWV4o</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45463.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1641,66 +1641,154 @@
         <v>1671</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4295665634674923</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.2554179566563468</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.315015479876161</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.05814905814905802</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.5205753914335942</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.4044264527514825</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.07499815581492324</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.09100882796610194</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.09100882796610194</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.5205753914335942</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>36.4402774003516</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>36.4402774003516</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>8K42rT3c</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45465.97916666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>167</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H15" t="n">
         <v>4</v>
       </c>
-      <c r="I14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.4727272727272727</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.2363636363636364</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.2909090909090909</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.05769230769230771</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="I15" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6045340050377834</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.23727959697733</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.1581863979848867</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.05360934182590227</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="n">
-        <v>0.3670770600203078</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.4077433881239975</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.2251795518556948</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.1713797517603611</v>
-      </c>
-      <c r="T14" t="n">
+      <c r="O15" t="n">
+        <v>0.4209874955756275</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.4367556184360717</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.1422568859883006</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.1994760214587418</v>
+      </c>
+      <c r="T15" t="n">
         <v>0</v>
       </c>
-      <c r="U14" t="n">
-        <v>0.1713797517603611</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.4077433881239975</v>
-      </c>
-      <c r="W14" t="n">
+      <c r="U15" t="n">
+        <v>0.1994760214587418</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.4367556184360717</v>
+      </c>
+      <c r="W15" t="n">
         <v>4</v>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.1</t>
-        </is>
-      </c>
-      <c r="Y14" t="n">
-        <v>28.54203716867982</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>28.54203716867982</v>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>30.57289329052502</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>30.57289329052502</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -609,28 +609,28 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4436791468412691</v>
+        <v>0.4436791468412699</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3705221432445802</v>
+        <v>0.3705221432445809</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1857987099141508</v>
+        <v>0.1857987099141491</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1950173445860046</v>
+        <v>-0.1950173445860038</v>
       </c>
       <c r="T2" t="n">
         <v>-1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1950173445860046</v>
+        <v>0.1950173445860038</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5563208531587309</v>
+        <v>0.55632085315873</v>
       </c>
       <c r="W2" t="n">
         <v>2.616279069767442</v>
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>38.94245972111116</v>
+        <v>38.9424597211111</v>
       </c>
       <c r="Z2" t="n">
-        <v>38.94245972111116</v>
+        <v>38.9424597211111</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -697,28 +697,28 @@
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3319918150420612</v>
+        <v>0.3319918150420605</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2821118769142622</v>
+        <v>0.282111876914261</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3858963080436765</v>
+        <v>0.3858963080436785</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.09079566239232822</v>
+        <v>0.09079566239233022</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09079566239232822</v>
+        <v>0.09079566239233022</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3858963080436765</v>
+        <v>0.3858963080436785</v>
       </c>
       <c r="W3" t="n">
         <v>3.2</v>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>27.01274156305735</v>
+        <v>27.01274156305749</v>
       </c>
       <c r="Z3" t="n">
-        <v>27.01274156305735</v>
+        <v>27.01274156305749</v>
       </c>
     </row>
     <row r="4">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -785,28 +785,28 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5605383605228289</v>
+        <v>0.5605383605228302</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3535581894345241</v>
+        <v>0.3535581894345236</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.08590345004264675</v>
+        <v>0.08590345004264613</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.04929736921866623</v>
+        <v>-0.0492973692186649</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.04929736921866623</v>
+        <v>-0.0492973692186649</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5605383605228289</v>
+        <v>0.5605383605228302</v>
       </c>
       <c r="W4" t="n">
         <v>1.55</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>39.23768523659803</v>
+        <v>39.23768523659812</v>
       </c>
       <c r="Z4" t="n">
-        <v>39.23768523659803</v>
+        <v>39.23768523659812</v>
       </c>
     </row>
     <row r="5">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4065117704358618</v>
+        <v>0.4065117704358609</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4180952329923645</v>
+        <v>0.4180952329923648</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1753929965717735</v>
+        <v>0.1753929965717745</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1998843898261959</v>
+        <v>0.1998843898261963</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1998843898261959</v>
+        <v>0.1998843898261963</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4180952329923645</v>
+        <v>0.4180952329923648</v>
       </c>
       <c r="W5" t="n">
         <v>4.33</v>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>29.26666630946551</v>
+        <v>29.26666630946553</v>
       </c>
       <c r="Z5" t="n">
-        <v>29.26666630946551</v>
+        <v>29.26666630946553</v>
       </c>
     </row>
     <row r="6">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -961,10 +961,10 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4336241512981687</v>
+        <v>0.4336241512981688</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3839572154861549</v>
+        <v>0.3839572154861547</v>
       </c>
       <c r="Q6" t="n">
         <v>0.1824186332156764</v>
@@ -973,16 +973,16 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1122160234211114</v>
+        <v>-0.1122160234211113</v>
       </c>
       <c r="T6" t="n">
         <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1122160234211114</v>
+        <v>0.1122160234211113</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5663758487018313</v>
+        <v>0.5663758487018312</v>
       </c>
       <c r="W6" t="n">
         <v>2.079231692677071</v>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1049,28 +1049,28 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4538576876343147</v>
+        <v>0.4518940673972829</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3445537488859154</v>
+        <v>0.361204355622729</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.20158856347977</v>
+        <v>0.1869015769799884</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.07245810183936946</v>
+        <v>-0.07442172207640124</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07245810183936946</v>
+        <v>0.07442172207640124</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5461423123656852</v>
+        <v>0.5481059326027171</v>
       </c>
       <c r="W7" t="n">
         <v>2</v>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>38.22996186559796</v>
+        <v>38.3674152821902</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.22996186559796</v>
+        <v>38.3674152821902</v>
       </c>
     </row>
     <row r="8">
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1113,66 +1113,66 @@
         <v>1671</v>
       </c>
       <c r="G8" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H8" t="n">
         <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5393258426966292</v>
+        <v>0.54584017471928</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2359550561797753</v>
+        <v>0.2360758755660886</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2247191011235955</v>
+        <v>0.2180839497146315</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05952380952380953</v>
+        <v>0.05898156429801493</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3797770002987284</v>
+        <v>0.3773370378645719</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2412557721298951</v>
+        <v>0.2414047650172821</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3789672275713766</v>
+        <v>0.3812581971181459</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1595488423979008</v>
+        <v>0.1631742474035144</v>
       </c>
       <c r="T8" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1595488423979008</v>
+        <v>0.1631742474035144</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6202229997012716</v>
+        <v>0.3812581971181459</v>
       </c>
       <c r="W8" t="n">
-        <v>2.048780487804879</v>
+        <v>4.33</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>43.41560997908901</v>
+        <v>26.68807379827021</v>
       </c>
       <c r="Z8" t="n">
-        <v>43.41560997908901</v>
+        <v>26.68807379827021</v>
       </c>
     </row>
     <row r="9">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1225,28 +1225,28 @@
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3757201307377791</v>
+        <v>0.3757201307377797</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3500274915414723</v>
+        <v>0.3500274915414737</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2742523777207485</v>
+        <v>0.2742523777207464</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0528512978336495</v>
+        <v>-0.05285129783364895</v>
       </c>
       <c r="T9" t="n">
         <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0528512978336495</v>
+        <v>0.05285129783364895</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6242798692622209</v>
+        <v>0.6242798692622203</v>
       </c>
       <c r="W9" t="n">
         <v>1.65</v>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>43.69959084835546</v>
+        <v>43.69959084835543</v>
       </c>
       <c r="Z9" t="n">
-        <v>43.69959084835546</v>
+        <v>43.69959084835543</v>
       </c>
     </row>
     <row r="10">
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1310,45 +1310,45 @@
         <v>0.05369843527738261</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2618796408719433</v>
+        <v>0.3720081039411632</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3590715274375488</v>
+        <v>0.337583047308818</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3790488316905077</v>
+        <v>0.2904088487500189</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1293019535264847</v>
+        <v>-0.140985483638992</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1293019535264847</v>
+        <v>0.140985483638992</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3790488316905077</v>
+        <v>0.6279918960588368</v>
       </c>
       <c r="W10" t="n">
-        <v>3.8</v>
+        <v>1.948717948717949</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>26.53341821833554</v>
+        <v>43.95943272411857</v>
       </c>
       <c r="Z10" t="n">
-        <v>26.53341821833554</v>
+        <v>43.95943272411857</v>
       </c>
     </row>
     <row r="11">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45465.9375</v>
+        <v>45466.0625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1401,28 +1401,28 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3086285968254135</v>
+        <v>0.3086285968254163</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5316170522423062</v>
+        <v>0.5316170522423029</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1597543509322801</v>
+        <v>0.1597543509322807</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3210907364528325</v>
+        <v>0.3210907364528293</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3210907364528325</v>
+        <v>0.3210907364528293</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5316170522423062</v>
+        <v>0.5316170522423029</v>
       </c>
       <c r="W11" t="n">
         <v>4.5</v>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>37.21319365696143</v>
+        <v>37.2131936569612</v>
       </c>
       <c r="Z11" t="n">
-        <v>37.21319365696143</v>
+        <v>37.2131936569612</v>
       </c>
     </row>
     <row r="12">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45465.9375</v>
+        <v>45466.0625</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1489,28 +1489,28 @@
         <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0.289341441372672</v>
+        <v>0.2928339855178089</v>
       </c>
       <c r="P12" t="n">
-        <v>0.243865103015309</v>
+        <v>0.2472243808527774</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4667934556120188</v>
+        <v>0.4599416336294134</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2329698794867369</v>
+        <v>0.2261180575041315</v>
       </c>
       <c r="T12" t="n">
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2329698794867369</v>
+        <v>0.2261180575041315</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4667934556120188</v>
+        <v>0.4599416336294134</v>
       </c>
       <c r="W12" t="n">
         <v>4</v>
@@ -1521,10 +1521,10 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>32.67554189284132</v>
+        <v>32.19591435405894</v>
       </c>
       <c r="Z12" t="n">
-        <v>32.67554189284132</v>
+        <v>32.19591435405894</v>
       </c>
     </row>
     <row r="13">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1577,28 +1577,28 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6190558219313727</v>
+        <v>0.6149171520084532</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3026384164933133</v>
+        <v>0.3027250780585539</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.07830576157531427</v>
+        <v>0.0823577699329931</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.06901757256404017</v>
+        <v>-0.07315624248695962</v>
       </c>
       <c r="T13" t="n">
         <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.06901757256404017</v>
+        <v>0.07315624248695962</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3809441780686273</v>
+        <v>0.3850828479915468</v>
       </c>
       <c r="W13" t="n">
         <v>3</v>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>26.66609246480391</v>
+        <v>26.95579935940827</v>
       </c>
       <c r="Z13" t="n">
-        <v>26.66609246480391</v>
+        <v>26.95579935940827</v>
       </c>
     </row>
     <row r="14">
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1665,28 +1665,28 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5205753914335942</v>
+        <v>0.520575391433595</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4044264527514825</v>
+        <v>0.4044264527514819</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.07499815581492324</v>
+        <v>0.07499815581492314</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.09100882796610194</v>
+        <v>0.09100882796610271</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09100882796610194</v>
+        <v>0.09100882796610271</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5205753914335942</v>
+        <v>0.520575391433595</v>
       </c>
       <c r="W14" t="n">
         <v>2.2</v>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>36.4402774003516</v>
+        <v>36.44027740035165</v>
       </c>
       <c r="Z14" t="n">
-        <v>36.4402774003516</v>
+        <v>36.44027740035165</v>
       </c>
     </row>
     <row r="15">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1753,28 +1753,28 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4209874955756275</v>
+        <v>0.420987495575627</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4367556184360717</v>
+        <v>0.4367556184360714</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1422568859883006</v>
+        <v>0.1422568859883015</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1994760214587418</v>
+        <v>0.1994760214587414</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1994760214587418</v>
+        <v>0.1994760214587414</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4367556184360717</v>
+        <v>0.4367556184360714</v>
       </c>
       <c r="W15" t="n">
         <v>4</v>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>30.57289329052502</v>
+        <v>30.572893290525</v>
       </c>
       <c r="Z15" t="n">
-        <v>30.57289329052502</v>
+        <v>30.572893290525</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -1577,28 +1577,28 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6149171520084532</v>
+        <v>0.6125718165728418</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3027250780585539</v>
+        <v>0.3031664238939512</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0823577699329931</v>
+        <v>0.0842617595332071</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.07315624248695962</v>
+        <v>-0.07550157792257106</v>
       </c>
       <c r="T13" t="n">
         <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07315624248695962</v>
+        <v>0.07550157792257106</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3850828479915468</v>
+        <v>0.3874281834271582</v>
       </c>
       <c r="W13" t="n">
         <v>3</v>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>26.95579935940827</v>
+        <v>27.11997283990108</v>
       </c>
       <c r="Z13" t="n">
-        <v>26.95579935940827</v>
+        <v>27.11997283990108</v>
       </c>
     </row>
     <row r="14">

--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -1049,28 +1049,28 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4518940673972829</v>
+        <v>0.4536949757806798</v>
       </c>
       <c r="P7" t="n">
-        <v>0.361204355622729</v>
+        <v>0.3438612530005293</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1869015769799884</v>
+        <v>0.2024437712187911</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.07442172207640124</v>
+        <v>-0.07262081369300438</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07442172207640124</v>
+        <v>0.07262081369300438</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5481059326027171</v>
+        <v>0.5463050242193201</v>
       </c>
       <c r="W7" t="n">
         <v>2</v>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>38.3674152821902</v>
+        <v>38.24135169535241</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.3674152821902</v>
+        <v>38.24135169535241</v>
       </c>
     </row>
     <row r="8">
@@ -1310,45 +1310,45 @@
         <v>0.05369843527738261</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3720081039411632</v>
+        <v>0.261879640871944</v>
       </c>
       <c r="P10" t="n">
-        <v>0.337583047308818</v>
+        <v>0.3590715274375495</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2904088487500189</v>
+        <v>0.3790488316905065</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.140985483638992</v>
+        <v>0.1293019535264836</v>
       </c>
       <c r="T10" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.140985483638992</v>
+        <v>0.1293019535264836</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6279918960588368</v>
+        <v>0.3790488316905065</v>
       </c>
       <c r="W10" t="n">
-        <v>1.948717948717949</v>
+        <v>3.8</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>43.95943272411857</v>
+        <v>26.53341821833546</v>
       </c>
       <c r="Z10" t="n">
-        <v>43.95943272411857</v>
+        <v>26.53341821833546</v>
       </c>
     </row>
     <row r="11">
@@ -1577,28 +1577,28 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6125718165728418</v>
+        <v>0.6144560676244835</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3031664238939512</v>
+        <v>0.3028120818651876</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0842617595332071</v>
+        <v>0.08273185051032889</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.07550157792257106</v>
+        <v>-0.07361732687092937</v>
       </c>
       <c r="T13" t="n">
         <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07550157792257106</v>
+        <v>0.07361732687092937</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3874281834271582</v>
+        <v>0.3855439323755165</v>
       </c>
       <c r="W13" t="n">
         <v>3</v>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>27.11997283990108</v>
+        <v>26.98807526628616</v>
       </c>
       <c r="Z13" t="n">
-        <v>27.11997283990108</v>
+        <v>26.98807526628616</v>
       </c>
     </row>
     <row r="14">

--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -849,66 +849,66 @@
         <v>1671</v>
       </c>
       <c r="G5" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="H5" t="n">
         <v>4.33</v>
       </c>
       <c r="I5" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6018171661844011</v>
+        <v>0.5888816959792844</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2182108431661685</v>
+        <v>0.2203206345234275</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1799719906494304</v>
+        <v>0.1907976694972882</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05836574785251614</v>
+        <v>0.0482308328343739</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4065117704358609</v>
+        <v>0.4061314979160774</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4180952329923648</v>
+        <v>0.3980054538324055</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1753929965717745</v>
+        <v>0.1958630482515173</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1998843898261963</v>
+        <v>-0.182750198063207</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1998843898261963</v>
+        <v>0.182750198063207</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4180952329923648</v>
+        <v>0.5938685020839225</v>
       </c>
       <c r="W5" t="n">
-        <v>4.33</v>
+        <v>2.320471596998928</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>29.26666630946553</v>
+        <v>41.57079514587458</v>
       </c>
       <c r="Z5" t="n">
-        <v>29.26666630946553</v>
+        <v>41.57079514587458</v>
       </c>
     </row>
     <row r="6">
@@ -961,28 +961,28 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4336241512981688</v>
+        <v>0.4342780967767457</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3839572154861547</v>
+        <v>0.3880867595947963</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1824186332156764</v>
+        <v>0.1776351436284577</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1122160234211113</v>
+        <v>-0.1115620779425343</v>
       </c>
       <c r="T6" t="n">
         <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1122160234211113</v>
+        <v>0.1115620779425343</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5663758487018312</v>
+        <v>0.5657219032232543</v>
       </c>
       <c r="W6" t="n">
         <v>2.079231692677071</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>39.64630940912819</v>
+        <v>39.6005332256278</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.64630940912819</v>
+        <v>39.6005332256278</v>
       </c>
     </row>
     <row r="7">
@@ -1025,66 +1025,66 @@
         <v>1671</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.4998268098372012</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2368421052631579</v>
+        <v>0.2435053688950468</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2368421052631579</v>
+        <v>0.2566678212677519</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.05299631615421085</v>
       </c>
       <c r="N7" t="n">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4536949757806798</v>
+        <v>0.4518940673972829</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3438612530005293</v>
+        <v>0.361204355622729</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2024437712187911</v>
+        <v>0.1869015769799884</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.07262081369300438</v>
+        <v>-0.0479327424399183</v>
       </c>
       <c r="T7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07262081369300438</v>
+        <v>-0.0479327424399183</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5463050242193201</v>
+        <v>0.4518940673972829</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>38.24135169535241</v>
+        <v>31.63258471780981</v>
       </c>
       <c r="Z7" t="n">
-        <v>38.24135169535241</v>
+        <v>31.63258471780981</v>
       </c>
     </row>
     <row r="8">
@@ -1201,25 +1201,25 @@
         <v>1671</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="H9" t="n">
         <v>3.3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.4192972007147112</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2857142857142858</v>
+        <v>0.2858844550327576</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2857142857142858</v>
+        <v>0.2948183442525313</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06060606060606055</v>
+        <v>0.0599747474747474</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
@@ -1237,30 +1237,30 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.05285129783364895</v>
+        <v>-0.0435770699769315</v>
       </c>
       <c r="T9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.05285129783364895</v>
+        <v>-0.0435770699769315</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6242798692622203</v>
+        <v>0.3757201307377797</v>
       </c>
       <c r="W9" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>43.69959084835543</v>
+        <v>26.30040915164458</v>
       </c>
       <c r="Z9" t="n">
-        <v>43.69959084835543</v>
+        <v>26.30040915164458</v>
       </c>
     </row>
     <row r="10">
@@ -1310,45 +1310,45 @@
         <v>0.05369843527738261</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.261879640871944</v>
+        <v>0.3720081039411632</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3590715274375495</v>
+        <v>0.337583047308818</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3790488316905065</v>
+        <v>0.2904088487500189</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1293019535264836</v>
+        <v>-0.140985483638992</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1293019535264836</v>
+        <v>0.140985483638992</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3790488316905065</v>
+        <v>0.6279918960588368</v>
       </c>
       <c r="W10" t="n">
-        <v>3.8</v>
+        <v>1.948717948717949</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>26.53341821833546</v>
+        <v>43.95943272411857</v>
       </c>
       <c r="Z10" t="n">
-        <v>26.53341821833546</v>
+        <v>43.95943272411857</v>
       </c>
     </row>
     <row r="11">
@@ -1377,25 +1377,25 @@
         <v>1671</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6543046357615894</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.1997350993377483</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.1459602649006622</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.05402764204942079</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1413,19 +1413,19 @@
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3210907364528293</v>
+        <v>0.3318819529045546</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3210907364528293</v>
+        <v>0.3318819529045546</v>
       </c>
       <c r="V11" t="n">
         <v>0.5316170522423029</v>
       </c>
       <c r="W11" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -1465,25 +1465,25 @@
         <v>1671</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="H12" t="n">
         <v>4.33</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.550173120294781</v>
+        <v>0.5362840799830516</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2160033035799371</v>
+        <v>0.2167429884458061</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2338235761252819</v>
+        <v>0.2469729315711422</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06918217633473711</v>
+        <v>0.06553334838250358</v>
       </c>
       <c r="N12" t="n">
         <v>2</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2261180575041315</v>
+        <v>0.2129687020582712</v>
       </c>
       <c r="T12" t="n">
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2261180575041315</v>
+        <v>0.2129687020582712</v>
       </c>
       <c r="V12" t="n">
         <v>0.4599416336294134</v>
       </c>
       <c r="W12" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -1556,19 +1556,19 @@
         <v>1.36</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="I13" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
         <v>0.6880733944954128</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1871559633027523</v>
+        <v>0.1782437745740498</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1247706422018349</v>
+        <v>0.1336828309305373</v>
       </c>
       <c r="M13" t="n">
         <v>0.06862745098039214</v>
@@ -1577,28 +1577,28 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6144560676244835</v>
+        <v>0.6171776308469605</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3028120818651876</v>
+        <v>0.3042189688659127</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.08273185051032889</v>
+        <v>0.07860340028712649</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.07361732687092937</v>
+        <v>-0.07089576364845229</v>
       </c>
       <c r="T13" t="n">
         <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07361732687092937</v>
+        <v>0.07089576364845229</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3855439323755165</v>
+        <v>0.3828223691530395</v>
       </c>
       <c r="W13" t="n">
         <v>3</v>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>26.98807526628616</v>
+        <v>26.79756584071276</v>
       </c>
       <c r="Z13" t="n">
-        <v>26.98807526628616</v>
+        <v>26.79756584071276</v>
       </c>
     </row>
     <row r="14">
@@ -1729,25 +1729,25 @@
         <v>1671</v>
       </c>
       <c r="G15" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6045340050377834</v>
+        <v>0.6538661131292164</v>
       </c>
       <c r="K15" t="n">
-        <v>0.23727959697733</v>
+        <v>0.210690192008303</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1581863979848867</v>
+        <v>0.1354436948624805</v>
       </c>
       <c r="M15" t="n">
-        <v>0.05360934182590227</v>
+        <v>0.05473453749315826</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1765,19 +1765,19 @@
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1994760214587414</v>
+        <v>0.2260654264277684</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1994760214587414</v>
+        <v>0.2260654264277684</v>
       </c>
       <c r="V15" t="n">
         <v>0.4367556184360714</v>
       </c>
       <c r="W15" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>

--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1310,45 +1310,45 @@
         <v>0.05369843527738261</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3720081039411632</v>
+        <v>0.261879640871944</v>
       </c>
       <c r="P10" t="n">
-        <v>0.337583047308818</v>
+        <v>0.3590715274375495</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2904088487500189</v>
+        <v>0.3790488316905065</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.140985483638992</v>
+        <v>0.1293019535264836</v>
       </c>
       <c r="T10" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.140985483638992</v>
+        <v>0.1293019535264836</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6279918960588368</v>
+        <v>0.3790488316905065</v>
       </c>
       <c r="W10" t="n">
-        <v>1.948717948717949</v>
+        <v>3.8</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.05</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>43.95943272411857</v>
+        <v>26.53341821833546</v>
       </c>
       <c r="Z10" t="n">
-        <v>43.95943272411857</v>
+        <v>26.53341821833546</v>
       </c>
     </row>
     <row r="11">
@@ -1577,28 +1577,28 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6171776308469605</v>
+        <v>0.6145717138326878</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3042189688659127</v>
+        <v>0.3027902689485072</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.07860340028712649</v>
+        <v>0.08263801721880513</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.07089576364845229</v>
+        <v>-0.073501680662725</v>
       </c>
       <c r="T13" t="n">
         <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07089576364845229</v>
+        <v>0.073501680662725</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3828223691530395</v>
+        <v>0.3854282861673122</v>
       </c>
       <c r="W13" t="n">
         <v>3</v>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>26.79756584071276</v>
+        <v>26.97998003171185</v>
       </c>
       <c r="Z13" t="n">
-        <v>26.79756584071276</v>
+        <v>26.97998003171185</v>
       </c>
     </row>
     <row r="14">
@@ -1789,6 +1789,1842 @@
       </c>
       <c r="Z15" t="n">
         <v>30.572893290525</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45471.97916666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>167</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.2462720620015046</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.4923339539454937</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2613939840530014</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.5076660460545063</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>35.53662322381544</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>35.53662322381544</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>167</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.4486050669888325</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.4047008090404339</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1466941239707336</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.5513949330111676</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>38.59764531078173</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>38.59764531078173</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>167</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.3145692862666382</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.4692743552439834</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2161563584893785</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.5307256447560167</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>37.15079513292117</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>37.15079513292117</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>167</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.3395212219234734</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.2837467714942478</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.3767320065822789</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.6232679934177211</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>43.62875953924048</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>43.62875953924048</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>167</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.319004676081902</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.4197691100698566</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.2612262138482416</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.5802308899301434</v>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>40.61616229511004</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>40.61616229511004</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>167</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.3468466868897144</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.3604566226280601</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.2926966904822257</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.6395433773719399</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>44.76803641603579</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>44.76803641603579</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>167</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.352099940595717</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.4534281625400888</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.194471896864194</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.5465718374599111</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>38.26002862219378</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>38.26002862219378</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>167</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.1884751250500326</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.2882272408643515</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.5232976340856157</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>0.4767023659143843</v>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>33.3691656140069</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>33.3691656140069</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>167</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.4491415382196292</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.3649273122968265</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.1859311494835444</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>0.5508584617803708</v>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
+        <v>38.56009232462596</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>38.56009232462596</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>167</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.5262868708033219</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.3324678315859552</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.1412452976107228</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="n">
+        <v>0.4737131291966781</v>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>33.15991904376747</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>33.15991904376747</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>167</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.603789322280942</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.3291009915269105</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.06710968619214784</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="n">
+        <v>0.396210677719058</v>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y26" t="n">
+        <v>27.73474744033406</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>27.73474744033406</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>167</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.3410847389107385</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.4719125839273521</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.1870026771619094</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="n">
+        <v>0.5280874160726479</v>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y27" t="n">
+        <v>36.96611912508535</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>36.96611912508535</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>167</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.458906160045076</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.4271192785075237</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.1139745614474004</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>0.5410938399549241</v>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y28" t="n">
+        <v>37.87656879684469</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>37.87656879684469</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>167</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.4542204032452292</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.3865699443481483</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.1592096524066227</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>0.5457795967547708</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y29" t="n">
+        <v>38.20457177283396</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>38.20457177283396</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>167</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.5050016708574175</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.3849675921712908</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.1100307369712915</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>0.4949983291425825</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y30" t="n">
+        <v>34.64988303998077</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>34.64988303998077</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>167</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.182866834220039</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.2334437671118067</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.5836893986681545</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>0.4163106013318455</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y31" t="n">
+        <v>29.14174209322918</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>29.14174209322918</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>167</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>2</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.2902861035528271</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.33017548571028</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.3795384107368928</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>0.6204615892631072</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y32" t="n">
+        <v>43.43231124841751</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>43.43231124841751</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>167</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.4444862769605148</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.3738661777520266</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.1816475452874586</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>0.5555137230394852</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y33" t="n">
+        <v>38.88596061276397</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>38.88596061276397</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>167</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.1556738986571048</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.4360717482454501</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.4082543530974453</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="n">
+        <v>0.5639282517545499</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y34" t="n">
+        <v>39.47497762281849</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>39.47497762281849</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45476.98958333334</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>167</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.2291534607267637</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.361229768531829</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.4096167707414073</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="n">
+        <v>0.5903832292585927</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y35" t="n">
+        <v>41.32682604810149</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>41.32682604810149</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>167</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.4395550098211475</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.4157662140662979</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.1446787761125546</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="n">
+        <v>0.5604449901788525</v>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y36" t="n">
+        <v>39.23114931251968</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>39.23114931251968</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>167</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.3588073437515735</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.3478863234417136</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.2933063328067126</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="n">
+        <v>0.6411926562484265</v>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y37" t="n">
+        <v>44.88348593738985</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>44.88348593738985</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>167</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.4478269336701768</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.3227439799731163</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.2294290863567066</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="n">
+        <v>0.5521730663298232</v>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y38" t="n">
+        <v>38.65211464308763</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>38.65211464308763</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45477.0625</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>167</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.3640386993361091</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.3611765105361796</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.2747847901277112</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>0.6359613006638909</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y39" t="n">
+        <v>44.51729104647237</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>44.51729104647237</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45478.02083333334</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>167</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.3336436547157847</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.4931748276163314</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.1731815176678841</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="n">
+        <v>0.5068251723836686</v>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y40" t="n">
+        <v>35.4777620668568</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>35.4777620668568</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45478.0625</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>167</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.3032410599203441</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.4777524411613178</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.219006498918338</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="n">
+        <v>0.5222475588386822</v>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y41" t="n">
+        <v>36.55732911870776</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>36.55732911870776</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45478.10416666666</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>167</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.3204829122770161</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.4160459857279659</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.2634711019950181</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="n">
+        <v>0.5839540142720341</v>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.05</t>
+        </is>
+      </c>
+      <c r="Y42" t="n">
+        <v>40.87678099904239</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>40.87678099904239</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -585,66 +585,66 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="I2" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6386964914272737</v>
+        <v>0.6558682952734998</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2100601794027478</v>
+        <v>0.1988316516197557</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1512433291699784</v>
+        <v>0.1453000531067446</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0578978978978979</v>
+        <v>0.05881691408007184</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.442947785562681</v>
+        <v>0.4881284508421808</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3696567110004065</v>
+        <v>0.3187793659702348</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1873955034369123</v>
+        <v>0.1930921831875844</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1957487058645927</v>
+        <v>-0.167739844431319</v>
       </c>
       <c r="T2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1957487058645927</v>
+        <v>-0.167739844431319</v>
       </c>
       <c r="V2" t="n">
-        <v>0.557052214437319</v>
+        <v>0.4881284508421808</v>
       </c>
       <c r="W2" t="n">
-        <v>2.616279069767442</v>
+        <v>1.44</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>38.99365501061233</v>
+        <v>34.16899155895265</v>
       </c>
       <c r="Z2" t="n">
-        <v>38.99365501061233</v>
+        <v>34.16899155895265</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -694,45 +694,45 @@
         <v>0.05896074646074645</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.330849415970903</v>
+        <v>0.1768895942076784</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2884875394026187</v>
+        <v>0.4143362044827341</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3806630446264782</v>
+        <v>0.4087742013095875</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.08556239897512991</v>
+        <v>0.1591140244599464</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.08556239897512991</v>
+        <v>0.1591140244599464</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3806630446264782</v>
+        <v>0.4143362044827341</v>
       </c>
       <c r="W3" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>26.64641312385347</v>
+        <v>29.00353431379139</v>
       </c>
       <c r="Z3" t="n">
-        <v>26.64641312385347</v>
+        <v>29.00353431379139</v>
       </c>
     </row>
     <row r="4">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -761,66 +761,66 @@
         <v>1671</v>
       </c>
       <c r="G4" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="H4" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6098357297414951</v>
+        <v>0.6342525399129173</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2183014736949925</v>
+        <v>0.2002902757619739</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1718627965635123</v>
+        <v>0.1654571843251089</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05792635435785254</v>
+        <v>0.05110602593440117</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5622116073024658</v>
+        <v>0.2719369575128672</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3421246695652593</v>
+        <v>0.5300255846962728</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.09566372313227506</v>
+        <v>0.19803745779086</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.04762412243902936</v>
+        <v>0.3297353089342989</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.04762412243902936</v>
+        <v>0.3297353089342989</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5622116073024658</v>
+        <v>0.5300255846962728</v>
       </c>
       <c r="W4" t="n">
-        <v>1.55</v>
+        <v>4.75</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>39.3548125111726</v>
+        <v>37.1017909287391</v>
       </c>
       <c r="Z4" t="n">
-        <v>39.3548125111726</v>
+        <v>37.1017909287391</v>
       </c>
     </row>
     <row r="5">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -849,66 +849,66 @@
         <v>1671</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="H5" t="n">
         <v>4.33</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5888816959792844</v>
+        <v>0.6098357297414951</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2203206345234275</v>
+        <v>0.2183014736949925</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1907976694972882</v>
+        <v>0.1718627965635123</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0482308328343739</v>
+        <v>0.05792635435785254</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4064097840638316</v>
+        <v>0.5517293360907328</v>
       </c>
       <c r="P5" t="n">
-        <v>0.406249628466087</v>
+        <v>0.2942182089095676</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1873405874700815</v>
+        <v>0.1540524549996996</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1824719119154528</v>
+        <v>-0.05810639365076231</v>
       </c>
       <c r="T5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1824719119154528</v>
+        <v>-0.05810639365076231</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5935902159361683</v>
+        <v>0.5517293360907328</v>
       </c>
       <c r="W5" t="n">
-        <v>2.320471596998928</v>
+        <v>1.55</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>41.55131511553179</v>
+        <v>38.6210535263513</v>
       </c>
       <c r="Z5" t="n">
-        <v>41.55131511553179</v>
+        <v>38.6210535263513</v>
       </c>
     </row>
     <row r="6">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>1671</v>
       </c>
       <c r="G6" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
@@ -946,57 +946,57 @@
         <v>4.33</v>
       </c>
       <c r="J6" t="n">
-        <v>0.54584017471928</v>
+        <v>0.550173120294781</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.2338235761252819</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.2160033035799371</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.06918217633473711</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.431972689407671</v>
+        <v>0.2361309624244033</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3757237719572734</v>
+        <v>0.4836453918188118</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1923035386350555</v>
+        <v>0.2802236457567848</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.113867485311609</v>
+        <v>0.2498218156935299</v>
       </c>
       <c r="T6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.113867485311609</v>
+        <v>0.2498218156935299</v>
       </c>
       <c r="V6" t="n">
-        <v>0.568027310592329</v>
+        <v>0.4836453918188118</v>
       </c>
       <c r="W6" t="n">
-        <v>2.079231692677071</v>
+        <v>4</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>39.76191174146303</v>
+        <v>33.85517742731682</v>
       </c>
       <c r="Z6" t="n">
-        <v>39.76191174146303</v>
+        <v>33.85517742731682</v>
       </c>
     </row>
     <row r="7">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45465.85416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1025,66 +1025,66 @@
         <v>1671</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="n">
         <v>3.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4998268098372012</v>
+        <v>0.4953320415712524</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2435053688950468</v>
+        <v>0.2489695261581821</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2566678212677519</v>
+        <v>0.2556984322705654</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05299631615421085</v>
+        <v>0.05698837443119609</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4352110096174183</v>
+        <v>0.1853488118649174</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4322347323892172</v>
+        <v>0.4586399964177667</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1325542579933644</v>
+        <v>0.3560111917173159</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.06461580021978297</v>
+        <v>0.2096704702595846</v>
       </c>
       <c r="T7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06461580021978297</v>
+        <v>0.2096704702595846</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5647889903825818</v>
+        <v>0.4586399964177667</v>
       </c>
       <c r="W7" t="n">
-        <v>1.898684210526316</v>
+        <v>3.8</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>39.53522932678072</v>
+        <v>32.10479974924367</v>
       </c>
       <c r="Z7" t="n">
-        <v>39.53522932678072</v>
+        <v>32.10479974924367</v>
       </c>
     </row>
     <row r="8">
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1134,45 +1134,45 @@
         <v>0.05898156429801493</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4585357639156413</v>
+        <v>0.3723226691402557</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3362499079698303</v>
+        <v>0.1948158673714422</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2052143281145281</v>
+        <v>0.4328614634883022</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.08730441080363877</v>
+        <v>0.2147775137736708</v>
       </c>
       <c r="T8" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08730441080363877</v>
+        <v>0.2147775137736708</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5414642360843587</v>
+        <v>0.4328614634883022</v>
       </c>
       <c r="W8" t="n">
-        <v>2.079231692677071</v>
+        <v>4.33</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>37.90249652590511</v>
+        <v>30.30030244418116</v>
       </c>
       <c r="Z8" t="n">
-        <v>37.90249652590511</v>
+        <v>30.30030244418116</v>
       </c>
     </row>
     <row r="9">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1201,66 +1201,66 @@
         <v>1671</v>
       </c>
       <c r="G9" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4192972007147112</v>
+        <v>0.4125736738703341</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2858844550327576</v>
+        <v>0.2711198428290766</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2948183442525313</v>
+        <v>0.3163064833005894</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0599747474747474</v>
+        <v>0.05383022774327118</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3762812603021553</v>
+        <v>0.3328004140349778</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3362450625534014</v>
+        <v>0.426784241468339</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2874736771444432</v>
+        <v>0.2404153444966831</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.04301594041255591</v>
+        <v>0.1556643986392624</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.04301594041255591</v>
+        <v>0.1556643986392624</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3762812603021553</v>
+        <v>0.426784241468339</v>
       </c>
       <c r="W9" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>26.33968822115087</v>
+        <v>29.87489690278373</v>
       </c>
       <c r="Z9" t="n">
-        <v>26.33968822115087</v>
+        <v>29.87489690278373</v>
       </c>
     </row>
     <row r="10">
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45466.02083333334</v>
+        <v>45465.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1289,66 +1289,66 @@
         <v>1671</v>
       </c>
       <c r="G10" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5129935875801552</v>
+        <v>0.4959022086400889</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2372595342558218</v>
+        <v>0.2255174329768023</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2497468781640229</v>
+        <v>0.2785803583831088</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05369843527738261</v>
+        <v>0.05577309457814539</v>
       </c>
       <c r="N10" t="n">
         <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2433648073553128</v>
+        <v>0.2032595674696957</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3403588267448442</v>
+        <v>0.2226757413052</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4162763658998431</v>
+        <v>0.5740646912251044</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1665294877358202</v>
+        <v>0.2954843328419956</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1665294877358202</v>
+        <v>0.2954843328419956</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4162763658998431</v>
+        <v>0.5740646912251044</v>
       </c>
       <c r="W10" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>29.13934561298902</v>
+        <v>40.18452838575731</v>
       </c>
       <c r="Z10" t="n">
-        <v>29.13934561298902</v>
+        <v>40.18452838575731</v>
       </c>
     </row>
     <row r="11">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45465.9375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1377,66 +1377,66 @@
         <v>1671</v>
       </c>
       <c r="G11" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="H11" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="I11" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6543046357615894</v>
+        <v>0.6849315068493151</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1997350993377483</v>
+        <v>0.1800391389432485</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1459602649006622</v>
+        <v>0.1350293542074364</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05402764204942079</v>
+        <v>0.05797101449275366</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3128952493758644</v>
+        <v>0.2818478117601487</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5361372692209605</v>
+        <v>0.4166745314495733</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.150967481403175</v>
+        <v>0.3014776567902779</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3364021698832122</v>
+        <v>0.2366353925063248</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3364021698832122</v>
+        <v>0.2366353925063248</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5361372692209605</v>
+        <v>0.4166745314495733</v>
       </c>
       <c r="W11" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>37.52960884546724</v>
+        <v>29.16721720147013</v>
       </c>
       <c r="Z11" t="n">
-        <v>37.52960884546724</v>
+        <v>29.16721720147013</v>
       </c>
     </row>
     <row r="12">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45466.0625</v>
+        <v>45465.9375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1489,42 +1489,42 @@
         <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2957512568246276</v>
+        <v>0.2679463459069347</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2512322781440824</v>
+        <v>0.2404162183091151</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4530164650312902</v>
+        <v>0.4916374357839501</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2169405894652016</v>
+        <v>0.2555615602178616</v>
       </c>
       <c r="T12" t="n">
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2169405894652016</v>
+        <v>0.2555615602178616</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4530164650312902</v>
+        <v>0.4916374357839501</v>
       </c>
       <c r="W12" t="n">
         <v>4</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>31.71115255219031</v>
+        <v>34.41462050487651</v>
       </c>
       <c r="Z12" t="n">
-        <v>31.71115255219031</v>
+        <v>34.41462050487651</v>
       </c>
     </row>
     <row r="13">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1553,66 +1553,66 @@
         <v>1671</v>
       </c>
       <c r="G13" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="H13" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6880733944954128</v>
+        <v>0.6845564074479737</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1782437745740498</v>
+        <v>0.1642935377875137</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1336828309305373</v>
+        <v>0.1511500547645126</v>
       </c>
       <c r="M13" t="n">
-        <v>0.06862745098039214</v>
+        <v>0.0585507246376813</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6288124535672187</v>
+        <v>0.3869700516647428</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3013673527911105</v>
+        <v>0.4439708949612933</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.06982019364167102</v>
+        <v>0.1690590533739638</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.05926094092819412</v>
+        <v>0.2796773571737797</v>
       </c>
       <c r="T13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.05926094092819412</v>
+        <v>0.2796773571737797</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3711875464327813</v>
+        <v>0.4439708949612933</v>
       </c>
       <c r="W13" t="n">
-        <v>3</v>
+        <v>5.75</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>25.98312825029469</v>
+        <v>31.07796264729053</v>
       </c>
       <c r="Z13" t="n">
-        <v>25.98312825029469</v>
+        <v>31.07796264729053</v>
       </c>
     </row>
     <row r="14">
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1641,66 +1641,66 @@
         <v>1671</v>
       </c>
       <c r="G14" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I14" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J14" t="n">
-        <v>0.439632042928325</v>
+        <v>0.4512126339537507</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2554618627826753</v>
+        <v>0.2526790750141004</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3049060942889996</v>
+        <v>0.2961082910321489</v>
       </c>
       <c r="M14" t="n">
-        <v>0.05796719450132803</v>
+        <v>0.05535714285714288</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5201066341798269</v>
+        <v>0.3641650161969446</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4046451603515387</v>
+        <v>0.2900694571601281</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.07524820546863475</v>
+        <v>0.3457655266429275</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.08047459125150191</v>
+        <v>-0.08704761775680608</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.08047459125150191</v>
+        <v>-0.08704761775680608</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5201066341798269</v>
+        <v>0.3641650161969446</v>
       </c>
       <c r="W14" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>36.40746439258788</v>
+        <v>25.49155113378612</v>
       </c>
       <c r="Z14" t="n">
-        <v>36.40746439258788</v>
+        <v>25.49155113378612</v>
       </c>
     </row>
     <row r="15">
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1729,66 +1729,66 @@
         <v>1671</v>
       </c>
       <c r="G15" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6538661131292164</v>
+        <v>0.6175562417291575</v>
       </c>
       <c r="K15" t="n">
-        <v>0.210690192008303</v>
+        <v>0.2249669166299073</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1354436948624805</v>
+        <v>0.1574768416409351</v>
       </c>
       <c r="M15" t="n">
-        <v>0.05473453749315826</v>
+        <v>0.05835667600373484</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3745130758574692</v>
+        <v>0.2443995218260647</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4403573203792</v>
+        <v>0.2882032729522528</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1851296037633309</v>
+        <v>0.4673972052216825</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>0.229667128370897</v>
+        <v>0.3099203635807474</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0.229667128370897</v>
+        <v>0.3099203635807474</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4403573203792</v>
+        <v>0.4673972052216825</v>
       </c>
       <c r="W15" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.05</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>30.825012426544</v>
+        <v>32.71780436551778</v>
       </c>
       <c r="Z15" t="n">
-        <v>30.825012426544</v>
+        <v>32.71780436551778</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -585,55 +585,55 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="H2" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6558682952734998</v>
+        <v>0.6849315068493151</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1988316516197557</v>
+        <v>0.189041095890411</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1453000531067446</v>
+        <v>0.126027397260274</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05881691408007184</v>
+        <v>0.05797101449275366</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4881284508421808</v>
+        <v>0.4761392615476333</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3187793659702348</v>
+        <v>0.3071275721315585</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1930921831875844</v>
+        <v>0.2167331663208083</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.167739844431319</v>
+        <v>-0.2087922453016819</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.167739844431319</v>
+        <v>-0.2087922453016819</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4881284508421808</v>
+        <v>0.4761392615476333</v>
       </c>
       <c r="W2" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>34.16899155895265</v>
+        <v>33.32974830833433</v>
       </c>
       <c r="Z2" t="n">
-        <v>34.16899155895265</v>
+        <v>33.32974830833433</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -673,55 +673,55 @@
         <v>1671</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="H3" t="n">
         <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>0.449677174325864</v>
+        <v>0.4295665634674923</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2552221800227877</v>
+        <v>0.2554179566563468</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2951006456513482</v>
+        <v>0.315015479876161</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05896074646074645</v>
+        <v>0.05814905814905802</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1768895942076784</v>
+        <v>0.1700536136842038</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4143362044827341</v>
+        <v>0.4010800352937268</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4087742013095875</v>
+        <v>0.4288663510220694</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1591140244599464</v>
+        <v>0.1138508711459084</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1591140244599464</v>
+        <v>0.1138508711459084</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4143362044827341</v>
+        <v>0.4288663510220694</v>
       </c>
       <c r="W3" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>29.00353431379139</v>
+        <v>30.02064457154486</v>
       </c>
       <c r="Z3" t="n">
-        <v>29.00353431379139</v>
+        <v>30.02064457154486</v>
       </c>
     </row>
     <row r="4">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -761,55 +761,55 @@
         <v>1671</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H4" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6342525399129173</v>
+        <v>0.5968169761273209</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2002902757619739</v>
+        <v>0.2122015915119363</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1654571843251089</v>
+        <v>0.1909814323607427</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05110602593440117</v>
+        <v>0.04722222222222228</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2719369575128672</v>
+        <v>0.2399392096277449</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5300255846962728</v>
+        <v>0.4835136265925929</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.19803745779086</v>
+        <v>0.2765471637796623</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3297353089342989</v>
+        <v>0.2713120350806566</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3297353089342989</v>
+        <v>0.2713120350806566</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5300255846962728</v>
+        <v>0.4835136265925929</v>
       </c>
       <c r="W4" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>37.1017909287391</v>
+        <v>33.8459538614815</v>
       </c>
       <c r="Z4" t="n">
-        <v>37.1017909287391</v>
+        <v>33.8459538614815</v>
       </c>
     </row>
     <row r="5">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -849,55 +849,55 @@
         <v>1671</v>
       </c>
       <c r="G5" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="H5" t="n">
         <v>4.33</v>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6098357297414951</v>
+        <v>0.6018171661844011</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2183014736949925</v>
+        <v>0.2182108431661685</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1718627965635123</v>
+        <v>0.1799719906494304</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05792635435785254</v>
+        <v>0.05836574785251614</v>
       </c>
       <c r="N5" t="n">
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5517293360907328</v>
+        <v>0.4957472790711372</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2942182089095676</v>
+        <v>0.2448591035222365</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1540524549996996</v>
+        <v>0.2593936174066264</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.05810639365076231</v>
+        <v>-0.1060698871132638</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.05810639365076231</v>
+        <v>-0.1060698871132638</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5517293360907328</v>
+        <v>0.4957472790711372</v>
       </c>
       <c r="W5" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>38.6210535263513</v>
+        <v>34.70230953497961</v>
       </c>
       <c r="Z5" t="n">
-        <v>38.6210535263513</v>
+        <v>34.70230953497961</v>
       </c>
     </row>
     <row r="6">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -937,55 +937,55 @@
         <v>1671</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="J6" t="n">
-        <v>0.550173120294781</v>
+        <v>0.5746381507885073</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2338235761252819</v>
+        <v>0.225750702095485</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2160033035799371</v>
+        <v>0.1996111471160078</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06918217633473711</v>
+        <v>0.05468215994531778</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2361309624244033</v>
+        <v>0.2064575634094828</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4836453918188118</v>
+        <v>0.4346844708020633</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2802236457567848</v>
+        <v>0.3588579657884538</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2498218156935299</v>
+        <v>0.2089337687065784</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2498218156935299</v>
+        <v>0.2089337687065784</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4836453918188118</v>
+        <v>0.4346844708020633</v>
       </c>
       <c r="W6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="Y6" t="n">
-        <v>33.85517742731682</v>
+        <v>30.42791295614444</v>
       </c>
       <c r="Z6" t="n">
-        <v>33.85517742731682</v>
+        <v>30.42791295614444</v>
       </c>
     </row>
     <row r="7">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45465.97916666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1025,55 +1025,55 @@
         <v>1671</v>
       </c>
       <c r="G7" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4953320415712524</v>
+        <v>0.4194683346364347</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2489695261581821</v>
+        <v>0.2550820953870211</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2556984322705654</v>
+        <v>0.3254495699765442</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05698837443119609</v>
+        <v>0.05954230092161117</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1853488118649174</v>
+        <v>0.1470755222311179</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4586399964177667</v>
+        <v>0.3804223516987789</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3560111917173159</v>
+        <v>0.4725021260701033</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2096704702595846</v>
+        <v>0.1470525560935591</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2096704702595846</v>
+        <v>0.1470525560935591</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4586399964177667</v>
+        <v>0.4725021260701033</v>
       </c>
       <c r="W7" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Y7" t="n">
-        <v>32.10479974924367</v>
+        <v>33.07514882490723</v>
       </c>
       <c r="Z7" t="n">
-        <v>32.10479974924367</v>
+        <v>33.07514882490723</v>
       </c>
     </row>
     <row r="8">
@@ -1094,7 +1094,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1201,25 +1201,25 @@
         <v>1671</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="H9" t="n">
         <v>3.5</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4125736738703341</v>
+        <v>0.3619297617627173</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2711198428290766</v>
+        <v>0.2719643638388418</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3163064833005894</v>
+        <v>0.3661058743984409</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05383022774327118</v>
+        <v>0.05055780721179959</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -1237,13 +1237,13 @@
         <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1556643986392624</v>
+        <v>0.1548198776294972</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1556643986392624</v>
+        <v>0.1548198776294972</v>
       </c>
       <c r="V9" t="n">
         <v>0.426784241468339</v>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45466.02083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1289,25 +1289,25 @@
         <v>1671</v>
       </c>
       <c r="G10" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="H10" t="n">
         <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4959022086400889</v>
+        <v>0.5180518051805181</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2255174329768023</v>
+        <v>0.2257225722572257</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2785803583831088</v>
+        <v>0.2562256225622562</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05577309457814539</v>
+        <v>0.05481359579720224</v>
       </c>
       <c r="N10" t="n">
         <v>2</v>
@@ -1325,19 +1325,19 @@
         <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2954843328419956</v>
+        <v>0.3178390686628482</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2954843328419956</v>
+        <v>0.3178390686628482</v>
       </c>
       <c r="V10" t="n">
         <v>0.5740646912251044</v>
       </c>
       <c r="W10" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1349,446 +1349,6 @@
       </c>
       <c r="Z10" t="n">
         <v>40.18452838575731</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Sx1kytXA</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45465.9375</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>colorado rapids</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>cf montreal</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>167</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="I11" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.6849315068493151</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.1800391389432485</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.1350293542074364</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.05797101449275366</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.2818478117601487</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.4166745314495733</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.3014776567902779</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.2366353925063248</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.2366353925063248</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.4166745314495733</v>
-      </c>
-      <c r="W11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y11" t="n">
-        <v>29.16721720147013</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>29.16721720147013</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2NHGKPBj</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45465.9375</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>real salt lake</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>los angeles galaxy</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>167</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="I12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.54584017471928</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.2180839497146315</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.2360758755660886</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.05898156429801493</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.2679463459069347</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.2404162183091151</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.4916374357839501</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.2555615602178616</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0.2555615602178616</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.4916374357839501</v>
-      </c>
-      <c r="W12" t="n">
-        <v>4</v>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y12" t="n">
-        <v>34.41462050487651</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>34.41462050487651</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>UT5bq9li</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>los angeles fc</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>san jose earthquakes</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>167</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H13" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="I13" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.6845564074479737</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.1642935377875137</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.1511500547645126</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.0585507246376813</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.3869700516647428</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.4439708949612933</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.1690590533739638</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.2796773571737797</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.2796773571737797</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.4439708949612933</v>
-      </c>
-      <c r="W13" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y13" t="n">
-        <v>31.07796264729053</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>31.07796264729053</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Ma0gz0nH</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>portland timbers</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>vancouver whitecaps</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>167</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.4512126339537507</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.2526790750141004</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.2961082910321489</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.05535714285714288</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.3641650161969446</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.2900694571601281</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.3457655266429275</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>-0.08704761775680608</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>-0.08704761775680608</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.3641650161969446</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y14" t="n">
-        <v>25.49155113378612</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>25.49155113378612</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>8K42rT3c</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>seattle sounders</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>fc dallas</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>167</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.6175562417291575</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.2249669166299073</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.1574768416409351</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.05835667600373484</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.2443995218260647</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.2882032729522528</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.4673972052216825</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.3099203635807474</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.3099203635807474</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.4673972052216825</v>
-      </c>
-      <c r="W15" t="n">
-        <v>6</v>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y15" t="n">
-        <v>32.71780436551778</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>32.71780436551778</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,20 +562,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -585,55 +585,55 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6849315068493151</v>
+        <v>0.7083825265643447</v>
       </c>
       <c r="K2" t="n">
-        <v>0.189041095890411</v>
+        <v>0.1570247933884298</v>
       </c>
       <c r="L2" t="n">
-        <v>0.126027397260274</v>
+        <v>0.1345926800472255</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05797101449275366</v>
+        <v>0.06140350877192979</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4761392615476333</v>
+        <v>0.3869700516647428</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3071275721315585</v>
+        <v>0.4439708949612933</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2167331663208083</v>
+        <v>0.1690590533739638</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2087922453016819</v>
+        <v>0.2869461015728636</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2087922453016819</v>
+        <v>0.2869461015728636</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4761392615476333</v>
+        <v>0.4439708949612933</v>
       </c>
       <c r="W2" t="n">
-        <v>1.38</v>
+        <v>6</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -641,29 +641,29 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>33.32974830833433</v>
+        <v>31.07796264729053</v>
       </c>
       <c r="Z2" t="n">
-        <v>33.32974830833433</v>
+        <v>31.07796264729053</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -673,55 +673,55 @@
         <v>1671</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="H3" t="n">
         <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4295665634674923</v>
+        <v>0.439632042928325</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2554179566563468</v>
+        <v>0.2554618627826753</v>
       </c>
       <c r="L3" t="n">
-        <v>0.315015479876161</v>
+        <v>0.3049060942889996</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05814905814905802</v>
+        <v>0.05796719450132803</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1700536136842038</v>
+        <v>0.3641650161969446</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4010800352937268</v>
+        <v>0.2900694571601281</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4288663510220694</v>
+        <v>0.3457655266429275</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1138508711459084</v>
+        <v>-0.07546702673138045</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1138508711459084</v>
+        <v>-0.07546702673138045</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4288663510220694</v>
+        <v>0.3641650161969446</v>
       </c>
       <c r="W3" t="n">
-        <v>3</v>
+        <v>2.15</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -729,29 +729,29 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>30.02064457154486</v>
+        <v>25.49155113378612</v>
       </c>
       <c r="Z3" t="n">
-        <v>30.02064457154486</v>
+        <v>25.49155113378612</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>8K42rT3c</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45466.10416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -761,55 +761,55 @@
         <v>1671</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5968169761273209</v>
+        <v>0.6102722850464338</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2122015915119363</v>
+        <v>0.2252195337671363</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1909814323607427</v>
+        <v>0.16450818118643</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04722222222222228</v>
+        <v>0.05716957189607941</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2399392096277449</v>
+        <v>0.2443995218260647</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4835136265925929</v>
+        <v>0.2882032729522528</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2765471637796623</v>
+        <v>0.4673972052216825</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2713120350806566</v>
+        <v>0.3028890240352525</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2713120350806566</v>
+        <v>0.3028890240352525</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4835136265925929</v>
+        <v>0.4673972052216825</v>
       </c>
       <c r="W4" t="n">
-        <v>4.5</v>
+        <v>5.75</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -817,538 +817,10 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>33.8459538614815</v>
+        <v>32.71780436551778</v>
       </c>
       <c r="Z4" t="n">
-        <v>33.8459538614815</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>ln2oxMH4</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>new york red bulls</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>toronto fc</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>167</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.6018171661844011</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.2182108431661685</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.1799719906494304</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.05836574785251614</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.4957472790711372</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.2448591035222365</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.2593936174066264</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-0.1060698871132638</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-0.1060698871132638</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.4957472790711372</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y5" t="n">
-        <v>34.70230953497961</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>34.70230953497961</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WYwYSm4A</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>orlando city</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>chicago fire</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>167</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.5746381507885073</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.225750702095485</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.1996111471160078</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.05468215994531778</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.2064575634094828</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.4346844708020633</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.3588579657884538</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.2089337687065784</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.2089337687065784</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.4346844708020633</v>
-      </c>
-      <c r="W6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y6" t="n">
-        <v>30.42791295614444</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>30.42791295614444</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>APxxS7JG</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45465.97916666666</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>philadelphia union</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>charlotte</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>167</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.4194683346364347</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.2550820953870211</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.3254495699765442</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.05954230092161117</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.1470755222311179</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.3804223516987789</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.4725021260701033</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.1470525560935591</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.1470525560935591</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.4725021260701033</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y7" t="n">
-        <v>33.07514882490723</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>33.07514882490723</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>4nxtRRYM</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45466.02083333334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>minnesota united</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>austin fc</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>167</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.54584017471928</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.2360758755660886</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.2180839497146315</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.05898156429801493</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.3723226691402557</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.1948158673714422</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.4328614634883022</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.2147775137736708</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.2147775137736708</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.4328614634883022</v>
-      </c>
-      <c r="W8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y8" t="n">
-        <v>30.30030244418116</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>30.30030244418116</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>IktpQolT</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45466.02083333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>nashville sc</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>new york city</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>167</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.3619297617627173</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2719643638388418</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.3661058743984409</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.05055780721179959</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.3328004140349778</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.426784241468339</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.2404153444966831</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.1548198776294972</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.1548198776294972</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.426784241468339</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y9" t="n">
-        <v>29.87489690278373</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>29.87489690278373</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>OWICL5dp</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45466.02083333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>st  louis city</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>atlanta utd</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>167</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.5180518051805181</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.2257225722572257</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.2562256225622562</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.05481359579720224</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.2032595674696957</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.2226757413052</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.5740646912251044</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.3178390686628482</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.3178390686628482</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.5740646912251044</v>
-      </c>
-      <c r="W10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y10" t="n">
-        <v>40.18452838575731</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>40.18452838575731</v>
+        <v>32.71780436551778</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -585,55 +585,55 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7083825265643447</v>
+        <v>0.7239382239382238</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1570247933884298</v>
+        <v>0.1505791505791506</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1345926800472255</v>
+        <v>0.1254826254826255</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06140350877192979</v>
+        <v>0.06256410256410261</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3869700516647428</v>
+        <v>0.3349990233680442</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4439708949612933</v>
+        <v>0.3841275358129648</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1690590533739638</v>
+        <v>0.280873440818991</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2869461015728636</v>
+        <v>0.2335483852338142</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2869461015728636</v>
+        <v>0.2335483852338142</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4439708949612933</v>
+        <v>0.3841275358129648</v>
       </c>
       <c r="W2" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>31.07796264729053</v>
+        <v>26.88892750690754</v>
       </c>
       <c r="Z2" t="n">
-        <v>31.07796264729053</v>
+        <v>26.88892750690754</v>
       </c>
     </row>
     <row r="3">
@@ -694,34 +694,34 @@
         <v>0.05796719450132803</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3641650161969446</v>
+        <v>0.3153639087876114</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2900694571601281</v>
+        <v>0.2454734549405155</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3457655266429275</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.07546702673138045</v>
+        <v>0.1342565419828735</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.07546702673138045</v>
+        <v>0.1342565419828735</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3641650161969446</v>
+        <v>0.4391626362718731</v>
       </c>
       <c r="W3" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>25.49155113378612</v>
+        <v>30.74138453903112</v>
       </c>
       <c r="Z3" t="n">
-        <v>25.49155113378612</v>
+        <v>30.74138453903112</v>
       </c>
     </row>
     <row r="4">
@@ -785,28 +785,28 @@
         <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2443995218260647</v>
+        <v>0.2068043869608158</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2882032729522528</v>
+        <v>0.242857704879984</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4673972052216825</v>
+        <v>0.5503379081592003</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3028890240352525</v>
+        <v>0.3858297269727703</v>
       </c>
       <c r="T4" t="n">
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3028890240352525</v>
+        <v>0.3858297269727703</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4673972052216825</v>
+        <v>0.5503379081592003</v>
       </c>
       <c r="W4" t="n">
         <v>5.75</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>32.71780436551778</v>
+        <v>38.52365357114402</v>
       </c>
       <c r="Z4" t="n">
-        <v>32.71780436551778</v>
+        <v>38.52365357114402</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -761,25 +761,25 @@
         <v>1671</v>
       </c>
       <c r="G4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
         <v>5.75</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6102722850464338</v>
+        <v>0.6038755619308649</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2252195337671363</v>
+        <v>0.2312401542027946</v>
       </c>
       <c r="L4" t="n">
-        <v>0.16450818118643</v>
+        <v>0.1648842838663405</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05716957189607941</v>
+        <v>0.05475815766188674</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
@@ -797,13 +797,13 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3858297269727703</v>
+        <v>0.3854536242928598</v>
       </c>
       <c r="T4" t="n">
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3858297269727703</v>
+        <v>0.3854536242928598</v>
       </c>
       <c r="V4" t="n">
         <v>0.5503379081592003</v>

--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,20 +562,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45471.97916666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -585,55 +585,55 @@
         <v>1671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="H2" t="n">
-        <v>6.25</v>
+        <v>3.8</v>
       </c>
       <c r="I2" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7239382239382238</v>
+        <v>0.483021608861449</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1505791505791506</v>
+        <v>0.2478663519157435</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1254826254826255</v>
+        <v>0.2691120392228073</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06256410256410261</v>
+        <v>0.06169269327164084</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3349990233680442</v>
+        <v>0.1642468697849789</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3841275358129648</v>
+        <v>0.3239081110463583</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.280873440818991</v>
+        <v>0.5118450191686629</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2335483852338142</v>
+        <v>0.2427329799458556</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2335483852338142</v>
+        <v>0.2427329799458556</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3841275358129648</v>
+        <v>0.5118450191686629</v>
       </c>
       <c r="W2" t="n">
-        <v>6.25</v>
+        <v>3.5</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -641,29 +641,29 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>26.88892750690754</v>
+        <v>35.8291513418064</v>
       </c>
       <c r="Z2" t="n">
-        <v>26.88892750690754</v>
+        <v>35.8291513418064</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -673,55 +673,55 @@
         <v>1671</v>
       </c>
       <c r="G3" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.439632042928325</v>
+        <v>0.542180339508165</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2554618627826753</v>
+        <v>0.2344929968372814</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3049060942889996</v>
+        <v>0.2233266636545537</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05796719450132803</v>
+        <v>0.06612992017616293</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3153639087876114</v>
+        <v>0.5495201590542395</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2454734549405155</v>
+        <v>0.2376684911701525</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4391626362718731</v>
+        <v>0.2128113497756081</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1342565419828735</v>
+        <v>0.007339819546074433</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1342565419828735</v>
+        <v>0.007339819546074433</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4391626362718731</v>
+        <v>0.5495201590542395</v>
       </c>
       <c r="W3" t="n">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -729,98 +729,2902 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>30.74138453903112</v>
+        <v>38.46641113379676</v>
       </c>
       <c r="Z3" t="n">
-        <v>30.74138453903112</v>
+        <v>38.46641113379676</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45466.10416666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>167</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3236831523924407</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.268194611982308</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4081222356252514</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.06532448061683449</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1112666056438713</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4673436835784407</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.4213897107776879</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1991490715961327</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.1991490715961327</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.4673436835784407</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>32.71405785049085</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>32.71405785049085</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>167</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3223762376237624</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2526732673267326</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4249504950495049</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.06964331102262133</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.2885538219241844</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.4315579098143414</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.2798882682614742</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.1788846424876088</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.1788846424876088</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.4315579098143414</v>
+      </c>
+      <c r="W5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>30.2090536870039</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>30.2090536870039</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45472.97916666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>167</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5546995377503853</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2357473035439137</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.2095531587057011</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.06045751633986929</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.2696524984710746</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.4044565330362194</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.325890968492706</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1687092294923057</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.1687092294923057</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.4044565330362194</v>
+      </c>
+      <c r="W6" t="n">
+        <v>4</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>28.31195731253536</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>28.31195731253536</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>167</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3567060741948635</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2680391357521402</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3752547900529964</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.06594242259641492</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1056844427493848</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.4070576290052907</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.4872579282453244</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.112003138192328</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.112003138192328</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.4872579282453244</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>34.10805497717271</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>34.10805497717271</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>167</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5220012055455093</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2610006027727547</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.216998191681736</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0642802155504234</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.2019387812030422</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.289818025706767</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5082431930901908</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.2912450014084549</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.2912450014084549</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.5082431930901908</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>35.57702351631336</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>35.57702351631336</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>167</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3958218801539307</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2770753161077515</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.3271028037383177</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.06150793650793651</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0761032136620981</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.3219959001578103</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.6019008861800916</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.2747980824417739</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.2747980824417739</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.6019008861800916</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>42.13306203260642</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>42.13306203260642</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45473.02083333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>167</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5228187919463088</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2476510067114094</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2295302013422819</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.06261588931678785</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.3408279566753958</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.1450477685978707</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.5141242747267334</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2845940733844515</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.2845940733844515</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.5141242747267334</v>
+      </c>
+      <c r="W10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>35.98869923087134</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>35.98869923087134</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>167</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6272727272727273</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2090909090909091</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1636363636363637</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.06280193236714959</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.4548433740951673</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.3177878431154366</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.227368782789396</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-0.17242935317756</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.17242935317756</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.4548433740951673</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>31.83903618666172</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>31.83903618666172</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>167</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4931506849315068</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.2465753424657534</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2602739726027397</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.06725146198830423</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.4638753279776394</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.359396816040525</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.1767278559818356</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0.02927535695386735</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.02927535695386735</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.4638753279776394</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>32.47127295843476</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>32.47127295843476</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>167</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.3692307692307692</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.2615384615384615</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.3692307692307692</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.06209150326797408</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.2337930636330741</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.2864780022701863</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4797289340967397</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1104981648659705</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.1104981648659705</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.4797289340967397</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>33.58102538677178</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>33.58102538677178</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>seattle sounders</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>167</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.5835764902042518</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.236348478532722</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.1800750312630263</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.05776014109347427</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.2292248832373925</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.3239337003004357</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.4468414164621718</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.2667663851991455</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.2667663851991455</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.4468414164621718</v>
+      </c>
+      <c r="W14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>31.27889915235203</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>31.27889915235203</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45473.10416666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>167</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5152153240048907</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.2548227143051216</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.2299619616899878</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.06062079672635434</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.1096026689551528</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.6508783927570068</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.2395189382878405</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.3960556784518852</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.3960556784518852</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.6508783927570068</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>45.56148749299047</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>45.56148749299047</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>167</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.2910801910715639</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.3187300557940925</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.3901897531343437</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.6098102468656563</v>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>42.68671728059594</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>42.68671728059594</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>167</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.11859282169494</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.2891652246559143</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.5922419536491457</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.4077580463508543</v>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>28.5430632445598</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>28.5430632445598</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>167</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.1300286073032101</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.2959344201278853</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.5740369725689046</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.4259630274310954</v>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>29.81741192017668</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>29.81741192017668</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>167</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.3021367112651189</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.3118254466460983</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.3860378420887828</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.6139621579112171</v>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>42.9773510537852</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>42.9773510537852</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45476.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>167</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.1137181767269389</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.347281232600631</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.5390005906724301</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.4609994093275699</v>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>32.26995865292989</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>32.26995865292989</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45476.98958333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>167</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.3377610251048948</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.2629343508692568</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.3993046240258485</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.6006953759741516</v>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>42.04867631819061</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>42.04867631819061</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>167</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.2102050138660907</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.4460485145786615</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.3437464715552478</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.5539514854213385</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>38.7766039794937</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>38.7766039794937</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>167</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.2039683792691152</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.2195417309854106</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.5764898897454743</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>0.4235101102545257</v>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>29.6457077178168</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>29.6457077178168</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45477.02083333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>167</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.165730761755151</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.3643945447399982</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.4698746935048509</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>0.530125306495149</v>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y24" t="n">
+        <v>37.10877145466043</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>37.10877145466043</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45477.0625</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>167</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.1804427270102636</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.3316364199201491</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.4879208530695873</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="n">
+        <v>0.5120791469304127</v>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>35.84554028512889</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>35.84554028512889</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45478.02083333334</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>fc dallas</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>167</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1671</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.6038755619308649</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.2312401542027946</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.1648842838663405</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.05475815766188674</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>167</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.1555948135238605</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.460780950832072</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.3836242356440675</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="n">
+        <v>0.539219049167928</v>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y26" t="n">
+        <v>37.74533344175496</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>37.74533344175496</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45478.0625</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>167</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.2464572160737567</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.4197114665611633</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.33383131736508</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="n">
+        <v>0.5802885334388367</v>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y27" t="n">
+        <v>40.62019734071857</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>40.62019734071857</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45478.10416666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>167</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.1912627821864503</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.5240250406309664</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.2847121771825833</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>0.4759749593690336</v>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y28" t="n">
+        <v>33.31824715583235</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>33.31824715583235</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>167</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
         <v>2</v>
       </c>
-      <c r="O4" t="n">
-        <v>0.2068043869608158</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.242857704879984</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.5503379081592003</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.3854536242928598</v>
-      </c>
-      <c r="T4" t="n">
+      <c r="O29" t="n">
+        <v>0.1339057857071087</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.3791454438510249</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.4869487704418664</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>0.5130512295581335</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y29" t="n">
+        <v>35.91358606906935</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>35.91358606906935</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>167</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.6970129084589971</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.1478901277561028</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.1550969637849001</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>0.3029870915410029</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y30" t="n">
+        <v>21.2090964078702</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>21.2090964078702</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>167</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="n">
         <v>2</v>
       </c>
-      <c r="U4" t="n">
-        <v>0.3854536242928598</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.5503379081592003</v>
-      </c>
-      <c r="W4" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
-        <v>38.52365357114402</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>38.52365357114402</v>
+      <c r="O31" t="n">
+        <v>0.1032657155921802</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.3638537276127817</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.5328805567950382</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>0.4671194432049618</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y31" t="n">
+        <v>32.69836102434733</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>32.69836102434733</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>167</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.2186122003093852</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.4397178547663033</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.3416699449243116</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>0.5602821452336968</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y32" t="n">
+        <v>39.21975016635878</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>39.21975016635878</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>167</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>2</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.1753271859574902</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.3795316382043792</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.4451411758381306</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>0.5548588241618694</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y33" t="n">
+        <v>38.84011769133085</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>38.84011769133085</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45480.02083333334</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>167</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.3635616090733832</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.3758222204173031</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.2606161705093137</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="n">
+        <v>0.6241777795826969</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y34" t="n">
+        <v>43.69244457078879</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>43.69244457078879</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45480.0625</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>167</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>2</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.2170576406952672</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.215256431144031</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.5676859281607018</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="n">
+        <v>0.4323140718392982</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y35" t="n">
+        <v>30.26198502875087</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>30.26198502875087</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45480.10416666666</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>167</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.1862907893755237</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.3809950351800475</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.4327141754444288</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="n">
+        <v>0.5672858245555712</v>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y36" t="n">
+        <v>39.71000771888998</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>39.71000771888998</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45481.02083333334</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>167</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>2</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.1172133659454251</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.3491915500948359</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.533595083959739</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="n">
+        <v>0.466404916040261</v>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y37" t="n">
+        <v>32.64834412281827</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>32.64834412281827</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45481.02083333334</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>167</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.2519730838065383</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.1717278774908062</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.5762990387026554</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="n">
+        <v>0.4237009612973446</v>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y38" t="n">
+        <v>29.65906729081412</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>29.65906729081412</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45481.0625</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>167</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.1053620075900685</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.584721392714579</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.3099165996953525</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>0.415278607285421</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y39" t="n">
+        <v>29.06950250997947</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>29.06950250997947</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45481.10416666666</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>167</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.4173085263408691</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.4131424591513406</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.1695490145077903</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="n">
+        <v>0.5826914736591309</v>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y40" t="n">
+        <v>40.78840315613916</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>40.78840315613916</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45481.10416666666</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>167</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>2</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.1942455617650128</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.3935222465769074</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.4122321916580799</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="n">
+        <v>0.5877678083419201</v>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y41" t="n">
+        <v>41.14374658393441</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>41.14374658393441</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45481.83333333334</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>167</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.2753350332114494</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.3677670757637634</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.3568978910247871</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="n">
+        <v>0.6322329242362366</v>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="Y42" t="n">
+        <v>44.25630469653656</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>44.25630469653656</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:AB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,100 +460,110 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>odds_home</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>odds_draw</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>odds_away</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>prob_home_bm</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>prob_draw_bm</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>prob_away_bm</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>overround</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>predicted_result</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>prob_class_1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>prob_class_0</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>prob_class_2</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>copiado_formaciones</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>result_to_bet</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>dif_prob_result_to_bet</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>prob_result_to_bet</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>odd_to_bet</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -562,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z7pPU9Zc</t>
+          <t>jqf7smJ3</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45471.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -584,86 +594,96 @@
       <c r="F2" t="n">
         <v>1671</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4.75</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I2" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6558682952734998</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1988316516197557</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1453000531067446</v>
+        <v>0.4713493530499075</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05881691408007184</v>
+        <v>0.2513863216266174</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.2772643253234751</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4881284508421808</v>
+        <v>0.0607843137254902</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3187793659702348</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1930921831875844</v>
+        <v>0.1682521216381868</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0.3300944701846407</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.167739844431319</v>
+        <v>0.5016534081771724</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.167739844431319</v>
+        <v>0.2243890828536974</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4881284508421808</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X2" t="inlineStr">
+        <v>0.2243890828536974</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.5016534081771724</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y2" t="n">
-        <v>34.16899155895265</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>34.16899155895265</v>
+      <c r="AA2" t="n">
+        <v>35.11573857240207</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>35.11573857240207</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>EcqTTTl4</t>
+          <t>G0IRHiWk</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -672,86 +692,96 @@
       <c r="F3" t="n">
         <v>1671</v>
       </c>
-      <c r="G3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3.7</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I3" t="n">
-        <v>3.2</v>
+        <v>1.73</v>
       </c>
       <c r="J3" t="n">
-        <v>0.449677174325864</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2552221800227877</v>
+        <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2951006456513482</v>
+        <v>0.542180339508165</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05896074646074645</v>
+        <v>0.2344929968372814</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.2233266636545537</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1768895942076784</v>
+        <v>0.06612992017616293</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4143362044827341</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4087742013095875</v>
+        <v>0.5600056986236961</v>
       </c>
       <c r="R3" t="n">
+        <v>0.225159641522652</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2148346598536519</v>
+      </c>
+      <c r="T3" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="n">
-        <v>0.1591140244599464</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
       <c r="U3" t="n">
-        <v>0.1591140244599464</v>
+        <v>0.01782535911553107</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4143362044827341</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X3" t="inlineStr">
+        <v>0.01782535911553107</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.5600056986236961</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y3" t="n">
-        <v>29.00353431379139</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>29.00353431379139</v>
+      <c r="AA3" t="n">
+        <v>39.20039890365872</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>39.20039890365872</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tpoLVkKi</t>
+          <t>fiHVGBod</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>new england revolution</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -760,86 +790,96 @@
       <c r="F4" t="n">
         <v>1671</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.75</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I4" t="n">
-        <v>5.75</v>
+        <v>2.9</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6342525399129173</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2002902757619739</v>
+        <v>2.3</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1654571843251089</v>
+        <v>0.3236831523924407</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05110602593440117</v>
+        <v>0.268194611982308</v>
       </c>
       <c r="N4" t="n">
+        <v>0.4081222356252514</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.06532448061683449</v>
+      </c>
+      <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="n">
-        <v>0.2719369575128672</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.5300255846962728</v>
-      </c>
       <c r="Q4" t="n">
-        <v>0.19803745779086</v>
+        <v>0.1129468828105194</v>
       </c>
       <c r="R4" t="n">
+        <v>0.4663873863083922</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.4206657308810886</v>
+      </c>
+      <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="S4" t="n">
-        <v>0.3297353089342989</v>
-      </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
+        <v>0.1981927743260842</v>
+      </c>
+      <c r="V4" t="n">
         <v>0</v>
       </c>
-      <c r="U4" t="n">
-        <v>0.3297353089342989</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.5300255846962728</v>
-      </c>
       <c r="W4" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="X4" t="inlineStr">
+        <v>0.1981927743260842</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.4663873863083922</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y4" t="n">
-        <v>37.1017909287391</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>37.1017909287391</v>
+      <c r="AA4" t="n">
+        <v>32.64711704158745</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>32.64711704158745</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ln2oxMH4</t>
+          <t>4nbBt7Y9</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>new england revolution</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -848,86 +888,96 @@
       <c r="F5" t="n">
         <v>1671</v>
       </c>
-      <c r="G5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.33</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6098357297414951</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2183014736949925</v>
+        <v>2.1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1718627965635123</v>
+        <v>0.3027681660899654</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05792635435785254</v>
+        <v>0.2502883506343714</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0.4469434832756632</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5517293360907328</v>
+        <v>0.06543778801843314</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2942182089095676</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1540524549996996</v>
+        <v>0.2861797795226119</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0.4240553306546914</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.05810639365076231</v>
+        <v>0.2897648898226965</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.05810639365076231</v>
+        <v>0.17376698002032</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5517293360907328</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X5" t="inlineStr">
+        <v>0.17376698002032</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.4240553306546914</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y5" t="n">
-        <v>38.6210535263513</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>38.6210535263513</v>
+      <c r="AA5" t="n">
+        <v>29.6838731458284</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>29.6838731458284</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WYwYSm4A</t>
+          <t>b9cFuRmG</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45472.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>dc united</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -936,86 +986,96 @@
       <c r="F6" t="n">
         <v>1671</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>1.7</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>4</v>
       </c>
-      <c r="I6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.550173120294781</v>
-      </c>
       <c r="K6" t="n">
-        <v>0.2338235761252819</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2160033035799371</v>
+        <v>0.5546995377503853</v>
       </c>
       <c r="M6" t="n">
-        <v>0.06918217633473711</v>
+        <v>0.2357473035439137</v>
       </c>
       <c r="N6" t="n">
+        <v>0.2095531587057011</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.06045751633986929</v>
+      </c>
+      <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="O6" t="n">
-        <v>0.2361309624244033</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.4836453918188118</v>
-      </c>
       <c r="Q6" t="n">
-        <v>0.2802236457567848</v>
+        <v>0.2640207443028547</v>
       </c>
       <c r="R6" t="n">
+        <v>0.4087786074831323</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.3272006482140131</v>
+      </c>
+      <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="n">
-        <v>0.2498218156935299</v>
-      </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
+        <v>0.1730313039392186</v>
+      </c>
+      <c r="V6" t="n">
         <v>0</v>
       </c>
-      <c r="U6" t="n">
-        <v>0.2498218156935299</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.4836453918188118</v>
-      </c>
       <c r="W6" t="n">
+        <v>0.1730313039392186</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.4087786074831323</v>
+      </c>
+      <c r="Y6" t="n">
         <v>4</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y6" t="n">
-        <v>33.85517742731682</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>33.85517742731682</v>
+      <c r="AA6" t="n">
+        <v>28.61450252381926</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>28.61450252381926</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>APxxS7JG</t>
+          <t>zZKrObIr</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45465.85416666666</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1024,86 +1084,96 @@
       <c r="F7" t="n">
         <v>1671</v>
       </c>
-      <c r="G7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.8</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I7" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4953320415712524</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2489695261581821</v>
+        <v>2.45</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2556984322705654</v>
+        <v>0.3480113636363636</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05698837443119609</v>
+        <v>0.2684659090909091</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.3835227272727272</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1853488118649174</v>
+        <v>0.06424792139077851</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4586399964177667</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3560111917173159</v>
+        <v>0.106432213173785</v>
       </c>
       <c r="R7" t="n">
+        <v>0.4026166806223695</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.4909511062038455</v>
+      </c>
+      <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="S7" t="n">
-        <v>0.2096704702595846</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
       <c r="U7" t="n">
-        <v>0.2096704702595846</v>
+        <v>0.1074283789311182</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4586399964177667</v>
+        <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="X7" t="inlineStr">
+        <v>0.1074283789311182</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.4909511062038455</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y7" t="n">
-        <v>32.10479974924367</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>32.10479974924367</v>
+      <c r="AA7" t="n">
+        <v>34.36657743426918</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>34.36657743426918</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4nxtRRYM</t>
+          <t>hAFmNIXl</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1112,77 +1182,87 @@
       <c r="F8" t="n">
         <v>1671</v>
       </c>
-      <c r="G8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I8" t="n">
-        <v>4.33</v>
+        <v>1.83</v>
       </c>
       <c r="J8" t="n">
-        <v>0.54584017471928</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2360758755660886</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2180839497146315</v>
+        <v>0.5143906919779547</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.2614819350887937</v>
       </c>
       <c r="N8" t="n">
+        <v>0.2241273729332517</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.06232110330470975</v>
+      </c>
+      <c r="P8" t="n">
         <v>2</v>
       </c>
-      <c r="O8" t="n">
-        <v>0.3723226691402557</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.1948158673714422</v>
-      </c>
       <c r="Q8" t="n">
-        <v>0.4328614634883022</v>
+        <v>0.2051950738923016</v>
       </c>
       <c r="R8" t="n">
+        <v>0.2807323395192119</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5140725865884865</v>
+      </c>
+      <c r="T8" t="n">
         <v>1</v>
       </c>
-      <c r="S8" t="n">
-        <v>0.2147775137736708</v>
-      </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
+        <v>0.2899452136552348</v>
+      </c>
+      <c r="V8" t="n">
         <v>2</v>
       </c>
-      <c r="U8" t="n">
-        <v>0.2147775137736708</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.4328614634883022</v>
-      </c>
       <c r="W8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X8" t="inlineStr">
+        <v>0.2899452136552348</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.5140725865884865</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y8" t="n">
-        <v>30.30030244418116</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>30.30030244418116</v>
+      <c r="AA8" t="n">
+        <v>35.98508106119406</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>35.98508106119406</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>IktpQolT</t>
+          <t>QNDeLd21</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1191,7 +1271,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1200,86 +1280,96 @@
       <c r="F9" t="n">
         <v>1671</v>
       </c>
-      <c r="G9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.5</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4125736738703341</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2711198428290766</v>
+        <v>2.88</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3163064833005894</v>
+        <v>0.3958218801539307</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05383022774327118</v>
+        <v>0.2770753161077515</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.3271028037383177</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3328004140349778</v>
+        <v>0.06150793650793651</v>
       </c>
       <c r="P9" t="n">
-        <v>0.426784241468339</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2404153444966831</v>
+        <v>0.07471301891153762</v>
       </c>
       <c r="R9" t="n">
+        <v>0.3248862903446154</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.6004006907438469</v>
+      </c>
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="S9" t="n">
-        <v>0.1556643986392624</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
       <c r="U9" t="n">
-        <v>0.1556643986392624</v>
+        <v>0.2732978870055292</v>
       </c>
       <c r="V9" t="n">
-        <v>0.426784241468339</v>
+        <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X9" t="inlineStr">
+        <v>0.2732978870055292</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.6004006907438469</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y9" t="n">
-        <v>29.87489690278373</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>29.87489690278373</v>
+      <c r="AA9" t="n">
+        <v>42.02804835206928</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>42.02804835206928</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OWICL5dp</t>
+          <t>W0EiMxme</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45465.89583333334</v>
+        <v>45472.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>st  louis city</t>
+          <t>sporting kansas city</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1288,86 +1378,96 @@
       <c r="F10" t="n">
         <v>1671</v>
       </c>
-      <c r="G10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.2</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I10" t="n">
-        <v>3.4</v>
+        <v>1.83</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4959022086400889</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2255174329768023</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2785803583831088</v>
+        <v>0.5140066820868672</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05577309457814539</v>
+        <v>0.2508352608583912</v>
       </c>
       <c r="N10" t="n">
+        <v>0.2351580570547417</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.06311475409836054</v>
+      </c>
+      <c r="P10" t="n">
         <v>2</v>
       </c>
-      <c r="O10" t="n">
-        <v>0.2032595674696957</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.2226757413052</v>
-      </c>
       <c r="Q10" t="n">
-        <v>0.5740646912251044</v>
+        <v>0.3498422993649441</v>
       </c>
       <c r="R10" t="n">
+        <v>0.1485508962089797</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.5016068044260763</v>
+      </c>
+      <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
-        <v>0.2954843328419956</v>
-      </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
+        <v>0.2664487473713346</v>
+      </c>
+      <c r="V10" t="n">
         <v>2</v>
       </c>
-      <c r="U10" t="n">
-        <v>0.2954843328419956</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.5740646912251044</v>
-      </c>
       <c r="W10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X10" t="inlineStr">
+        <v>0.2664487473713346</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.5016068044260763</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y10" t="n">
-        <v>40.18452838575731</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>40.18452838575731</v>
+      <c r="AA10" t="n">
+        <v>35.11247630982534</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>35.11247630982534</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Sx1kytXA</t>
+          <t>xbHaKGH7</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45465.9375</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>colorado rapids</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>cf montreal</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1376,86 +1476,96 @@
       <c r="F11" t="n">
         <v>1671</v>
       </c>
-      <c r="G11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H11" t="n">
-        <v>5.25</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6849315068493151</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1800391389432485</v>
+        <v>5.75</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1350293542074364</v>
+        <v>0.6272727272727273</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05797101449275366</v>
+        <v>0.2090909090909091</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.1636363636363637</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2818478117601487</v>
+        <v>0.06280193236714959</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4166745314495733</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3014776567902779</v>
+        <v>0.4422691314418863</v>
       </c>
       <c r="R11" t="n">
+        <v>0.3286453147672837</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2290855537908299</v>
+      </c>
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
-        <v>0.2366353925063248</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
-        <v>0.2366353925063248</v>
+        <v>-0.185003595830841</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4166745314495733</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="X11" t="inlineStr">
+        <v>-0.185003595830841</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.4422691314418863</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y11" t="n">
-        <v>29.16721720147013</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>29.16721720147013</v>
+      <c r="AA11" t="n">
+        <v>30.95883920093204</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>30.95883920093204</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2NHGKPBj</t>
+          <t>v3erq0f8</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45465.9375</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1464,86 +1574,96 @@
       <c r="F12" t="n">
         <v>1671</v>
       </c>
-      <c r="G12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4.33</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>1.95</v>
       </c>
       <c r="J12" t="n">
-        <v>0.54584017471928</v>
+        <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2180839497146315</v>
+        <v>3.5</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2360758755660886</v>
+        <v>0.483021608861449</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05898156429801493</v>
+        <v>0.2478663519157435</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>0.2691120392228073</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2679463459069347</v>
+        <v>0.06169269327164084</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2404162183091151</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4916374357839501</v>
+        <v>0.4555814572970544</v>
       </c>
       <c r="R12" t="n">
+        <v>0.3625125463477152</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.1819059963552304</v>
+      </c>
+      <c r="T12" t="n">
         <v>1</v>
       </c>
-      <c r="S12" t="n">
-        <v>0.2555615602178616</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
       <c r="U12" t="n">
-        <v>0.2555615602178616</v>
+        <v>-0.02744015156439461</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4916374357839501</v>
+        <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>4</v>
-      </c>
-      <c r="X12" t="inlineStr">
+        <v>-0.02744015156439461</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.4555814572970544</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y12" t="n">
-        <v>34.41462050487651</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>34.41462050487651</v>
+      <c r="AA12" t="n">
+        <v>31.89070201079381</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>31.89070201079381</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>UT5bq9li</t>
+          <t>IgfnrK9E</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1552,86 +1672,96 @@
       <c r="F13" t="n">
         <v>1671</v>
       </c>
-      <c r="G13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H13" t="n">
-        <v>5.75</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I13" t="n">
-        <v>6.25</v>
+        <v>2.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6845564074479737</v>
+        <v>3.6</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1642935377875137</v>
+        <v>2.5</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1511500547645126</v>
+        <v>0.3620273531777956</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0585507246376813</v>
+        <v>0.2614641995172969</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.3765084473049075</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3869700516647428</v>
+        <v>0.06239316239316239</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4439708949612933</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1690590533739638</v>
+        <v>0.2393503601607635</v>
       </c>
       <c r="R13" t="n">
+        <v>0.2828453383132996</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.4778043015259369</v>
+      </c>
+      <c r="T13" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
-        <v>0.2796773571737797</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
       <c r="U13" t="n">
-        <v>0.2796773571737797</v>
+        <v>0.1012958542210294</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4439708949612933</v>
+        <v>2</v>
       </c>
       <c r="W13" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="X13" t="inlineStr">
+        <v>0.1012958542210294</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.4778043015259369</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y13" t="n">
-        <v>31.07796264729053</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>31.07796264729053</v>
+      <c r="AA13" t="n">
+        <v>33.44630110681558</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>33.44630110681558</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Ma0gz0nH</t>
+          <t>nTbjsvPK</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>vancouver whitecaps</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1640,86 +1770,96 @@
       <c r="F14" t="n">
         <v>1671</v>
       </c>
-      <c r="G14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3.75</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
       </c>
       <c r="I14" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4512126339537507</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2526790750141004</v>
+        <v>5.25</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2961082910321489</v>
+        <v>0.5865921787709497</v>
       </c>
       <c r="M14" t="n">
-        <v>0.05535714285714288</v>
+        <v>0.2346368715083799</v>
       </c>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>0.1787709497206704</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3641650161969446</v>
+        <v>0.06547619047619047</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2900694571601281</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3457655266429275</v>
+        <v>0.2265084418619253</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0.3315487108690001</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.08704761775680608</v>
+        <v>0.4419428472690747</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.08704761775680608</v>
+        <v>0.2631718975484043</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3641650161969446</v>
+        <v>2</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="X14" t="inlineStr">
+        <v>0.2631718975484043</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.4419428472690747</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y14" t="n">
-        <v>25.49155113378612</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>25.49155113378612</v>
+      <c r="AA14" t="n">
+        <v>30.93599930883523</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>30.93599930883523</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>8K42rT3c</t>
+          <t>YyTMIXGq</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45465.97916666666</v>
+        <v>45472.97916666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>st  louis city</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1728,67 +1868,77 @@
       <c r="F15" t="n">
         <v>1671</v>
       </c>
-      <c r="G15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H15" t="n">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K15" t="n">
         <v>4.2</v>
       </c>
-      <c r="I15" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.6175562417291575</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.2249669166299073</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1574768416409351</v>
+        <v>0.5239520958083832</v>
       </c>
       <c r="M15" t="n">
-        <v>0.05835667600373484</v>
+        <v>0.2514970059880239</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>0.2245508982035928</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2443995218260647</v>
+        <v>0.06031746031746033</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2882032729522528</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.4673972052216825</v>
+        <v>0.1100905502923824</v>
       </c>
       <c r="R15" t="n">
+        <v>0.6480526468975325</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2418568028100851</v>
+      </c>
+      <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="S15" t="n">
-        <v>0.3099203635807474</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
       <c r="U15" t="n">
-        <v>0.3099203635807474</v>
+        <v>0.3965556409095086</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4673972052216825</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>6</v>
-      </c>
-      <c r="X15" t="inlineStr">
+        <v>0.3965556409095086</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.6480526468975325</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
-      <c r="Y15" t="n">
-        <v>32.71780436551778</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>32.71780436551778</v>
+      <c r="AA15" t="n">
+        <v>45.36368528282728</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>45.36368528282728</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB15"/>
+  <dimension ref="A1:AB46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,66 +605,66 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4713493530499075</v>
+        <v>0.5066666666666666</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2513863216266174</v>
+        <v>0.2466666666666667</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2772643253234751</v>
+        <v>0.2466666666666667</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0607843137254902</v>
+        <v>0.06685633001422464</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1682521216381868</v>
+        <v>0.1585296251078339</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3300944701846407</v>
+        <v>0.3603816340318831</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5016534081771724</v>
+        <v>0.4810887408602829</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2243890828536974</v>
+        <v>0.2344220741936162</v>
       </c>
       <c r="V2" t="n">
         <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2243890828536974</v>
+        <v>0.2344220741936162</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5016534081771724</v>
+        <v>0.4810887408602829</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>35.11573857240207</v>
+        <v>19.05443704301414</v>
       </c>
       <c r="AB2" t="n">
-        <v>35.11573857240207</v>
+        <v>19.05443704301414</v>
       </c>
     </row>
     <row r="3">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="J3" t="n">
         <v>4</v>
@@ -712,57 +712,57 @@
         <v>4.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.542180339508165</v>
+        <v>0.5393258426966292</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2344929968372814</v>
+        <v>0.2359550561797753</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2233266636545537</v>
+        <v>0.2247191011235955</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06612992017616293</v>
+        <v>0.05952380952380953</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5600056986236961</v>
+        <v>0.600582874090608</v>
       </c>
       <c r="R3" t="n">
-        <v>0.225159641522652</v>
+        <v>0.2593121032056201</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2148346598536519</v>
+        <v>0.1401050227037719</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01782535911553107</v>
+        <v>0.06125703139397876</v>
       </c>
       <c r="V3" t="n">
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01782535911553107</v>
+        <v>0.06125703139397876</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5600056986236961</v>
+        <v>0.600582874090608</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>39.20039890365872</v>
+        <v>25.0291437045304</v>
       </c>
       <c r="AB3" t="n">
-        <v>39.20039890365872</v>
+        <v>25.0291437045304</v>
       </c>
     </row>
     <row r="4">
@@ -801,66 +801,66 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="J4" t="n">
         <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3236831523924407</v>
+        <v>0.369093490164267</v>
       </c>
       <c r="M4" t="n">
-        <v>0.268194611982308</v>
+        <v>0.2689109714053944</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4081222356252514</v>
+        <v>0.3619955384303387</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06532448061683449</v>
+        <v>0.06248653307476837</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1129468828105194</v>
+        <v>0.1011077281055308</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4663873863083922</v>
+        <v>0.2294654363350203</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4206657308810886</v>
+        <v>0.6694268355594488</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1981927743260842</v>
+        <v>0.3074312971291102</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1981927743260842</v>
+        <v>0.3074312971291102</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4663873863083922</v>
+        <v>0.6694268355594488</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>32.64711704158745</v>
+        <v>28.47134177797244</v>
       </c>
       <c r="AB4" t="n">
-        <v>32.64711704158745</v>
+        <v>28.47134177797244</v>
       </c>
     </row>
     <row r="5">
@@ -899,66 +899,66 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3027681660899654</v>
+        <v>0.3129548762736535</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2502883506343714</v>
+        <v>0.2503639010189229</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4469434832756632</v>
+        <v>0.4366812227074235</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06543778801843314</v>
+        <v>0.06511627906976747</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2861797795226119</v>
+        <v>0.3174985794909022</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4240553306546914</v>
+        <v>0.2631537432633123</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2897648898226965</v>
+        <v>0.4193476772457856</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.17376698002032</v>
+        <v>-0.01733354546163796</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="W5" t="n">
-        <v>0.17376698002032</v>
+        <v>0.01733354546163796</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4240553306546914</v>
+        <v>0.5806523227542144</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.75</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>29.6838731458284</v>
+        <v>24.03261613771072</v>
       </c>
       <c r="AB5" t="n">
-        <v>29.6838731458284</v>
+        <v>24.03261613771072</v>
       </c>
     </row>
     <row r="6">
@@ -997,66 +997,66 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5546995377503853</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2357473035439137</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2095531587057011</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06045751633986929</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2640207443028547</v>
+        <v>0.5113280515068027</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4087786074831323</v>
+        <v>0.2294201897299064</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3272006482140131</v>
+        <v>0.2592517587632908</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1730313039392186</v>
+        <v>-0.1202508958616183</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1730313039392186</v>
+        <v>0.1202508958616183</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4087786074831323</v>
+        <v>0.4886719484931973</v>
       </c>
       <c r="Y6" t="n">
-        <v>4</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>28.61450252381926</v>
+        <v>19.43359742465987</v>
       </c>
       <c r="AB6" t="n">
-        <v>28.61450252381926</v>
+        <v>19.43359742465987</v>
       </c>
     </row>
     <row r="7">
@@ -1095,66 +1095,66 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K7" t="n">
         <v>2.7</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2.45</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.3480113636363636</v>
+        <v>0.375767498976668</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2684659090909091</v>
+        <v>0.2762996316004912</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3835227272727272</v>
+        <v>0.3479328694228407</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06424792139077851</v>
+        <v>0.06448801742919397</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.106432213173785</v>
+        <v>0.1461905207264745</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4026166806223695</v>
+        <v>0.2006163205883511</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4909511062038455</v>
+        <v>0.6531931586851744</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1074283789311182</v>
+        <v>0.3052602892623336</v>
       </c>
       <c r="V7" t="n">
         <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1074283789311182</v>
+        <v>0.3052602892623336</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4909511062038455</v>
+        <v>0.6531931586851744</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>34.36657743426918</v>
+        <v>27.65965793425872</v>
       </c>
       <c r="AB7" t="n">
-        <v>34.36657743426918</v>
+        <v>27.65965793425872</v>
       </c>
     </row>
     <row r="8">
@@ -1193,66 +1193,66 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="J8" t="n">
         <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5143906919779547</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2614819350887937</v>
+        <v>0.2592592592592593</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2241273729332517</v>
+        <v>0.2074074074074074</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06232110330470975</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2051950738923016</v>
+        <v>0.2770150961145689</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2807323395192119</v>
+        <v>0.3381121763154563</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5140725865884865</v>
+        <v>0.3848727275699747</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2899452136552348</v>
+        <v>0.1774653201625673</v>
       </c>
       <c r="V8" t="n">
         <v>2</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2899452136552348</v>
+        <v>0.1774653201625673</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5140725865884865</v>
+        <v>0.3848727275699747</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>35.98508106119406</v>
+        <v>14.24363637849873</v>
       </c>
       <c r="AB8" t="n">
-        <v>35.98508106119406</v>
+        <v>14.24363637849873</v>
       </c>
     </row>
     <row r="9">
@@ -1291,66 +1291,66 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3958218801539307</v>
+        <v>0.4983388704318937</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2770753161077515</v>
+        <v>0.2491694352159468</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3271028037383177</v>
+        <v>0.2524916943521595</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06150793650793651</v>
+        <v>0.05614035087719293</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.07471301891153762</v>
+        <v>0.1822897025916111</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3248862903446154</v>
+        <v>0.4115121503485941</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6004006907438469</v>
+        <v>0.4061981470597947</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2732978870055292</v>
+        <v>0.1623427151326473</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2732978870055292</v>
+        <v>0.1623427151326473</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6004006907438469</v>
+        <v>0.4115121503485941</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>42.02804835206928</v>
+        <v>15.57560751742971</v>
       </c>
       <c r="AB9" t="n">
-        <v>42.02804835206928</v>
+        <v>15.57560751742971</v>
       </c>
     </row>
     <row r="10">
@@ -1389,66 +1389,66 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5140066820868672</v>
+        <v>0.5228187919463088</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2508352608583912</v>
+        <v>0.2476510067114094</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2351580570547417</v>
+        <v>0.2295302013422819</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06311475409836054</v>
+        <v>0.06261588931678785</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3498422993649441</v>
+        <v>0.2562809039497406</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1485508962089797</v>
+        <v>0.343238534749213</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5016068044260763</v>
+        <v>0.4004805613010465</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2664487473713346</v>
+        <v>0.1709503599587646</v>
       </c>
       <c r="V10" t="n">
         <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2664487473713346</v>
+        <v>0.1709503599587646</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5016068044260763</v>
+        <v>0.4004805613010465</v>
       </c>
       <c r="Y10" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>35.11247630982534</v>
+        <v>15.02402806505232</v>
       </c>
       <c r="AB10" t="n">
-        <v>35.11247630982534</v>
+        <v>15.02402806505232</v>
       </c>
     </row>
     <row r="11">
@@ -1511,42 +1511,42 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4422691314418863</v>
+        <v>0.6842793279755205</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3286453147672837</v>
+        <v>0.2583691465609907</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2290855537908299</v>
+        <v>0.05735152546348866</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.185003595830841</v>
+        <v>0.05700660070279318</v>
       </c>
       <c r="V11" t="n">
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.185003595830841</v>
+        <v>0.05700660070279318</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4422691314418863</v>
+        <v>0.6842793279755205</v>
       </c>
       <c r="Y11" t="n">
         <v>1.5</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>30.95883920093204</v>
+        <v>29.21396639877602</v>
       </c>
       <c r="AB11" t="n">
-        <v>30.95883920093204</v>
+        <v>29.21396639877602</v>
       </c>
     </row>
     <row r="12">
@@ -1585,66 +1585,66 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
-        <v>0.483021608861449</v>
+        <v>0.5082095387021109</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2478663519157435</v>
+        <v>0.2410737555381809</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2691120392228073</v>
+        <v>0.2507167057597081</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06169269327164084</v>
+        <v>0.06361746361746357</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4555814572970544</v>
+        <v>0.6556394530658596</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3625125463477152</v>
+        <v>0.1749962637134689</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1819059963552304</v>
+        <v>0.1693642832206717</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.02744015156439461</v>
+        <v>0.1474299143637486</v>
       </c>
       <c r="V12" t="n">
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.02744015156439461</v>
+        <v>0.1474299143637486</v>
       </c>
       <c r="X12" t="n">
-        <v>0.4555814572970544</v>
+        <v>0.6556394530658596</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>31.89070201079381</v>
+        <v>27.78197265329298</v>
       </c>
       <c r="AB12" t="n">
-        <v>31.89070201079381</v>
+        <v>27.78197265329298</v>
       </c>
     </row>
     <row r="13">
@@ -1686,63 +1686,63 @@
         <v>2.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
         <v>2.5</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3620273531777956</v>
+        <v>0.3646038628301144</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2614641995172969</v>
+        <v>0.2562081198265668</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3765084473049075</v>
+        <v>0.379188017343319</v>
       </c>
       <c r="O13" t="n">
-        <v>0.06239316239316239</v>
+        <v>0.05488565488565467</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2393503601607635</v>
+        <v>0.2392310608947727</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2828453383132996</v>
+        <v>0.3227469299461854</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4778043015259369</v>
+        <v>0.4380220091590419</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1012958542210294</v>
+        <v>0.05883399181572296</v>
       </c>
       <c r="V13" t="n">
         <v>2</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1012958542210294</v>
+        <v>0.05883399181572296</v>
       </c>
       <c r="X13" t="n">
-        <v>0.4778043015259369</v>
+        <v>0.4380220091590419</v>
       </c>
       <c r="Y13" t="n">
         <v>2.5</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>33.44630110681558</v>
+        <v>16.9011004579521</v>
       </c>
       <c r="AB13" t="n">
-        <v>33.44630110681558</v>
+        <v>16.9011004579521</v>
       </c>
     </row>
     <row r="14">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="J14" t="n">
         <v>4</v>
@@ -1790,57 +1790,57 @@
         <v>5.25</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5865921787709497</v>
+        <v>0.5835764902042518</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2346368715083799</v>
+        <v>0.236348478532722</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1787709497206704</v>
+        <v>0.1800750312630263</v>
       </c>
       <c r="O14" t="n">
-        <v>0.06547619047619047</v>
+        <v>0.05776014109347427</v>
       </c>
       <c r="P14" t="n">
         <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2265084418619253</v>
+        <v>0.1104422495607779</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3315487108690001</v>
+        <v>0.3755765015243285</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4419428472690747</v>
+        <v>0.5139812489148935</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2631718975484043</v>
+        <v>0.3339062176518672</v>
       </c>
       <c r="V14" t="n">
         <v>2</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2631718975484043</v>
+        <v>0.3339062176518672</v>
       </c>
       <c r="X14" t="n">
-        <v>0.4419428472690747</v>
+        <v>0.5139812489148935</v>
       </c>
       <c r="Y14" t="n">
         <v>5.25</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>30.93599930883523</v>
+        <v>20.69906244574468</v>
       </c>
       <c r="AB14" t="n">
-        <v>30.93599930883523</v>
+        <v>20.69906244574468</v>
       </c>
     </row>
     <row r="15">
@@ -1882,64 +1882,2700 @@
         <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K15" t="n">
         <v>4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5239520958083832</v>
+        <v>0.5221774193548387</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2514970059880239</v>
+        <v>0.2540322580645161</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2245508982035928</v>
+        <v>0.2237903225806452</v>
       </c>
       <c r="O15" t="n">
-        <v>0.06031746031746033</v>
+        <v>0.06392106392106389</v>
       </c>
       <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3511615882647987</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.2676215560887525</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.3812168556464487</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.1574265330658036</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.1574265330658036</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.3812168556464487</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA15" t="n">
+        <v>14.06084278232244</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>14.06084278232244</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45476.8125</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>167</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.5636978579481398</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2536640360766629</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.1826381059751973</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.09506172839506166</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2986195152733523</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2383247333879759</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4630557513386717</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.2804176453634744</v>
+      </c>
+      <c r="V16" t="n">
+        <v>2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.2804176453634744</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.4630557513386717</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA16" t="n">
+        <v>18.15278756693358</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>18.15278756693358</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>charlotte</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>167</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.4343286698684485</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2806431405303822</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2850281896011694</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.09638278388278376</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1836536507829496</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3266724605478561</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.4896738886691943</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.2046456990680249</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.2046456990680249</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.4896738886691943</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA17" t="n">
+        <v>19.48369443345971</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>19.48369443345971</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>167</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.3521126760563379</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2816901408450704</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3661971830985915</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.09230769230769242</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1553928911572484</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3170210187805046</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.527586090062247</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.1613889069636555</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.1613889069636555</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.527586090062247</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>21.37930450311235</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>21.37930450311235</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>167</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.5811960717106538</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2433274220228604</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.1754765062664858</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.09591703413359465</v>
+      </c>
+      <c r="P19" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0.1100905502923824</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.6480526468975325</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.2418568028100851</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.3965556409095086</v>
-      </c>
-      <c r="V15" t="n">
+      <c r="Q19" t="n">
+        <v>0.303257120057161</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.4890266717119621</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.2077162082308768</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.2456992496891018</v>
+      </c>
+      <c r="V19" t="n">
         <v>0</v>
       </c>
-      <c r="W15" t="n">
-        <v>0.3965556409095086</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.6480526468975325</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="W19" t="n">
+        <v>0.2456992496891018</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.4890266717119621</v>
+      </c>
+      <c r="Y19" t="n">
         <v>3.75</v>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA15" t="n">
-        <v>45.36368528282728</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>45.36368528282728</v>
-      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>19.45133358559811</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>19.45133358559811</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45476.85416666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>167</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.4051585169263837</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2804943578721118</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.3143471252015046</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.0969643383436487</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.09331688082328962</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.2367728396021617</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.6699102795745489</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.3555631543730443</v>
+      </c>
+      <c r="V20" t="n">
+        <v>2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.3555631543730443</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.6699102795745489</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
+        <v>28.49551397872744</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>28.49551397872744</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45476.86458333334</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>167</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.4051585169263837</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2804943578721118</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.3143471252015046</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0969643383436487</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.3927384873205019</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.2829980502106852</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.3242634624688129</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.01242002960588179</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.01242002960588179</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.6072615126794981</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.532520325203252</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA21" t="n">
+        <v>25.3630756339749</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>25.3630756339749</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>167</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.4051585169263837</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.2804943578721118</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.3143471252015046</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.0969643383436487</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.332706312209954</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.2913184969117958</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.3759751908782502</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.06162806567674561</v>
+      </c>
+      <c r="V22" t="n">
+        <v>2</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.06162806567674561</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.3759751908782502</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>13.79875954391251</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>13.79875954391251</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>167</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.4051585169263837</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.2804943578721118</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.3143471252015046</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.0969643383436487</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.2399367110755938</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.4607248436047824</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.2993384453196239</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.1802304857326706</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.1802304857326706</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.4607248436047824</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>18.03624218023912</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>18.03624218023912</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45476.89583333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>167</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.5639990501068629</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.2436475896461648</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.1923533602469722</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.09447693307342431</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.3015832438805195</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.3189591270404248</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.3794576290790557</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.1871042688320835</v>
+      </c>
+      <c r="V24" t="n">
+        <v>2</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.1871042688320835</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.3794576290790557</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>13.97288145395278</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>13.97288145395278</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45476.9375</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>167</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.5280322219860701</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.2609987840102575</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.2109689940036723</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.09469585001230074</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.3384884511422985</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.3447227435307231</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.3167888053269785</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.08372395952046557</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.08372395952046557</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.3447227435307231</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA25" t="n">
+        <v>12.23613717653615</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>12.23613717653615</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45477.89583333334</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>167</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.3803786574870912</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.2685025817555938</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.3511187607573149</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.09539969834087492</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.1165722926010396</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.2643952151519466</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.6190324922470138</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.2679137314896989</v>
+      </c>
+      <c r="V26" t="n">
+        <v>2</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.2679137314896989</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.6190324922470138</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA26" t="n">
+        <v>25.95162461235069</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>25.95162461235069</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45477.9375</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>167</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.5636978579481398</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.2536640360766629</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.1826381059751973</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.09506172839506166</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.3553081675807302</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.3166251980902031</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.3280666343290666</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.2083896903674095</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.2083896903674095</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.6446918324192698</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.093023255813954</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA27" t="n">
+        <v>27.23459162096349</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>27.23459162096349</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45477.97916666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>167</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.3803786574870912</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.2685025817555938</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.3511187607573149</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.09539969834087492</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.1577702476860585</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.3783477455351054</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.4638820067788361</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.1127632460215212</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.1127632460215212</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.4638820067788361</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA28" t="n">
+        <v>18.19410033894181</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>18.19410033894181</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>cf montreal</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>vancouver whitecaps</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>167</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.2198767360298228</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.3762799186433601</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.4038433453268171</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="n">
+        <v>0.5961566546731829</v>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA29" t="n">
+        <v>24.80783273365915</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>24.80783273365915</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>columbus crew</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>toronto fc</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>167</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.6517450933228697</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.2462058230352516</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.1020490836418788</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="n">
+        <v>0.3482549066771303</v>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA30" t="n">
+        <v>12.41274533385652</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>12.41274533385652</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>fc cincinnati</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>inter miami</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>167</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.2340252767550797</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.4533277151477706</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.3126470080971495</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="n">
+        <v>0.5466722848522294</v>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA31" t="n">
+        <v>22.33361424261147</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>22.33361424261147</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>orlando city</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>dc united</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>167</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.4879230264703818</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.2880531314804122</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.224023842049206</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="n">
+        <v>0.5120769735296182</v>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA32" t="n">
+        <v>20.60384867648091</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>20.60384867648091</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45479.85416666666</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>philadelphia union</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>new york red bulls</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>167</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.3248000313835386</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.4291690095653991</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.2460309590510623</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="n">
+        <v>0.5708309904346009</v>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA33" t="n">
+        <v>23.54154952173005</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>23.54154952173005</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45479.89583333334</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>austin fc</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>new york city</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>167</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.2992059919222956</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.2498873569671831</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.4509066511105214</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="n">
+        <v>0.5490933488894787</v>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA34" t="n">
+        <v>22.45466744447393</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>22.45466744447393</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45479.9375</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>real salt lake</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>167</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.3212718705413699</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.390346703945361</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0.2883814255132691</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="n">
+        <v>0.609653296054639</v>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA35" t="n">
+        <v>25.48266480273195</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>25.48266480273195</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45479.97916666666</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>new england revolution</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>167</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.225668000183265</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.4145494309309021</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.3597825688858328</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="n">
+        <v>0.5854505690690979</v>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA36" t="n">
+        <v>24.27252845345489</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>24.27252845345489</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>AoWGqXpJ</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45480.89583333334</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>houston dynamo</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>167</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.1112410798441106</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.266165823801843</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.6225930963540462</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="n">
+        <v>0.3774069036459538</v>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA37" t="n">
+        <v>13.87034518229769</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>13.87034518229769</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45480.89583333334</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>san jose earthquakes</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>chicago fire</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>167</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.2392316636670534</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.3479242645368</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.4128440717961466</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="n">
+        <v>0.5871559282038534</v>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA38" t="n">
+        <v>24.35779641019267</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>24.35779641019267</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45480.89583333334</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>167</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.2027394013853659</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.3507673632106973</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.4464932354039368</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="n">
+        <v>0.5535067645960632</v>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA39" t="n">
+        <v>22.67533822980316</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>22.67533822980316</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45480.9375</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>colorado rapids</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>st  louis city</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>167</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.1832356348957332</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.2403955547468579</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.5763688103574088</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="n">
+        <v>0.4236311896425912</v>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA40" t="n">
+        <v>16.18155948212956</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>16.18155948212956</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45480.97916666666</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>los angeles galaxy</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>minnesota united</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>167</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.4443843597147053</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.3332789578993695</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.2223366823859252</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="n">
+        <v>0.5556156402852948</v>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA41" t="n">
+        <v>22.78078201426474</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>22.78078201426474</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45480.97916666666</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>portland timbers</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>nashville sc</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>167</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1671</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.3771408747564578</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.2843206683708714</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.3385384568726707</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="n">
+        <v>0.6228591252435423</v>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA42" t="n">
+        <v>26.14295626217711</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>26.14295626217711</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>SKZvN7pn</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>45482.83333333334</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>atlanta utd</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>indy eleven</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>167</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1672</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>APpAklQ6</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45483</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>sacramento republic</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>seattle sounders</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>167</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1672</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>d0ReJPqB</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>45483.91666666666</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>fc dallas</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>167</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1672</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.1866426214177104</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.333167626535192</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.4801897520470976</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="n">
+        <v>0.5198102479529023</v>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA45" t="n">
+        <v>20.99051239764512</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>20.99051239764512</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>0YXnLoFb</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45484</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>los angeles fc</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>new mexico</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>167</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1672</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>us open cup</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="n">
+        <v>-100</v>
+      </c>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -605,55 +605,55 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5066666666666666</v>
+        <v>0.510925955038516</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2466666666666667</v>
+        <v>0.2397421789026883</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2466666666666667</v>
+        <v>0.2493318660587958</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06685633001422464</v>
+        <v>0.06952501050861692</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1585296251078339</v>
+        <v>0.1600414027325715</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3603816340318831</v>
+        <v>0.3548428194046342</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4810887408602829</v>
+        <v>0.4851157778627943</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2344220741936162</v>
+        <v>0.2357839118039984</v>
       </c>
       <c r="V2" t="n">
         <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2344220741936162</v>
+        <v>0.2357839118039984</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4810887408602829</v>
+        <v>0.4851157778627943</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>19.05443704301414</v>
+        <v>2.425578889313971</v>
       </c>
       <c r="AB2" t="n">
-        <v>19.05443704301414</v>
+        <v>2.425578889313971</v>
       </c>
     </row>
     <row r="3">
@@ -727,28 +727,28 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.600582874090608</v>
+        <v>0.6135764462322538</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2593121032056201</v>
+        <v>0.2825583427564414</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1401050227037719</v>
+        <v>0.1038652110113047</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06125703139397876</v>
+        <v>0.07425060353562463</v>
       </c>
       <c r="V3" t="n">
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.06125703139397876</v>
+        <v>0.07425060353562463</v>
       </c>
       <c r="X3" t="n">
-        <v>0.600582874090608</v>
+        <v>0.6135764462322538</v>
       </c>
       <c r="Y3" t="n">
         <v>1.75</v>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>25.0291437045304</v>
+        <v>3.067882231161269</v>
       </c>
       <c r="AB3" t="n">
-        <v>25.0291437045304</v>
+        <v>3.067882231161269</v>
       </c>
     </row>
     <row r="4">
@@ -825,28 +825,28 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1011077281055308</v>
+        <v>0.0706619627663416</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2294654363350203</v>
+        <v>0.2511722045198468</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6694268355594488</v>
+        <v>0.6781658327138117</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3074312971291102</v>
+        <v>0.316170294283473</v>
       </c>
       <c r="V4" t="n">
         <v>2</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3074312971291102</v>
+        <v>0.316170294283473</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6694268355594488</v>
+        <v>0.6781658327138117</v>
       </c>
       <c r="Y4" t="n">
         <v>2.6</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>28.47134177797244</v>
+        <v>3.390829163569058</v>
       </c>
       <c r="AB4" t="n">
-        <v>28.47134177797244</v>
+        <v>3.390829163569058</v>
       </c>
     </row>
     <row r="5">
@@ -920,45 +920,45 @@
         <v>0.06511627906976747</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3174985794909022</v>
+        <v>0.1964722326397506</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2631537432633123</v>
+        <v>0.4125912331172771</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4193476772457856</v>
+        <v>0.3909365342429724</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.01733354546163796</v>
+        <v>0.1622273320983542</v>
       </c>
       <c r="V5" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01733354546163796</v>
+        <v>0.1622273320983542</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5806523227542144</v>
+        <v>0.4125912331172771</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.666666666666667</v>
+        <v>3.75</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>24.03261613771072</v>
+        <v>2.062956165586385</v>
       </c>
       <c r="AB5" t="n">
-        <v>24.03261613771072</v>
+        <v>2.062956165586385</v>
       </c>
     </row>
     <row r="6">
@@ -1021,28 +1021,28 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5113280515068027</v>
+        <v>0.4489400143010975</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2294201897299064</v>
+        <v>0.3040135939367658</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2592517587632908</v>
+        <v>0.2470463917621368</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1202508958616183</v>
+        <v>-0.1826389330673235</v>
       </c>
       <c r="V6" t="n">
         <v>-1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1202508958616183</v>
+        <v>0.1826389330673235</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4886719484931973</v>
+        <v>0.5510599856989025</v>
       </c>
       <c r="Y6" t="n">
         <v>2.571428571428571</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>19.43359742465987</v>
+        <v>2.755299928494512</v>
       </c>
       <c r="AB6" t="n">
-        <v>19.43359742465987</v>
+        <v>2.755299928494512</v>
       </c>
     </row>
     <row r="7">
@@ -1095,55 +1095,55 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="L7" t="n">
-        <v>0.375767498976668</v>
+        <v>0.3619955384303387</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2762996316004912</v>
+        <v>0.2689109714053944</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3479328694228407</v>
+        <v>0.369093490164267</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06448801742919397</v>
+        <v>0.06248653307476837</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1461905207264745</v>
+        <v>0.1285853626482153</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2006163205883511</v>
+        <v>0.2521890736131565</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6531931586851744</v>
+        <v>0.6192255637386282</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3052602892623336</v>
+        <v>0.2501320735743613</v>
       </c>
       <c r="V7" t="n">
         <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3052602892623336</v>
+        <v>0.2501320735743613</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6531931586851744</v>
+        <v>0.6192255637386282</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>27.65965793425872</v>
+        <v>3.096127818693141</v>
       </c>
       <c r="AB7" t="n">
-        <v>27.65965793425872</v>
+        <v>3.096127818693141</v>
       </c>
     </row>
     <row r="8">
@@ -1217,28 +1217,28 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2770150961145689</v>
+        <v>0.2868517150384613</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3381121763154563</v>
+        <v>0.3390256513186948</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3848727275699747</v>
+        <v>0.3741226336428439</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1774653201625673</v>
+        <v>0.1667152262354365</v>
       </c>
       <c r="V8" t="n">
         <v>2</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1774653201625673</v>
+        <v>0.1667152262354365</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3848727275699747</v>
+        <v>0.3741226336428439</v>
       </c>
       <c r="Y8" t="n">
         <v>4.5</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>14.24363637849873</v>
+        <v>1.870613168214219</v>
       </c>
       <c r="AB8" t="n">
-        <v>14.24363637849873</v>
+        <v>1.870613168214219</v>
       </c>
     </row>
     <row r="9">
@@ -1291,55 +1291,55 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="J9" t="n">
         <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4983388704318937</v>
+        <v>0.4953320415712524</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2491694352159468</v>
+        <v>0.2489695261581821</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2524916943521595</v>
+        <v>0.2556984322705654</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05614035087719293</v>
+        <v>0.05698837443119609</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1822897025916111</v>
+        <v>0.07899396123747764</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4115121503485941</v>
+        <v>0.2628148092904548</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4061981470597947</v>
+        <v>0.6581912294720677</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1623427151326473</v>
+        <v>0.4024927972015022</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1623427151326473</v>
+        <v>0.4024927972015022</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4115121503485941</v>
+        <v>0.6581912294720677</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>15.57560751742971</v>
+        <v>3.290956147360338</v>
       </c>
       <c r="AB9" t="n">
-        <v>15.57560751742971</v>
+        <v>3.290956147360338</v>
       </c>
     </row>
     <row r="10">
@@ -1395,49 +1395,49 @@
         <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5228187919463088</v>
+        <v>0.5256916996047432</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2476510067114094</v>
+        <v>0.2490118577075099</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2295302013422819</v>
+        <v>0.225296442687747</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06261588931678785</v>
+        <v>0.05680868838763575</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2562809039497406</v>
+        <v>0.2519603951479352</v>
       </c>
       <c r="R10" t="n">
-        <v>0.343238534749213</v>
+        <v>0.3332635017594314</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4004805613010465</v>
+        <v>0.4147761030926335</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1709503599587646</v>
+        <v>0.1894796604048865</v>
       </c>
       <c r="V10" t="n">
         <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1709503599587646</v>
+        <v>0.1894796604048865</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4004805613010465</v>
+        <v>0.4147761030926335</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>15.02402806505232</v>
+        <v>2.073880515463168</v>
       </c>
       <c r="AB10" t="n">
-        <v>15.02402806505232</v>
+        <v>2.073880515463168</v>
       </c>
     </row>
     <row r="11">
@@ -1511,28 +1511,28 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.6842793279755205</v>
+        <v>0.650131948091704</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2583691465609907</v>
+        <v>0.2779189034356739</v>
       </c>
       <c r="S11" t="n">
-        <v>0.05735152546348866</v>
+        <v>0.07194914847262197</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.05700660070279318</v>
+        <v>0.02285922081897673</v>
       </c>
       <c r="V11" t="n">
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.05700660070279318</v>
+        <v>0.02285922081897673</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6842793279755205</v>
+        <v>0.650131948091704</v>
       </c>
       <c r="Y11" t="n">
         <v>1.5</v>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>29.21396639877602</v>
+        <v>3.25065974045852</v>
       </c>
       <c r="AB11" t="n">
-        <v>29.21396639877602</v>
+        <v>3.25065974045852</v>
       </c>
     </row>
     <row r="12">
@@ -1609,28 +1609,28 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6556394530658596</v>
+        <v>0.688836885905344</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1749962637134689</v>
+        <v>0.1566867042163429</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1693642832206717</v>
+        <v>0.1544764098783133</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1474299143637486</v>
+        <v>0.180627347203233</v>
       </c>
       <c r="V12" t="n">
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1474299143637486</v>
+        <v>0.180627347203233</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6556394530658596</v>
+        <v>0.688836885905344</v>
       </c>
       <c r="Y12" t="n">
         <v>1.85</v>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>27.78197265329298</v>
+        <v>3.44418442952672</v>
       </c>
       <c r="AB12" t="n">
-        <v>27.78197265329298</v>
+        <v>3.44418442952672</v>
       </c>
     </row>
     <row r="13">
@@ -1707,28 +1707,28 @@
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2392310608947727</v>
+        <v>0.2111363599934632</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3227469299461854</v>
+        <v>0.2528128853098374</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4380220091590419</v>
+        <v>0.5360507546966995</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.05883399181572296</v>
+        <v>0.1568627373533805</v>
       </c>
       <c r="V13" t="n">
         <v>2</v>
       </c>
       <c r="W13" t="n">
-        <v>0.05883399181572296</v>
+        <v>0.1568627373533805</v>
       </c>
       <c r="X13" t="n">
-        <v>0.4380220091590419</v>
+        <v>0.5360507546966995</v>
       </c>
       <c r="Y13" t="n">
         <v>2.5</v>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>16.9011004579521</v>
+        <v>2.680253773483497</v>
       </c>
       <c r="AB13" t="n">
-        <v>16.9011004579521</v>
+        <v>2.680253773483497</v>
       </c>
     </row>
     <row r="14">
@@ -1805,28 +1805,28 @@
         <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1104422495607779</v>
+        <v>0.1101391702825879</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3755765015243285</v>
+        <v>0.3923018476563575</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5139812489148935</v>
+        <v>0.4975589820610545</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3339062176518672</v>
+        <v>0.3174839507980283</v>
       </c>
       <c r="V14" t="n">
         <v>2</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3339062176518672</v>
+        <v>0.3174839507980283</v>
       </c>
       <c r="X14" t="n">
-        <v>0.5139812489148935</v>
+        <v>0.4975589820610545</v>
       </c>
       <c r="Y14" t="n">
         <v>5.25</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>20.69906244574468</v>
+        <v>2.487794910305273</v>
       </c>
       <c r="AB14" t="n">
-        <v>20.69906244574468</v>
+        <v>2.487794910305273</v>
       </c>
     </row>
     <row r="15">
@@ -1903,28 +1903,28 @@
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.3511615882647987</v>
+        <v>0.3419055891466642</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2676215560887525</v>
+        <v>0.2647645273290432</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3812168556464487</v>
+        <v>0.3933298835242927</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1574265330658036</v>
+        <v>0.1695395609436476</v>
       </c>
       <c r="V15" t="n">
         <v>2</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1574265330658036</v>
+        <v>0.1695395609436476</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3812168556464487</v>
+        <v>0.3933298835242927</v>
       </c>
       <c r="Y15" t="n">
         <v>4.2</v>
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>14.06084278232244</v>
+        <v>1.966649417621464</v>
       </c>
       <c r="AB15" t="n">
-        <v>14.06084278232244</v>
+        <v>1.966649417621464</v>
       </c>
     </row>
     <row r="16">
@@ -2001,28 +2001,28 @@
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.2986195152733523</v>
+        <v>0.2968325553819417</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2383247333879759</v>
+        <v>0.2265005769057136</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4630557513386717</v>
+        <v>0.4766668677123448</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2804176453634744</v>
+        <v>0.2940287617371475</v>
       </c>
       <c r="V16" t="n">
         <v>2</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2804176453634744</v>
+        <v>0.2940287617371475</v>
       </c>
       <c r="X16" t="n">
-        <v>0.4630557513386717</v>
+        <v>0.4766668677123448</v>
       </c>
       <c r="Y16" t="n">
         <v>5</v>
@@ -2033,10 +2033,10 @@
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>18.15278756693358</v>
+        <v>2.383334338561724</v>
       </c>
       <c r="AB16" t="n">
-        <v>18.15278756693358</v>
+        <v>2.383334338561724</v>
       </c>
     </row>
     <row r="17">
@@ -2099,28 +2099,28 @@
         <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1836536507829496</v>
+        <v>0.1839455355924454</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3266724605478561</v>
+        <v>0.3280930314040816</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4896738886691943</v>
+        <v>0.4879614330034731</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2046456990680249</v>
+        <v>0.2029332434023037</v>
       </c>
       <c r="V17" t="n">
         <v>2</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2046456990680249</v>
+        <v>0.2029332434023037</v>
       </c>
       <c r="X17" t="n">
-        <v>0.4896738886691943</v>
+        <v>0.4879614330034731</v>
       </c>
       <c r="Y17" t="n">
         <v>3.2</v>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="AA17" t="n">
-        <v>19.48369443345971</v>
+        <v>2.439807165017365</v>
       </c>
       <c r="AB17" t="n">
-        <v>19.48369443345971</v>
+        <v>2.439807165017365</v>
       </c>
     </row>
     <row r="18">
@@ -2197,28 +2197,28 @@
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.1553928911572484</v>
+        <v>0.1546325039321441</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3170210187805046</v>
+        <v>0.3258389601561393</v>
       </c>
       <c r="S18" t="n">
-        <v>0.527586090062247</v>
+        <v>0.5195285359117165</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1613889069636555</v>
+        <v>0.153331352813125</v>
       </c>
       <c r="V18" t="n">
         <v>2</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1613889069636555</v>
+        <v>0.153331352813125</v>
       </c>
       <c r="X18" t="n">
-        <v>0.527586090062247</v>
+        <v>0.5195285359117165</v>
       </c>
       <c r="Y18" t="n">
         <v>2.5</v>
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>21.37930450311235</v>
+        <v>2.597642679558583</v>
       </c>
       <c r="AB18" t="n">
-        <v>21.37930450311235</v>
+        <v>2.597642679558583</v>
       </c>
     </row>
     <row r="19">
@@ -2271,55 +2271,55 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5811960717106538</v>
+        <v>0.6359043646830759</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2433274220228604</v>
+        <v>0.211478587792986</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1754765062664858</v>
+        <v>0.1526170475239382</v>
       </c>
       <c r="O19" t="n">
-        <v>0.09591703413359465</v>
+        <v>0.09205799332820108</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.303257120057161</v>
+        <v>0.2962823561221066</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4890266717119621</v>
+        <v>0.4856871051415895</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2077162082308768</v>
+        <v>0.2180305387363038</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2456992496891018</v>
+        <v>0.2742085173486035</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2456992496891018</v>
+        <v>0.2742085173486035</v>
       </c>
       <c r="X19" t="n">
-        <v>0.4890266717119621</v>
+        <v>0.4856871051415895</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>19.45133358559811</v>
+        <v>2.428435525707947</v>
       </c>
       <c r="AB19" t="n">
-        <v>19.45133358559811</v>
+        <v>2.428435525707947</v>
       </c>
     </row>
     <row r="20">
@@ -2393,28 +2393,28 @@
         <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.09331688082328962</v>
+        <v>0.09582627098066902</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2367728396021617</v>
+        <v>0.2336393823796127</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6699102795745489</v>
+        <v>0.6705343466397182</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3555631543730443</v>
+        <v>0.3561872214382136</v>
       </c>
       <c r="V20" t="n">
         <v>2</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3555631543730443</v>
+        <v>0.3561872214382136</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6699102795745489</v>
+        <v>0.6705343466397182</v>
       </c>
       <c r="Y20" t="n">
         <v>2.9</v>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="AA20" t="n">
-        <v>28.49551397872744</v>
+        <v>3.352671733198591</v>
       </c>
       <c r="AB20" t="n">
-        <v>28.49551397872744</v>
+        <v>3.352671733198591</v>
       </c>
     </row>
     <row r="21">
@@ -2491,28 +2491,28 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.3927384873205019</v>
+        <v>0.4043701639172806</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2829980502106852</v>
+        <v>0.2780547405980152</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3242634624688129</v>
+        <v>0.3175750954847041</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.01242002960588179</v>
+        <v>-0.0007883530091030155</v>
       </c>
       <c r="V21" t="n">
         <v>-1</v>
       </c>
       <c r="W21" t="n">
-        <v>0.01242002960588179</v>
+        <v>0.0007883530091030155</v>
       </c>
       <c r="X21" t="n">
-        <v>0.6072615126794981</v>
+        <v>0.5956298360827194</v>
       </c>
       <c r="Y21" t="n">
         <v>1.532520325203252</v>
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="AA21" t="n">
-        <v>25.3630756339749</v>
+        <v>2.978149180413597</v>
       </c>
       <c r="AB21" t="n">
-        <v>25.3630756339749</v>
+        <v>2.978149180413597</v>
       </c>
     </row>
     <row r="22">
@@ -2589,28 +2589,28 @@
         <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.332706312209954</v>
+        <v>0.3439326658646624</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2913184969117958</v>
+        <v>0.2927412809917307</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3759751908782502</v>
+        <v>0.3633260531436069</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0.06162806567674561</v>
+        <v>0.04897892794210235</v>
       </c>
       <c r="V22" t="n">
         <v>2</v>
       </c>
       <c r="W22" t="n">
-        <v>0.06162806567674561</v>
+        <v>0.04897892794210235</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3759751908782502</v>
+        <v>0.3633260531436069</v>
       </c>
       <c r="Y22" t="n">
         <v>2.9</v>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="AA22" t="n">
-        <v>13.79875954391251</v>
+        <v>1.816630265718035</v>
       </c>
       <c r="AB22" t="n">
-        <v>13.79875954391251</v>
+        <v>1.816630265718035</v>
       </c>
     </row>
     <row r="23">
@@ -2687,28 +2687,28 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2399367110755938</v>
+        <v>0.2448931430703108</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4607248436047824</v>
+        <v>0.4556050920427626</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2993384453196239</v>
+        <v>0.2995017648869266</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1802304857326706</v>
+        <v>0.1751107341706508</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1802304857326706</v>
+        <v>0.1751107341706508</v>
       </c>
       <c r="X23" t="n">
-        <v>0.4607248436047824</v>
+        <v>0.4556050920427626</v>
       </c>
       <c r="Y23" t="n">
         <v>3.25</v>
@@ -2719,10 +2719,10 @@
         </is>
       </c>
       <c r="AA23" t="n">
-        <v>18.03624218023912</v>
+        <v>2.278025460213813</v>
       </c>
       <c r="AB23" t="n">
-        <v>18.03624218023912</v>
+        <v>2.278025460213813</v>
       </c>
     </row>
     <row r="24">
@@ -2785,28 +2785,28 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.3015832438805195</v>
+        <v>0.2985644244914996</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3189591270404248</v>
+        <v>0.3169153134554451</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3794576290790557</v>
+        <v>0.3845202620530553</v>
       </c>
       <c r="T24" t="n">
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1871042688320835</v>
+        <v>0.1921669018060831</v>
       </c>
       <c r="V24" t="n">
         <v>2</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1871042688320835</v>
+        <v>0.1921669018060831</v>
       </c>
       <c r="X24" t="n">
-        <v>0.3794576290790557</v>
+        <v>0.3845202620530553</v>
       </c>
       <c r="Y24" t="n">
         <v>4.75</v>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="AA24" t="n">
-        <v>13.97288145395278</v>
+        <v>1.922601310265276</v>
       </c>
       <c r="AB24" t="n">
-        <v>13.97288145395278</v>
+        <v>1.922601310265276</v>
       </c>
     </row>
     <row r="25">
@@ -2880,45 +2880,45 @@
         <v>0.09469585001230074</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.3384884511422985</v>
+        <v>0.3422502016557549</v>
       </c>
       <c r="R25" t="n">
-        <v>0.3447227435307231</v>
+        <v>0.3415599378636597</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3167888053269785</v>
+        <v>0.3161898604805853</v>
       </c>
       <c r="T25" t="n">
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0.08372395952046557</v>
+        <v>-0.1857820203303152</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W25" t="n">
-        <v>0.08372395952046557</v>
+        <v>0.1857820203303152</v>
       </c>
       <c r="X25" t="n">
-        <v>0.3447227435307231</v>
+        <v>0.6577497983442451</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.5</v>
+        <v>1.935504469987229</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &lt; 0.0</t>
         </is>
       </c>
       <c r="AA25" t="n">
-        <v>12.23613717653615</v>
+        <v>3.288748991721225</v>
       </c>
       <c r="AB25" t="n">
-        <v>12.23613717653615</v>
+        <v>3.288748991721225</v>
       </c>
     </row>
     <row r="26">
@@ -2957,55 +2957,55 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K26" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3803786574870912</v>
+        <v>0.4329004329004328</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2685025817555938</v>
+        <v>0.2424242424242424</v>
       </c>
       <c r="N26" t="n">
-        <v>0.3511187607573149</v>
+        <v>0.3246753246753247</v>
       </c>
       <c r="O26" t="n">
-        <v>0.09539969834087492</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="P26" t="n">
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1165722926010396</v>
+        <v>0.1161871972015239</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2643952151519466</v>
+        <v>0.2590926084503565</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6190324922470138</v>
+        <v>0.6247201943481197</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2679137314896989</v>
+        <v>0.300044869672795</v>
       </c>
       <c r="V26" t="n">
         <v>2</v>
       </c>
       <c r="W26" t="n">
-        <v>0.2679137314896989</v>
+        <v>0.300044869672795</v>
       </c>
       <c r="X26" t="n">
-        <v>0.6190324922470138</v>
+        <v>0.6247201943481197</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="AA26" t="n">
-        <v>25.95162461235069</v>
+        <v>3.123600971740598</v>
       </c>
       <c r="AB26" t="n">
-        <v>25.95162461235069</v>
+        <v>3.123600971740598</v>
       </c>
     </row>
     <row r="27">
@@ -3055,55 +3055,55 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="J27" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5636978579481398</v>
+        <v>0.5949500412764382</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2536640360766629</v>
+        <v>0.2395456745139343</v>
       </c>
       <c r="N27" t="n">
-        <v>0.1826381059751973</v>
+        <v>0.1655042842096274</v>
       </c>
       <c r="O27" t="n">
-        <v>0.09506172839506166</v>
+        <v>0.0985708477968541</v>
       </c>
       <c r="P27" t="n">
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.3553081675807302</v>
+        <v>0.3708726163433075</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3166251980902031</v>
+        <v>0.3150255188123561</v>
       </c>
       <c r="S27" t="n">
-        <v>0.3280666343290666</v>
+        <v>0.3141018648443366</v>
       </c>
       <c r="T27" t="n">
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2083896903674095</v>
+        <v>-0.2240774249331308</v>
       </c>
       <c r="V27" t="n">
         <v>-1</v>
       </c>
       <c r="W27" t="n">
-        <v>0.2083896903674095</v>
+        <v>0.2240774249331308</v>
       </c>
       <c r="X27" t="n">
-        <v>0.6446918324192698</v>
+        <v>0.6291273836566925</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.093023255813954</v>
+        <v>2.247311827956989</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="AA27" t="n">
-        <v>27.23459162096349</v>
+        <v>3.145636918283463</v>
       </c>
       <c r="AB27" t="n">
-        <v>27.23459162096349</v>
+        <v>3.145636918283463</v>
       </c>
     </row>
     <row r="28">
@@ -3153,55 +3153,55 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3803786574870912</v>
+        <v>0.41797976447172</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2685025817555938</v>
+        <v>0.2627301376679383</v>
       </c>
       <c r="N28" t="n">
-        <v>0.3511187607573149</v>
+        <v>0.3192900978603417</v>
       </c>
       <c r="O28" t="n">
-        <v>0.09539969834087492</v>
+        <v>0.08748196248196249</v>
       </c>
       <c r="P28" t="n">
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.1577702476860585</v>
+        <v>0.1630457610990916</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3783477455351054</v>
+        <v>0.3785328609147655</v>
       </c>
       <c r="S28" t="n">
-        <v>0.4638820067788361</v>
+        <v>0.4584213779861428</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0.1127632460215212</v>
+        <v>0.1391312801258011</v>
       </c>
       <c r="V28" t="n">
         <v>2</v>
       </c>
       <c r="W28" t="n">
-        <v>0.1127632460215212</v>
+        <v>0.1391312801258011</v>
       </c>
       <c r="X28" t="n">
-        <v>0.4638820067788361</v>
+        <v>0.4584213779861428</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="AA28" t="n">
-        <v>18.19410033894181</v>
+        <v>2.292106889930714</v>
       </c>
       <c r="AB28" t="n">
-        <v>18.19410033894181</v>
+        <v>2.292106889930714</v>
       </c>
     </row>
     <row r="29">
@@ -3261,13 +3261,13 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.2198767360298228</v>
+        <v>0.223759155178852</v>
       </c>
       <c r="R29" t="n">
-        <v>0.3762799186433601</v>
+        <v>0.3735870219714469</v>
       </c>
       <c r="S29" t="n">
-        <v>0.4038433453268171</v>
+        <v>0.4026538228497012</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="n">
-        <v>0.5961566546731829</v>
+        <v>0.5973461771502988</v>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr">
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="AA29" t="n">
-        <v>24.80783273365915</v>
+        <v>2.986730885751494</v>
       </c>
       <c r="AB29" t="n">
-        <v>24.80783273365915</v>
+        <v>2.986730885751494</v>
       </c>
     </row>
     <row r="30">
@@ -3339,13 +3339,13 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.6517450933228697</v>
+        <v>0.6553996133903959</v>
       </c>
       <c r="R30" t="n">
-        <v>0.2462058230352516</v>
+        <v>0.2410638081451136</v>
       </c>
       <c r="S30" t="n">
-        <v>0.1020490836418788</v>
+        <v>0.1035365784644905</v>
       </c>
       <c r="T30" t="n">
         <v>1</v>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="n">
-        <v>0.3482549066771303</v>
+        <v>0.3446003866096041</v>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr">
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="AA30" t="n">
-        <v>12.41274533385652</v>
+        <v>1.723001933048021</v>
       </c>
       <c r="AB30" t="n">
-        <v>12.41274533385652</v>
+        <v>1.723001933048021</v>
       </c>
     </row>
     <row r="31">
@@ -3417,13 +3417,13 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.2340252767550797</v>
+        <v>0.2360330562038147</v>
       </c>
       <c r="R31" t="n">
-        <v>0.4533277151477706</v>
+        <v>0.4495899136506157</v>
       </c>
       <c r="S31" t="n">
-        <v>0.3126470080971495</v>
+        <v>0.3143770301455694</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="n">
-        <v>0.5466722848522294</v>
+        <v>0.5504100863493844</v>
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr">
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="AA31" t="n">
-        <v>22.33361424261147</v>
+        <v>2.752050431746922</v>
       </c>
       <c r="AB31" t="n">
-        <v>22.33361424261147</v>
+        <v>2.752050431746922</v>
       </c>
     </row>
     <row r="32">
@@ -3495,13 +3495,13 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.4879230264703818</v>
+        <v>0.4795172639227532</v>
       </c>
       <c r="R32" t="n">
-        <v>0.2880531314804122</v>
+        <v>0.2875773278385532</v>
       </c>
       <c r="S32" t="n">
-        <v>0.224023842049206</v>
+        <v>0.2329054082386934</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="n">
-        <v>0.5120769735296182</v>
+        <v>0.5204827360772468</v>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="AA32" t="n">
-        <v>20.60384867648091</v>
+        <v>2.602413680386234</v>
       </c>
       <c r="AB32" t="n">
-        <v>20.60384867648091</v>
+        <v>2.602413680386234</v>
       </c>
     </row>
     <row r="33">
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.3248000313835386</v>
+        <v>0.3186060955835326</v>
       </c>
       <c r="R33" t="n">
-        <v>0.4291690095653991</v>
+        <v>0.4299583669421621</v>
       </c>
       <c r="S33" t="n">
-        <v>0.2460309590510623</v>
+        <v>0.2514355374743054</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="n">
-        <v>0.5708309904346009</v>
+        <v>0.5700416330578379</v>
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr">
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="AA33" t="n">
-        <v>23.54154952173005</v>
+        <v>2.85020816528919</v>
       </c>
       <c r="AB33" t="n">
-        <v>23.54154952173005</v>
+        <v>2.85020816528919</v>
       </c>
     </row>
     <row r="34">
@@ -3651,13 +3651,13 @@
         <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.2992059919222956</v>
+        <v>0.3070182371591425</v>
       </c>
       <c r="R34" t="n">
-        <v>0.2498873569671831</v>
+        <v>0.2545542891632127</v>
       </c>
       <c r="S34" t="n">
-        <v>0.4509066511105214</v>
+        <v>0.4384274736776448</v>
       </c>
       <c r="T34" t="n">
         <v>1</v>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
-        <v>0.5490933488894787</v>
+        <v>0.5615725263223552</v>
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="AA34" t="n">
-        <v>22.45466744447393</v>
+        <v>2.807862631611776</v>
       </c>
       <c r="AB34" t="n">
-        <v>22.45466744447393</v>
+        <v>2.807862631611776</v>
       </c>
     </row>
     <row r="35">
@@ -3729,13 +3729,13 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.3212718705413699</v>
+        <v>0.3237649678672507</v>
       </c>
       <c r="R35" t="n">
-        <v>0.390346703945361</v>
+        <v>0.3903995195351682</v>
       </c>
       <c r="S35" t="n">
-        <v>0.2883814255132691</v>
+        <v>0.2858355125975812</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="n">
-        <v>0.609653296054639</v>
+        <v>0.6096004804648318</v>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr">
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="AA35" t="n">
-        <v>25.48266480273195</v>
+        <v>3.048002402324159</v>
       </c>
       <c r="AB35" t="n">
-        <v>25.48266480273195</v>
+        <v>3.048002402324159</v>
       </c>
     </row>
     <row r="36">
@@ -3807,13 +3807,13 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.225668000183265</v>
+        <v>0.2238260684664798</v>
       </c>
       <c r="R36" t="n">
-        <v>0.4145494309309021</v>
+        <v>0.4161708195251439</v>
       </c>
       <c r="S36" t="n">
-        <v>0.3597825688858328</v>
+        <v>0.3600031120083761</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="n">
-        <v>0.5854505690690979</v>
+        <v>0.5838291804748561</v>
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="AA36" t="n">
-        <v>24.27252845345489</v>
+        <v>2.919145902374281</v>
       </c>
       <c r="AB36" t="n">
-        <v>24.27252845345489</v>
+        <v>2.919145902374281</v>
       </c>
     </row>
     <row r="37">
@@ -3885,13 +3885,13 @@
         <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.1112410798441106</v>
+        <v>0.1120165223774064</v>
       </c>
       <c r="R37" t="n">
-        <v>0.266165823801843</v>
+        <v>0.2698353424998143</v>
       </c>
       <c r="S37" t="n">
-        <v>0.6225930963540462</v>
+        <v>0.6181481351227792</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="n">
-        <v>0.3774069036459538</v>
+        <v>0.3818518648772208</v>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="AA37" t="n">
-        <v>13.87034518229769</v>
+        <v>1.909259324386104</v>
       </c>
       <c r="AB37" t="n">
-        <v>13.87034518229769</v>
+        <v>1.909259324386104</v>
       </c>
     </row>
     <row r="38">
@@ -3963,13 +3963,13 @@
         <v>2</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.2392316636670534</v>
+        <v>0.2405801587546016</v>
       </c>
       <c r="R38" t="n">
-        <v>0.3479242645368</v>
+        <v>0.3523714869042734</v>
       </c>
       <c r="S38" t="n">
-        <v>0.4128440717961466</v>
+        <v>0.407048354341125</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="n">
-        <v>0.5871559282038534</v>
+        <v>0.592951645658875</v>
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr">
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="AA38" t="n">
-        <v>24.35779641019267</v>
+        <v>2.964758228294375</v>
       </c>
       <c r="AB38" t="n">
-        <v>24.35779641019267</v>
+        <v>2.964758228294375</v>
       </c>
     </row>
     <row r="39">
@@ -4041,13 +4041,13 @@
         <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.2027394013853659</v>
+        <v>0.198872053428177</v>
       </c>
       <c r="R39" t="n">
-        <v>0.3507673632106973</v>
+        <v>0.3501070220679228</v>
       </c>
       <c r="S39" t="n">
-        <v>0.4464932354039368</v>
+        <v>0.4510209245039001</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="n">
-        <v>0.5535067645960632</v>
+        <v>0.5489790754960999</v>
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr">
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="AA39" t="n">
-        <v>22.67533822980316</v>
+        <v>2.7448953774805</v>
       </c>
       <c r="AB39" t="n">
-        <v>22.67533822980316</v>
+        <v>2.7448953774805</v>
       </c>
     </row>
     <row r="40">
@@ -4119,13 +4119,13 @@
         <v>2</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.1832356348957332</v>
+        <v>0.188470341582974</v>
       </c>
       <c r="R40" t="n">
-        <v>0.2403955547468579</v>
+        <v>0.2394887306904805</v>
       </c>
       <c r="S40" t="n">
-        <v>0.5763688103574088</v>
+        <v>0.5720409277265455</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
-        <v>0.4236311896425912</v>
+        <v>0.4279590722734545</v>
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr">
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="AA40" t="n">
-        <v>16.18155948212956</v>
+        <v>2.139795361367272</v>
       </c>
       <c r="AB40" t="n">
-        <v>16.18155948212956</v>
+        <v>2.139795361367272</v>
       </c>
     </row>
     <row r="41">
@@ -4197,13 +4197,13 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.4443843597147053</v>
+        <v>0.4414859472229207</v>
       </c>
       <c r="R41" t="n">
-        <v>0.3332789578993695</v>
+        <v>0.3348306941728106</v>
       </c>
       <c r="S41" t="n">
-        <v>0.2223366823859252</v>
+        <v>0.2236833586042686</v>
       </c>
       <c r="T41" t="n">
         <v>1</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="n">
-        <v>0.5556156402852948</v>
+        <v>0.5585140527770793</v>
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="AA41" t="n">
-        <v>22.78078201426474</v>
+        <v>2.792570263885397</v>
       </c>
       <c r="AB41" t="n">
-        <v>22.78078201426474</v>
+        <v>2.792570263885397</v>
       </c>
     </row>
     <row r="42">
@@ -4275,13 +4275,13 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.3771408747564578</v>
+        <v>0.3763245744414552</v>
       </c>
       <c r="R42" t="n">
-        <v>0.2843206683708714</v>
+        <v>0.2845306901402596</v>
       </c>
       <c r="S42" t="n">
-        <v>0.3385384568726707</v>
+        <v>0.3391447354182852</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="n">
-        <v>0.6228591252435423</v>
+        <v>0.6236754255585448</v>
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr">
@@ -4301,10 +4301,10 @@
         </is>
       </c>
       <c r="AA42" t="n">
-        <v>26.14295626217711</v>
+        <v>3.118377127792724</v>
       </c>
       <c r="AB42" t="n">
-        <v>26.14295626217711</v>
+        <v>3.118377127792724</v>
       </c>
     </row>
     <row r="43">
@@ -4481,13 +4481,13 @@
         <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.1866426214177104</v>
+        <v>0.182855882324076</v>
       </c>
       <c r="R45" t="n">
-        <v>0.333167626535192</v>
+        <v>0.332272585414535</v>
       </c>
       <c r="S45" t="n">
-        <v>0.4801897520470976</v>
+        <v>0.4848715322613889</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
@@ -4498,7 +4498,7 @@
       </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="n">
-        <v>0.5198102479529023</v>
+        <v>0.5151284677386111</v>
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr">
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="AA45" t="n">
-        <v>20.99051239764512</v>
+        <v>2.575642338693056</v>
       </c>
       <c r="AB45" t="n">
-        <v>20.99051239764512</v>
+        <v>2.575642338693056</v>
       </c>
     </row>
     <row r="46">

--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB19"/>
+  <dimension ref="A1:AB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,55 +605,55 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
         <v>2.63</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3723196069450807</v>
+        <v>0.3868633181006922</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2737644168713828</v>
+        <v>0.252750701159119</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3539159761835367</v>
+        <v>0.3603859807401887</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0743457839409527</v>
+        <v>0.05505806885491848</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4137128402005514</v>
+        <v>0.4120075461470778</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2256689955088615</v>
+        <v>0.2399522924860793</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3606181642905871</v>
+        <v>0.348040161366843</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04139323325547073</v>
+        <v>0.02514422804638555</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0.04139323325547073</v>
+        <v>0.02514422804638555</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4137128402005514</v>
+        <v>0.4120075461470778</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -703,55 +703,55 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K3" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.4992684711046086</v>
+        <v>0.473491773308958</v>
       </c>
       <c r="M3" t="n">
-        <v>0.263899049012436</v>
+        <v>0.2559414990859232</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2368324798829554</v>
+        <v>0.2705667276051189</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08266508266508255</v>
+        <v>0.05598455598455576</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3009886769347357</v>
+        <v>0.3024719433464994</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2186574243515443</v>
+        <v>0.2339276892420784</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4803538987137199</v>
+        <v>0.4636003674114222</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2435214188307645</v>
+        <v>0.1930336398063033</v>
       </c>
       <c r="V3" t="n">
         <v>2</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2435214188307645</v>
+        <v>0.1930336398063033</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4803538987137199</v>
+        <v>0.4636003674114222</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -801,55 +801,55 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5546995377503853</v>
+        <v>0.5830269494941478</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2357473035439137</v>
+        <v>0.2181301750994271</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2095531587057011</v>
+        <v>0.1988428754064251</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06045751633986929</v>
+        <v>0.05875714862384762</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4128180649634455</v>
+        <v>0.4053627591789879</v>
       </c>
       <c r="R4" t="n">
-        <v>0.316191233277152</v>
+        <v>0.3299841907325591</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2709907017594025</v>
+        <v>0.264653050088453</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1418814727869398</v>
+        <v>-0.1776641903151599</v>
       </c>
       <c r="V4" t="n">
         <v>-1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1418814727869398</v>
+        <v>0.1776641903151599</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5871819350365546</v>
+        <v>0.5946372408210121</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.117647058823529</v>
+        <v>2.265143171806167</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -899,55 +899,55 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4081222356252514</v>
+        <v>0.330520393811533</v>
       </c>
       <c r="M5" t="n">
-        <v>0.268194611982308</v>
+        <v>0.2644163150492265</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3236831523924407</v>
+        <v>0.4050632911392406</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06532448061683449</v>
+        <v>0.05053191489361697</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3662780538962588</v>
+        <v>0.3854648541884057</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1603744326479972</v>
+        <v>0.1423191655544808</v>
       </c>
       <c r="S5" t="n">
-        <v>0.473347513455744</v>
+        <v>0.4722159802571135</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1496643610633033</v>
+        <v>0.06715268911787292</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1496643610633033</v>
+        <v>0.06715268911787292</v>
       </c>
       <c r="X5" t="n">
-        <v>0.473347513455744</v>
+        <v>0.4722159802571135</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
@@ -1003,49 +1003,49 @@
         <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4532775453277545</v>
+        <v>0.4512126339537507</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2538354253835425</v>
+        <v>0.2526790750141004</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2928870292887029</v>
+        <v>0.2961082910321489</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05054945054945059</v>
+        <v>0.05535714285714288</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2403672920883207</v>
+        <v>0.2430156693782383</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1532880116659609</v>
+        <v>0.172066675491981</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6063446962457184</v>
+        <v>0.5849176551297807</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3134576669570155</v>
+        <v>0.2888093640976317</v>
       </c>
       <c r="V6" t="n">
         <v>2</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3134576669570155</v>
+        <v>0.2888093640976317</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6063446962457184</v>
+        <v>0.5849176551297807</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1095,55 +1095,55 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3828316115075915</v>
+        <v>0.3281853281853282</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2605381800537775</v>
+        <v>0.277992277992278</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3566302084386309</v>
+        <v>0.3938223938223938</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06616917996602956</v>
+        <v>0.05800653594771243</v>
       </c>
       <c r="P7" t="n">
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1929531369729005</v>
+        <v>0.1922850569335584</v>
       </c>
       <c r="R7" t="n">
-        <v>0.06507720501433815</v>
+        <v>0.06423020902147274</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7419696580127614</v>
+        <v>0.7434847340449688</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3853394495741305</v>
+        <v>0.349662340222575</v>
       </c>
       <c r="V7" t="n">
         <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3853394495741305</v>
+        <v>0.349662340222575</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7419696580127614</v>
+        <v>0.7434847340449688</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
@@ -1196,49 +1196,49 @@
         <v>2.35</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3997567403202919</v>
+        <v>0.4012738853503184</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2763024528684371</v>
+        <v>0.2619426751592356</v>
       </c>
       <c r="N8" t="n">
-        <v>0.323940806811271</v>
+        <v>0.3367834394904458</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06447714815933714</v>
+        <v>0.06045254981425208</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5252103048985133</v>
+        <v>0.5277473715805453</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2209823988276818</v>
+        <v>0.1669485086708993</v>
       </c>
       <c r="S8" t="n">
-        <v>0.253807296273805</v>
+        <v>0.3053041197485554</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1254535645782214</v>
+        <v>0.1264734862302269</v>
       </c>
       <c r="V8" t="n">
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1254535645782214</v>
+        <v>0.1264734862302269</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5252103048985133</v>
+        <v>0.5277473715805453</v>
       </c>
       <c r="Y8" t="n">
         <v>2.35</v>
@@ -1291,55 +1291,55 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3512470746979824</v>
+        <v>0.3299728576967816</v>
       </c>
       <c r="M9" t="n">
-        <v>0.271699943075204</v>
+        <v>0.2568437378829003</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3770529822268137</v>
+        <v>0.4131834044203179</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08250904924707525</v>
+        <v>0.05227510118814482</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1985979768843253</v>
+        <v>0.2046846001509572</v>
       </c>
       <c r="R9" t="n">
-        <v>0.157246904575213</v>
+        <v>0.2003671284217851</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6441551185404617</v>
+        <v>0.5949482714272577</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.267102136313648</v>
+        <v>0.1817648670069398</v>
       </c>
       <c r="V9" t="n">
         <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>0.267102136313648</v>
+        <v>0.1817648670069398</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6441551185404617</v>
+        <v>0.5949482714272577</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -1389,55 +1389,55 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="J10" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="K10" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5648296364052138</v>
+        <v>0.5645371577574968</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2389663846329751</v>
+        <v>0.2177314211212516</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1962039789618111</v>
+        <v>0.2177314211212516</v>
       </c>
       <c r="O10" t="n">
-        <v>0.07299717826033625</v>
+        <v>0.06069615964376096</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5540427532837758</v>
+        <v>0.5101760932850352</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2849093932203131</v>
+        <v>0.3323561098478121</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1610478534959111</v>
+        <v>0.1574677968671527</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.01078688312143794</v>
+        <v>-0.05436106447246158</v>
       </c>
       <c r="V10" t="n">
         <v>-1</v>
       </c>
       <c r="W10" t="n">
-        <v>0.01078688312143794</v>
+        <v>0.05436106447246158</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4459572467162242</v>
+        <v>0.4898239067149648</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.141618497109826</v>
+        <v>2.165</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
@@ -1487,55 +1487,55 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.4600259692079393</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2763157894736842</v>
+        <v>0.2357633092190688</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2763157894736842</v>
+        <v>0.3042107215729921</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06442577030812324</v>
+        <v>0.06038552321007074</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3201239244678765</v>
+        <v>0.3233849158712691</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1847526926088418</v>
+        <v>0.2114547644288544</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4951233829232818</v>
+        <v>0.4651603196998764</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2188075934495976</v>
+        <v>0.1609495981268844</v>
       </c>
       <c r="V11" t="n">
         <v>2</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2188075934495976</v>
+        <v>0.1609495981268844</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4951233829232818</v>
+        <v>0.4651603196998764</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
@@ -1585,55 +1585,55 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="J12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.6</v>
       </c>
-      <c r="K12" t="n">
-        <v>3.2</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.4465116279069767</v>
+        <v>0.4866595517609391</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2604651162790698</v>
+        <v>0.2497331910352187</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2930232558139535</v>
+        <v>0.263607257203842</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06646825396825395</v>
+        <v>0.05375618533513293</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2658318514540754</v>
+        <v>0.2573061840870435</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2096696849141911</v>
+        <v>0.1971455063979872</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5244984636317335</v>
+        <v>0.5455483095149692</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0.23147520781778</v>
+        <v>0.2819410523111273</v>
       </c>
       <c r="V12" t="n">
         <v>2</v>
       </c>
       <c r="W12" t="n">
-        <v>0.23147520781778</v>
+        <v>0.2819410523111273</v>
       </c>
       <c r="X12" t="n">
-        <v>0.5244984636317335</v>
+        <v>0.5455483095149692</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
@@ -1683,55 +1683,55 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4295665634674923</v>
+        <v>0.4600259692079393</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2554179566563468</v>
+        <v>0.2357633092190688</v>
       </c>
       <c r="N13" t="n">
-        <v>0.315015479876161</v>
+        <v>0.3042107215729921</v>
       </c>
       <c r="O13" t="n">
-        <v>0.05814905814905802</v>
+        <v>0.06038552321007074</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5424906369717334</v>
+        <v>0.5386537708866274</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2145488083580464</v>
+        <v>0.2599869325267105</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2429605546702203</v>
+        <v>0.2013592965866622</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1129240735042411</v>
+        <v>0.0786278016786881</v>
       </c>
       <c r="V13" t="n">
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1129240735042411</v>
+        <v>0.0786278016786881</v>
       </c>
       <c r="X13" t="n">
-        <v>0.5424906369717334</v>
+        <v>0.5386537708866274</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
@@ -1781,59 +1781,59 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="J14" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5210981189628877</v>
+        <v>0.5429892624813857</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2501270971021861</v>
+        <v>0.2194529351830081</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2287747839349263</v>
+        <v>0.2375578023356062</v>
       </c>
       <c r="O14" t="n">
-        <v>0.06612466124661243</v>
+        <v>0.05237545364566154</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4350477971680538</v>
+        <v>0.3685024625659371</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2797139176385446</v>
+        <v>0.428914582969479</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2852382851934016</v>
+        <v>0.2025829544645839</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.08605032179483396</v>
+        <v>0.209461647786471</v>
       </c>
       <c r="V14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.08605032179483396</v>
+        <v>0.209461647786471</v>
       </c>
       <c r="X14" t="n">
-        <v>0.5649522028319462</v>
+        <v>0.428914582969479</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.95859872611465</v>
+        <v>4.33</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; 0.0</t>
         </is>
       </c>
       <c r="AA14" t="n">
@@ -1879,55 +1879,55 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4612804025719877</v>
+        <v>0.472913616398243</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2521666200726866</v>
+        <v>0.2489019033674963</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2865529773553256</v>
+        <v>0.2781844802342606</v>
       </c>
       <c r="O15" t="n">
-        <v>0.05750184774575029</v>
+        <v>0.05727554179566563</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6563630536354403</v>
+        <v>0.6406292034534421</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1379215456414999</v>
+        <v>0.1428509825934022</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2057154007230597</v>
+        <v>0.2165198139531558</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1950826510634526</v>
+        <v>0.1677155870551991</v>
       </c>
       <c r="V15" t="n">
         <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1950826510634526</v>
+        <v>0.1677155870551991</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6563630536354403</v>
+        <v>0.6406292034534421</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
@@ -1938,340 +1938,6 @@
         <v>1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>SKZvN7pn</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45482.83333333334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>atlanta utd</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>indy eleven</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>167</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1672</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>us open cup</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.5716922089384578</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.2393484714755677</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.1889593195859745</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.114135657615376</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="n">
-        <v>1.17998417721519</v>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
-        </is>
-      </c>
-      <c r="AA16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>APpAklQ6</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45483</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>sacramento republic</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>seattle sounders</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>167</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1672</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>us open cup</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.3339882121807466</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.2652259332023576</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.4007858546168959</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.1089324618736383</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="n">
-        <v>1.227272727272727</v>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
-        </is>
-      </c>
-      <c r="AA17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>d0ReJPqB</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45483.91666666666</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>sporting kansas city</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>fc dallas</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>167</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1672</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>us open cup</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.4697360646787379</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.259522687667811</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.2707412476534513</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.06442753196299766</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.3156567540786541</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.2461677846984608</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.4381754612228851</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0.1674342135694338</v>
-      </c>
-      <c r="V18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.1674342135694338</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.4381754612228851</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
-        </is>
-      </c>
-      <c r="AA18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>0YXnLoFb</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45484</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>los angeles fc</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>new mexico</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>167</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1672</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>us open cup</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
-        </is>
-      </c>
-      <c r="AA19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB19" t="n">
         <v>1</v>
       </c>
     </row>

--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -572,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>GvBXzXxS</t>
+          <t>AszX60rp</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45486.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>cf montreal</t>
+          <t>atlanta utd</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>atlanta utd</t>
+          <t>columbus crew</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -605,85 +605,85 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3868633181006922</v>
+        <v>0.3107476635514019</v>
       </c>
       <c r="M2" t="n">
-        <v>0.252750701159119</v>
+        <v>0.2453271028037383</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3603859807401887</v>
+        <v>0.4439252336448598</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05505806885491848</v>
+        <v>0.07268170426065157</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4120075461470778</v>
+        <v>0.2237674119919342</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2399522924860793</v>
+        <v>0.1423251672385004</v>
       </c>
       <c r="S2" t="n">
-        <v>0.348040161366843</v>
+        <v>0.6339074207695654</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.02514422804638555</v>
+        <v>0.1899821871247056</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02514422804638555</v>
+        <v>0.1899821871247056</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4120075461470778</v>
+        <v>0.6339074207695654</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>1</v>
+        <v>26.69537103847827</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>26.69537103847827</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QHhnaCp6</t>
+          <t>jix3jCxF</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45486.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dc united</t>
+          <t>cf montreal</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>nashville sc</t>
+          <t>toronto fc</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -703,85 +703,85 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.473491773308958</v>
+        <v>0.4543876567020251</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2559414990859232</v>
+        <v>0.2451301832208293</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2705667276051189</v>
+        <v>0.3004821600771456</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05598455598455576</v>
+        <v>0.07354341794691299</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3024719433464994</v>
+        <v>0.4716665978042428</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2339276892420784</v>
+        <v>0.3057764132792871</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4636003674114222</v>
+        <v>0.22255698891647</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1930336398063033</v>
+        <v>0.01727894110221773</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1930336398063033</v>
+        <v>0.01727894110221773</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4636003674114222</v>
+        <v>0.4716665978042428</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>1</v>
+        <v>18.58332989021214</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>18.58332989021214</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Iigr0hVa</t>
+          <t>h6Py6Kcj</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45486.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fc cincinnati</t>
+          <t>inter miami</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>charlotte</t>
+          <t>chicago fire</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -801,76 +801,76 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="J4" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="K4" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5830269494941478</v>
+        <v>0.6142109006271417</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2181301750994271</v>
+        <v>0.197840563780953</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1988428754064251</v>
+        <v>0.1879485355919054</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05875714862384762</v>
+        <v>0.06412108703130381</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4053627591789879</v>
+        <v>0.4608860245548594</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3299841907325591</v>
+        <v>0.4119164577141742</v>
       </c>
       <c r="S4" t="n">
-        <v>0.264653050088453</v>
+        <v>0.1271975177309664</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1776641903151599</v>
+        <v>-0.1533248760722823</v>
       </c>
       <c r="V4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1776641903151599</v>
+        <v>-0.1533248760722823</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5946372408210121</v>
+        <v>0.4608860245548594</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.265143171806167</v>
+        <v>1.53</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>1</v>
+        <v>18.04430122774297</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>18.04430122774297</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>48ijbWaC</t>
+          <t>WdOu5vDd</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45486.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>orlando city</t>
+          <t>fc dallas</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -899,85 +899,85 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.88</v>
+        <v>1.9</v>
       </c>
       <c r="J5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.6</v>
       </c>
-      <c r="K5" t="n">
-        <v>2.35</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.330520393811533</v>
+        <v>0.4931506849315068</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2644163150492265</v>
+        <v>0.2465753424657534</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4050632911392406</v>
+        <v>0.2602739726027397</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05053191489361697</v>
+        <v>0.06725146198830423</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3854648541884057</v>
+        <v>0.4717603017795625</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1423191655544808</v>
+        <v>0.1640172582120076</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4722159802571135</v>
+        <v>0.3642224400084297</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06715268911787292</v>
+        <v>-0.02139038315194425</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06715268911787292</v>
+        <v>-0.02139038315194425</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4722159802571135</v>
+        <v>0.4717603017795625</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>1</v>
+        <v>18.58801508897812</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>18.58801508897812</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dYh0Wjoq</t>
+          <t>KCHNTNkc</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45486.85416666666</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>toronto fc</t>
+          <t>new york red bulls</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>philadelphia union</t>
+          <t>fc cincinnati</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -997,85 +997,85 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4512126339537507</v>
+        <v>0.4701492537313433</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2526790750141004</v>
+        <v>0.2611940298507463</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2961082910321489</v>
+        <v>0.2686567164179104</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05535714285714288</v>
+        <v>0.06349206349206349</v>
       </c>
       <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.3772373909516088</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3337991261284413</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2889634829199499</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.09291186277973451</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.09291186277973451</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.3772373909516088</v>
+      </c>
+      <c r="Y6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0.2430156693782383</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.172066675491981</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.5849176551297807</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.2888093640976317</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0.2888093640976317</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.5849176551297807</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>3.2</v>
-      </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>1</v>
+        <v>13.86186954758044</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>13.86186954758044</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>nXtecjFI</t>
+          <t>b3GRSs53</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45486.89583333334</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>austin fc</t>
+          <t>orlando city</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>seattle sounders</t>
+          <t>new york city</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1095,85 +1095,85 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="J7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.4</v>
       </c>
-      <c r="K7" t="n">
-        <v>2.4</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.3281853281853282</v>
+        <v>0.4776622646810902</v>
       </c>
       <c r="M7" t="n">
-        <v>0.277992277992278</v>
+        <v>0.2483843776341668</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3938223938223938</v>
+        <v>0.2739533576847429</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05800653594771243</v>
+        <v>0.0736048265460032</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1922850569335584</v>
+        <v>0.5546105282822001</v>
       </c>
       <c r="R7" t="n">
-        <v>0.06423020902147274</v>
+        <v>0.2939363270407325</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7434847340449688</v>
+        <v>0.1514531446770673</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.349662340222575</v>
+        <v>0.07694826360110996</v>
       </c>
       <c r="V7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.349662340222575</v>
+        <v>0.07694826360110996</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7434847340449688</v>
+        <v>0.5546105282822001</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>1</v>
+        <v>22.73052641411001</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>22.73052641411001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0zoadAUO</t>
+          <t>tS5WR1K9</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45486.89583333334</v>
+        <v>45493.85416666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>chicago fire</t>
+          <t>philadelphia union</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>new york city</t>
+          <t>nashville sc</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1193,85 +1193,85 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4012738853503184</v>
+        <v>0.5122702571735143</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2619426751592356</v>
+        <v>0.253366100169603</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3367834394904458</v>
+        <v>0.2343636426568828</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06045254981425208</v>
+        <v>0.0667183577019641</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5277473715805453</v>
+        <v>0.4103886683887465</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1669485086708993</v>
+        <v>0.4470546204411845</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3053041197485554</v>
+        <v>0.1425567111700689</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1264734862302269</v>
+        <v>0.1936885202715816</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1264734862302269</v>
+        <v>0.1936885202715816</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5277473715805453</v>
+        <v>0.4470546204411845</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.35</v>
+        <v>3.7</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>1</v>
+        <v>17.35273102205923</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>17.35273102205923</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EwZtLg7P</t>
+          <t>h29zRLZF</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45486.89583333334</v>
+        <v>45493.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fc dallas</t>
+          <t>austin fc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>los angeles galaxy</t>
+          <t>charlotte</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1291,85 +1291,85 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3299728576967816</v>
+        <v>0.3805181347150259</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2568437378829003</v>
+        <v>0.2741968911917099</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4131834044203179</v>
+        <v>0.3452849740932643</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05227510118814482</v>
+        <v>0.07265128273531629</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2046846001509572</v>
+        <v>0.3222766247980349</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2003671284217851</v>
+        <v>0.2344352758301926</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5949482714272577</v>
+        <v>0.4432880993717725</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1817648670069398</v>
+        <v>0.0980031252785083</v>
       </c>
       <c r="V9" t="n">
         <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1817648670069398</v>
+        <v>0.0980031252785083</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5949482714272577</v>
+        <v>0.4432880993717725</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>1</v>
+        <v>17.16440496858863</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>17.16440496858863</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GnL8GDFt</t>
+          <t>QF7rPa4S</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45486.89583333334</v>
+        <v>45493.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>houston dynamo</t>
+          <t>minnesota united</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>minnesota united</t>
+          <t>san jose earthquakes</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1389,85 +1389,85 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5645371577574968</v>
+        <v>0.5239520958083832</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2177314211212516</v>
+        <v>0.2245508982035928</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2177314211212516</v>
+        <v>0.2514970059880239</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06069615964376096</v>
+        <v>0.06031746031746033</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5101760932850352</v>
+        <v>0.27946395579522</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3323561098478121</v>
+        <v>0.1739022625123053</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1574677968671527</v>
+        <v>0.5466337816924747</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.05436106447246158</v>
+        <v>0.2951367757044507</v>
       </c>
       <c r="V10" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>0.05436106447246158</v>
+        <v>0.2951367757044507</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4898239067149648</v>
+        <v>0.5466337816924747</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.165</v>
+        <v>3.75</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>1</v>
+        <v>22.33168908462373</v>
       </c>
       <c r="AB10" t="n">
-        <v>1</v>
+        <v>22.33168908462373</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>zPi4VA0k</t>
+          <t>nP8vQukM</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45486.89583333334</v>
+        <v>45493.89583333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>sporting kansas city</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>st  louis city</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1487,76 +1487,76 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="J11" t="n">
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4600259692079393</v>
+        <v>0.5059732958538299</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2357633092190688</v>
+        <v>0.2340126493323963</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3042107215729921</v>
+        <v>0.2600140548137738</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06038552321007074</v>
+        <v>0.06831831831831825</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3233849158712691</v>
+        <v>0.3392164300507117</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2114547644288544</v>
+        <v>0.223741298361287</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4651603196998764</v>
+        <v>0.4370422715880014</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1609495981268844</v>
+        <v>0.1770282167742276</v>
       </c>
       <c r="V11" t="n">
         <v>2</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1609495981268844</v>
+        <v>0.1770282167742276</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4651603196998764</v>
+        <v>0.4370422715880014</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>1</v>
+        <v>16.85211357940007</v>
       </c>
       <c r="AB11" t="n">
-        <v>1</v>
+        <v>16.85211357940007</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>YNFDFXUn</t>
+          <t>69kBKJCq</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45486.9375</v>
+        <v>45493.9375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>new york red bulls</t>
+          <t>real salt lake</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1588,82 +1588,82 @@
         <v>1.95</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4866595517609391</v>
+        <v>0.4776622646810902</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2497331910352187</v>
+        <v>0.2483843776341668</v>
       </c>
       <c r="N12" t="n">
-        <v>0.263607257203842</v>
+        <v>0.2739533576847429</v>
       </c>
       <c r="O12" t="n">
-        <v>0.05375618533513293</v>
+        <v>0.0736048265460032</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2573061840870435</v>
+        <v>0.2797005830628954</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1971455063979872</v>
+        <v>0.2360734268906812</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5455483095149692</v>
+        <v>0.4842259900464234</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2819410523111273</v>
+        <v>0.2102726323616805</v>
       </c>
       <c r="V12" t="n">
         <v>2</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2819410523111273</v>
+        <v>0.2102726323616805</v>
       </c>
       <c r="X12" t="n">
-        <v>0.5455483095149692</v>
+        <v>0.4842259900464234</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>1</v>
+        <v>19.21129950232117</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>19.21129950232117</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>6yELDBaa</t>
+          <t>vNmJIcsd</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45486.97569444445</v>
+        <v>45493.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>portland timbers</t>
+          <t>seattle sounders</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>real salt lake</t>
+          <t>los angeles fc</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1683,85 +1683,85 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K13" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4600259692079393</v>
+        <v>0.3877149877149877</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2357633092190688</v>
+        <v>0.2584766584766585</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3042107215729921</v>
+        <v>0.3538083538083538</v>
       </c>
       <c r="O13" t="n">
-        <v>0.06038552321007074</v>
+        <v>0.07467258132657362</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5386537708866274</v>
+        <v>0.356771925226066</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2599869325267105</v>
+        <v>0.184535917014175</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2013592965866622</v>
+        <v>0.4586921577597591</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0786278016786881</v>
+        <v>0.1048838039514053</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0786278016786881</v>
+        <v>0.1048838039514053</v>
       </c>
       <c r="X13" t="n">
-        <v>0.5386537708866274</v>
+        <v>0.4586921577597591</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>1</v>
+        <v>17.93460788798796</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>17.93460788798796</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>CEEHEipg</t>
+          <t>MHXbihN8</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45486.97916666666</v>
+        <v>45493.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>los angeles fc</t>
+          <t>vancouver whitecaps</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>columbus crew</t>
+          <t>houston dynamo</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1781,85 +1781,85 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="J14" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5429892624813857</v>
+        <v>0.4833968426782798</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2194529351830081</v>
+        <v>0.2547632008709852</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2375578023356062</v>
+        <v>0.2618399564507349</v>
       </c>
       <c r="O14" t="n">
-        <v>0.05237545364566154</v>
+        <v>0.06086856086856107</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3685024625659371</v>
+        <v>0.4821355104292507</v>
       </c>
       <c r="R14" t="n">
-        <v>0.428914582969479</v>
+        <v>0.1407946202715505</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2025829544645839</v>
+        <v>0.3770698692991988</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0.209461647786471</v>
+        <v>-0.001261332249029079</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0.209461647786471</v>
+        <v>-0.001261332249029079</v>
       </c>
       <c r="X14" t="n">
-        <v>0.428914582969479</v>
+        <v>0.4821355104292507</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.33</v>
+        <v>1.95</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>1</v>
+        <v>19.10677552146253</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>19.10677552146253</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>4MWOCVE5</t>
+          <t>p0lFJwSk</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45486.97916666666</v>
+        <v>45493.98958333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>san jose earthquakes</t>
+          <t>los angeles galaxy</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>sporting kansas city</t>
+          <t>portland timbers</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1879,66 +1879,66 @@
         </is>
       </c>
       <c r="I15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5399533013361008</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2075820469581009</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2524646517057984</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.07052717457341728</v>
+      </c>
+      <c r="P15" t="n">
         <v>2</v>
       </c>
-      <c r="J15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.472913616398243</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2489019033674963</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.2781844802342606</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.05727554179566563</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
       <c r="Q15" t="n">
-        <v>0.6406292034534421</v>
+        <v>0.322235015899543</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1428509825934022</v>
+        <v>0.2533216753681761</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2165198139531558</v>
+        <v>0.4244433087322809</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1677155870551991</v>
+        <v>0.1719786570264825</v>
       </c>
       <c r="V15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1677155870551991</v>
+        <v>0.1719786570264825</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6406292034534421</v>
+        <v>0.4244433087322809</v>
       </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; 0.0</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>1</v>
+        <v>16.22216543661404</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>16.22216543661404</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/usa/predicciones.xlsx
+++ b/p6_deployment/data/usa/predicciones.xlsx
@@ -605,55 +605,53 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3107476635514019</v>
+        <v>0.3442622950819672</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2453271028037383</v>
+        <v>0.2254098360655738</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4439252336448598</v>
+        <v>0.430327868852459</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07268170426065157</v>
+        <v>0.05627705627705626</v>
       </c>
       <c r="P2" t="n">
         <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2237674119919342</v>
+        <v>0.3171981931068084</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1423251672385004</v>
+        <v>0.09734605233779631</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6339074207695654</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
+        <v>0.5854557545553953</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>0.1899821871247056</v>
+        <v>0.1551278857029363</v>
       </c>
       <c r="V2" t="n">
         <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1899821871247056</v>
+        <v>0.1551278857029363</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6339074207695654</v>
+        <v>0.5854557545553953</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -661,10 +659,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>26.69537103847827</v>
+        <v>24.27278772776977</v>
       </c>
       <c r="AB2" t="n">
-        <v>26.69537103847827</v>
+        <v>24.27278772776977</v>
       </c>
     </row>
     <row r="3">
@@ -703,55 +701,53 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
         <v>3.1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4543876567020251</v>
+        <v>0.4540461369461735</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2451301832208293</v>
+        <v>0.2383742218967411</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3004821600771456</v>
+        <v>0.3075796411570853</v>
       </c>
       <c r="O3" t="n">
-        <v>0.07354341794691299</v>
+        <v>0.04877112135176653</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4716665978042428</v>
+        <v>0.3952923866051036</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3057764132792871</v>
+        <v>0.3647683548218201</v>
       </c>
       <c r="S3" t="n">
-        <v>0.22255698891647</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
+        <v>0.2399392585730763</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>0.01727894110221773</v>
+        <v>-0.05875375034106994</v>
       </c>
       <c r="V3" t="n">
         <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01727894110221773</v>
+        <v>-0.05875375034106994</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4716665978042428</v>
+        <v>0.3952923866051036</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -759,10 +755,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>18.58332989021214</v>
+        <v>14.76461933025518</v>
       </c>
       <c r="AB3" t="n">
-        <v>18.58332989021214</v>
+        <v>14.76461933025518</v>
       </c>
     </row>
     <row r="4">
@@ -801,55 +797,53 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="J4" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6142109006271417</v>
+        <v>0.5129935875801552</v>
       </c>
       <c r="M4" t="n">
-        <v>0.197840563780953</v>
+        <v>0.2372595342558218</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1879485355919054</v>
+        <v>0.2497468781640229</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06412108703130381</v>
+        <v>0.05369843527738261</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4608860245548594</v>
+        <v>0.5651107829134597</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4119164577141742</v>
+        <v>0.3272216985544737</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1271975177309664</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
+        <v>0.1076675185320665</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>-0.1533248760722823</v>
+        <v>0.0521171953333045</v>
       </c>
       <c r="V4" t="n">
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1533248760722823</v>
+        <v>0.0521171953333045</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4608860245548594</v>
+        <v>0.5651107829134597</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -857,10 +851,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>18.04430122774297</v>
+        <v>23.25553914567299</v>
       </c>
       <c r="AB4" t="n">
-        <v>18.04430122774297</v>
+        <v>23.25553914567299</v>
       </c>
     </row>
     <row r="5">
@@ -899,55 +893,53 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="J5" t="n">
         <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4931506849315068</v>
+        <v>0.483021608861449</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2465753424657534</v>
+        <v>0.2478663519157435</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2602739726027397</v>
+        <v>0.2691120392228073</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06725146198830423</v>
+        <v>0.06169269327164084</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4717603017795625</v>
+        <v>0.5744780353398029</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1640172582120076</v>
+        <v>0.1582272001885582</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3642224400084297</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
+        <v>0.2672947644716389</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>-0.02139038315194425</v>
+        <v>0.09145642647835389</v>
       </c>
       <c r="V5" t="n">
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.02139038315194425</v>
+        <v>0.09145642647835389</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4717603017795625</v>
+        <v>0.5744780353398029</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
@@ -955,10 +947,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>18.58801508897812</v>
+        <v>23.72390176699015</v>
       </c>
       <c r="AB5" t="n">
-        <v>18.58801508897812</v>
+        <v>23.72390176699015</v>
       </c>
     </row>
     <row r="6">
@@ -997,55 +989,53 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4701492537313433</v>
+        <v>0.5190138736400838</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2611940298507463</v>
+        <v>0.2435372791695778</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2686567164179104</v>
+        <v>0.2374488471903384</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06349206349206349</v>
+        <v>0.05285834384195032</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3772373909516088</v>
+        <v>0.4270633323371791</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3337991261284413</v>
+        <v>0.2503592251123753</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2889634829199499</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
+        <v>0.3225774425504456</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>-0.09291186277973451</v>
+        <v>-0.09195054130290464</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.09291186277973451</v>
+        <v>-0.09195054130290464</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3772373909516088</v>
+        <v>0.4270633323371791</v>
       </c>
       <c r="Y6" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1053,10 +1043,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>13.86186954758044</v>
+        <v>16.35316661685896</v>
       </c>
       <c r="AB6" t="n">
-        <v>13.86186954758044</v>
+        <v>16.35316661685896</v>
       </c>
     </row>
     <row r="7">
@@ -1098,49 +1088,47 @@
         <v>1.95</v>
       </c>
       <c r="J7" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4776622646810902</v>
+        <v>0.486111111111111</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2483843776341668</v>
+        <v>0.2430555555555555</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2739533576847429</v>
+        <v>0.2708333333333333</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0736048265460032</v>
+        <v>0.05494505494505519</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5546105282822001</v>
+        <v>0.5439950475586786</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2939363270407325</v>
+        <v>0.254427650280188</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1514531446770673</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
+        <v>0.2015773021611334</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>0.07694826360110996</v>
+        <v>0.05788393644756751</v>
       </c>
       <c r="V7" t="n">
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07694826360110996</v>
+        <v>0.05788393644756751</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5546105282822001</v>
+        <v>0.5439950475586786</v>
       </c>
       <c r="Y7" t="n">
         <v>1.95</v>
@@ -1151,10 +1139,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>22.73052641411001</v>
+        <v>22.19975237793393</v>
       </c>
       <c r="AB7" t="n">
-        <v>22.73052641411001</v>
+        <v>22.19975237793393</v>
       </c>
     </row>
     <row r="8">
@@ -1193,55 +1181,53 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5122702571735143</v>
+        <v>0.5804311774461028</v>
       </c>
       <c r="M8" t="n">
-        <v>0.253366100169603</v>
+        <v>0.2280265339966833</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2343636426568828</v>
+        <v>0.1915422885572139</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0667183577019641</v>
+        <v>0.04415584415584406</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4103886683887465</v>
+        <v>0.5007784001595581</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4470546204411845</v>
+        <v>0.4077788553508637</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1425567111700689</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
+        <v>0.09144274448957818</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>0.1936885202715816</v>
+        <v>-0.07965277728654474</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1936885202715816</v>
+        <v>-0.07965277728654474</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4470546204411845</v>
+        <v>0.5007784001595581</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
@@ -1249,10 +1235,10 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>17.35273102205923</v>
+        <v>20.0389200079779</v>
       </c>
       <c r="AB8" t="n">
-        <v>17.35273102205923</v>
+        <v>20.0389200079779</v>
       </c>
     </row>
     <row r="9">
@@ -1291,52 +1277,52 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
         <v>2.7</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3805181347150259</v>
+        <v>0.3787575150300601</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2741968911917099</v>
+        <v>0.2705410821643286</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3452849740932643</v>
+        <v>0.3507014028056112</v>
       </c>
       <c r="O9" t="n">
-        <v>0.07265128273531629</v>
+        <v>0.05608465608465618</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3222766247980349</v>
+        <v>0.3059042849263034</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2344352758301926</v>
+        <v>0.2411412109970197</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4432880993717725</v>
+        <v>0.4529545040766769</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0980031252785083</v>
+        <v>0.1022531012710657</v>
       </c>
       <c r="V9" t="n">
         <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0980031252785083</v>
+        <v>0.1022531012710657</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4432880993717725</v>
+        <v>0.4529545040766769</v>
       </c>
       <c r="Y9" t="n">
         <v>2.7</v>
@@ -1347,10 +1333,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>17.16440496858863</v>
+        <v>17.64772520383385</v>
       </c>
       <c r="AB9" t="n">
-        <v>17.16440496858863</v>
+        <v>17.64772520383385</v>
       </c>
     </row>
     <row r="10">
@@ -1389,55 +1375,55 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5239520958083832</v>
+        <v>0.6020278833967048</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2245508982035928</v>
+        <v>0.1989860583016477</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2514970059880239</v>
+        <v>0.1989860583016477</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06031746031746033</v>
+        <v>0.05799530673818287</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.27946395579522</v>
+        <v>0.278032638556221</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1739022625123053</v>
+        <v>0.1727465748734516</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5466337816924747</v>
+        <v>0.5492207865703275</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2951367757044507</v>
+        <v>0.3502347282686798</v>
       </c>
       <c r="V10" t="n">
         <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2951367757044507</v>
+        <v>0.3502347282686798</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5466337816924747</v>
+        <v>0.5492207865703275</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
@@ -1445,10 +1431,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>22.33168908462373</v>
+        <v>22.46103932851637</v>
       </c>
       <c r="AB10" t="n">
-        <v>22.33168908462373</v>
+        <v>22.46103932851637</v>
       </c>
     </row>
     <row r="11">
@@ -1487,55 +1473,55 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5059732958538299</v>
+        <v>0.4698795180722892</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2340126493323963</v>
+        <v>0.2409638554216868</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2600140548137738</v>
+        <v>0.2891566265060241</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06831831831831825</v>
+        <v>0.0641025641025641</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3392164300507117</v>
+        <v>0.3544309155237736</v>
       </c>
       <c r="R11" t="n">
-        <v>0.223741298361287</v>
+        <v>0.2227510400406634</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4370422715880014</v>
+        <v>0.422818044435563</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1770282167742276</v>
+        <v>0.1336614179295388</v>
       </c>
       <c r="V11" t="n">
         <v>2</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1770282167742276</v>
+        <v>0.1336614179295388</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4370422715880014</v>
+        <v>0.422818044435563</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
@@ -1543,10 +1529,10 @@
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>16.85211357940007</v>
+        <v>16.14090222177815</v>
       </c>
       <c r="AB11" t="n">
-        <v>16.85211357940007</v>
+        <v>16.14090222177815</v>
       </c>
     </row>
     <row r="12">
@@ -1585,55 +1571,55 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4776622646810902</v>
+        <v>0.4689603590127151</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2483843776341668</v>
+        <v>0.2468212415856395</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2739533576847429</v>
+        <v>0.2842183994016455</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0736048265460032</v>
+        <v>0.06618819776714502</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2797005830628954</v>
+        <v>0.2638376359246903</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2360734268906812</v>
+        <v>0.2365134786384609</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4842259900464234</v>
+        <v>0.4996488854368489</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2102726323616805</v>
+        <v>0.2154304860352034</v>
       </c>
       <c r="V12" t="n">
         <v>2</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2102726323616805</v>
+        <v>0.2154304860352034</v>
       </c>
       <c r="X12" t="n">
-        <v>0.4842259900464234</v>
+        <v>0.4996488854368489</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
@@ -1641,10 +1627,10 @@
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>19.21129950232117</v>
+        <v>19.98244427184244</v>
       </c>
       <c r="AB12" t="n">
-        <v>19.21129950232117</v>
+        <v>19.98244427184244</v>
       </c>
     </row>
     <row r="13">
@@ -1683,55 +1669,55 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3877149877149877</v>
+        <v>0.4317656129529684</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2584766584766585</v>
+        <v>0.2713955281418658</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3538083538083538</v>
+        <v>0.2968388589051658</v>
       </c>
       <c r="O13" t="n">
-        <v>0.07467258132657362</v>
+        <v>0.05275974025974017</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.356771925226066</v>
+        <v>0.3588342128344589</v>
       </c>
       <c r="R13" t="n">
-        <v>0.184535917014175</v>
+        <v>0.1782778900516307</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4586921577597591</v>
+        <v>0.4628878971139105</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1048838039514053</v>
+        <v>0.1660490382087447</v>
       </c>
       <c r="V13" t="n">
         <v>2</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1048838039514053</v>
+        <v>0.1660490382087447</v>
       </c>
       <c r="X13" t="n">
-        <v>0.4586921577597591</v>
+        <v>0.4628878971139105</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
@@ -1739,10 +1725,10 @@
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>17.93460788798796</v>
+        <v>18.14439485569552</v>
       </c>
       <c r="AB13" t="n">
-        <v>17.93460788798796</v>
+        <v>18.14439485569552</v>
       </c>
     </row>
     <row r="14">
@@ -1781,55 +1767,55 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4833968426782798</v>
+        <v>0.4308880308880309</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2547632008709852</v>
+        <v>0.2633204633204634</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2618399564507349</v>
+        <v>0.3057915057915058</v>
       </c>
       <c r="O14" t="n">
-        <v>0.06086856086856107</v>
+        <v>0.05490387748452252</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4821355104292507</v>
+        <v>0.4648599986654099</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1407946202715505</v>
+        <v>0.1333223620980795</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3770698692991988</v>
+        <v>0.4018176392365106</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.001261332249029079</v>
+        <v>0.03397196777737899</v>
       </c>
       <c r="V14" t="n">
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.001261332249029079</v>
+        <v>0.03397196777737899</v>
       </c>
       <c r="X14" t="n">
-        <v>0.4821355104292507</v>
+        <v>0.4648599986654099</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
@@ -1837,10 +1823,10 @@
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>19.10677552146253</v>
+        <v>18.24299993327049</v>
       </c>
       <c r="AB14" t="n">
-        <v>19.10677552146253</v>
+        <v>18.24299993327049</v>
       </c>
     </row>
     <row r="15">
@@ -1879,55 +1865,55 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="J15" t="n">
         <v>4.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5399533013361008</v>
+        <v>0.4947263544851754</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2075820469581009</v>
+        <v>0.2099838526814855</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2524646517057984</v>
+        <v>0.2952897928333391</v>
       </c>
       <c r="O15" t="n">
-        <v>0.07052717457341728</v>
+        <v>0.05828243164630598</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.322235015899543</v>
+        <v>0.3290979258065211</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2533216753681761</v>
+        <v>0.2519301582287538</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4244433087322809</v>
+        <v>0.4189719159647251</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1719786570264825</v>
+        <v>0.123682123131386</v>
       </c>
       <c r="V15" t="n">
         <v>2</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1719786570264825</v>
+        <v>0.123682123131386</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4244433087322809</v>
+        <v>0.4189719159647251</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
@@ -1935,10 +1921,10 @@
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>16.22216543661404</v>
+        <v>15.94859579823625</v>
       </c>
       <c r="AB15" t="n">
-        <v>16.22216543661404</v>
+        <v>15.94859579823625</v>
       </c>
     </row>
   </sheetData>
